--- a/spreadsheets/bandgap_benchmark.xlsx
+++ b/spreadsheets/bandgap_benchmark.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD473"/>
+  <dimension ref="A1:AE473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -460,10 +460,11 @@
     <col width="11" customWidth="1" min="24" max="24"/>
     <col width="15" customWidth="1" min="25" max="25"/>
     <col width="9" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="71" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="71" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -599,20 +600,25 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>QSGW80</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>QSGW^</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>QSGW^+SOC</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Experimental</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
@@ -687,10 +693,11 @@
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>10.1021/jp077127w</t>
         </is>
@@ -714,7 +721,7 @@
         <v>0.04</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="3" t="n">
@@ -764,17 +771,18 @@
       </c>
       <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="3" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="inlineStr"/>
       <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="3" t="n">
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="AD3" s="2" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.saa.2012.03.044</t>
         </is>
@@ -849,10 +857,11 @@
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="3" t="n">
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="AD4" s="2" t="inlineStr">
+      <c r="AE4" s="2" t="inlineStr">
         <is>
           <t>10.1039/C5TA05248C</t>
         </is>
@@ -941,12 +950,15 @@
       <c r="Z5" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AA5" s="3" t="n">
+        <v>1.61</v>
+      </c>
       <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="3" t="n">
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD5" s="2" t="inlineStr">
+      <c r="AE5" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.41.3190</t>
         </is>
@@ -1021,10 +1033,10 @@
         <v>2.63</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>1.06</v>
@@ -1035,12 +1047,15 @@
       <c r="Z6" s="3" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AA6" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="3" t="n">
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="3" t="n">
         <v>0.18</v>
       </c>
-      <c r="AD6" s="2" t="inlineStr">
+      <c r="AE6" s="2" t="inlineStr">
         <is>
           <t>10.1016/S1293-2558(00)01128-6</t>
         </is>
@@ -1116,17 +1131,18 @@
         <v>1.06</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="inlineStr"/>
       <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="3" t="n">
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="AD7" s="2" t="inlineStr">
+      <c r="AE7" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -1209,10 +1225,11 @@
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="inlineStr"/>
       <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="3" t="n">
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="AD8" s="2" t="inlineStr">
+      <c r="AE8" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -1287,10 +1304,11 @@
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="inlineStr"/>
       <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="3" t="n">
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="3" t="n">
         <v>2.13</v>
       </c>
-      <c r="AD9" s="2" t="inlineStr">
+      <c r="AE9" s="2" t="inlineStr">
         <is>
           <t>10.1088/0953-8984/1/9/011</t>
         </is>
@@ -1365,10 +1383,11 @@
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="3" t="n">
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="3" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD10" s="2" t="inlineStr">
+      <c r="AE10" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -1443,10 +1462,11 @@
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="3" t="n">
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD11" s="2" t="inlineStr">
+      <c r="AE11" s="2" t="inlineStr">
         <is>
           <t>10.1002/zaac.200500476</t>
         </is>
@@ -1521,10 +1541,11 @@
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="inlineStr"/>
       <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="3" t="n">
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="3" t="n">
         <v>2.95</v>
       </c>
-      <c r="AD12" s="2" t="inlineStr">
+      <c r="AE12" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.4718342</t>
         </is>
@@ -1548,7 +1569,7 @@
         <v>1.91</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="3" t="n">
@@ -1558,7 +1579,7 @@
         <v>2.12</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.11</v>
@@ -1603,10 +1624,11 @@
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="inlineStr"/>
       <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="3" t="n">
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="3" t="n">
         <v>3.13</v>
       </c>
-      <c r="AD13" s="2" t="inlineStr">
+      <c r="AE13" s="2" t="inlineStr">
         <is>
           <t>10.1088/0022-3727/4/8/319</t>
         </is>
@@ -1687,10 +1709,11 @@
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="inlineStr"/>
       <c r="AB14" s="2" t="inlineStr"/>
-      <c r="AC14" s="3" t="n">
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="3" t="n">
         <v>2.55</v>
       </c>
-      <c r="AD14" s="2" t="inlineStr">
+      <c r="AE14" s="2" t="inlineStr">
         <is>
           <t>10.1088/0022-3727/4/8/319</t>
         </is>
@@ -1773,10 +1796,11 @@
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="inlineStr"/>
       <c r="AB15" s="2" t="inlineStr"/>
-      <c r="AC15" s="3" t="n">
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="AD15" s="2" t="inlineStr">
+      <c r="AE15" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.9.5203</t>
         </is>
@@ -1851,10 +1875,11 @@
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="inlineStr"/>
       <c r="AB16" s="2" t="inlineStr"/>
-      <c r="AC16" s="3" t="n">
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD16" s="2" t="inlineStr">
+      <c r="AE16" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic050357%2B</t>
         </is>
@@ -1929,10 +1954,11 @@
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="inlineStr"/>
       <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="3" t="n">
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD17" s="2" t="inlineStr">
+      <c r="AE17" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic050357%2B</t>
         </is>
@@ -2022,15 +2048,18 @@
         <v>2.94</v>
       </c>
       <c r="AA18" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB18" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AB18" s="3" t="n">
+      <c r="AC18" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="AC18" s="3" t="n">
+      <c r="AD18" s="3" t="n">
         <v>2.71</v>
       </c>
-      <c r="AD18" s="2" t="inlineStr">
+      <c r="AE18" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -2120,15 +2149,18 @@
         <v>3.58</v>
       </c>
       <c r="AA19" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB19" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AB19" s="3" t="n">
+      <c r="AC19" s="3" t="n">
         <v>2.98</v>
       </c>
-      <c r="AC19" s="3" t="n">
+      <c r="AD19" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="AD19" s="2" t="inlineStr">
+      <c r="AE19" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -2213,12 +2245,15 @@
       <c r="Z20" s="3" t="n">
         <v>3.18</v>
       </c>
-      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AA20" s="3" t="n">
+        <v>2.34</v>
+      </c>
       <c r="AB20" s="2" t="inlineStr"/>
-      <c r="AC20" s="3" t="n">
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="AD20" s="2" t="inlineStr">
+      <c r="AE20" s="2" t="inlineStr">
         <is>
           <t>10.1039/B211678B</t>
         </is>
@@ -2297,10 +2332,11 @@
       <c r="Z21" s="2" t="inlineStr"/>
       <c r="AA21" s="2" t="inlineStr"/>
       <c r="AB21" s="2" t="inlineStr"/>
-      <c r="AC21" s="3" t="n">
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="3" t="n">
         <v>2.71</v>
       </c>
-      <c r="AD21" s="2" t="inlineStr">
+      <c r="AE21" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.4.4455</t>
         </is>
@@ -2379,10 +2415,11 @@
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="inlineStr"/>
       <c r="AB22" s="2" t="inlineStr"/>
-      <c r="AC22" s="3" t="n">
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="3" t="n">
         <v>1.81</v>
       </c>
-      <c r="AD22" s="2" t="inlineStr">
+      <c r="AE22" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -2461,10 +2498,11 @@
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="inlineStr"/>
       <c r="AB23" s="2" t="inlineStr"/>
-      <c r="AC23" s="3" t="n">
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="AD23" s="2" t="inlineStr">
+      <c r="AE23" s="2" t="inlineStr">
         <is>
           <t>10.1007/s10853-005-6103-5</t>
         </is>
@@ -2549,10 +2587,11 @@
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="inlineStr"/>
       <c r="AB24" s="2" t="inlineStr"/>
-      <c r="AC24" s="3" t="n">
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="3" t="n">
         <v>3.02</v>
       </c>
-      <c r="AD24" s="2" t="inlineStr">
+      <c r="AE24" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -2642,15 +2681,18 @@
         <v>3.14</v>
       </c>
       <c r="AA25" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB25" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="AB25" s="3" t="n">
+      <c r="AC25" s="3" t="n">
         <v>2.49</v>
       </c>
-      <c r="AC25" s="3" t="n">
+      <c r="AD25" s="3" t="n">
         <v>2.91</v>
       </c>
-      <c r="AD25" s="2" t="inlineStr">
+      <c r="AE25" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -2725,10 +2767,10 @@
         <v>3.38</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>2.07</v>
@@ -2740,15 +2782,18 @@
         <v>2.76</v>
       </c>
       <c r="AA26" s="3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB26" s="3" t="n">
         <v>2.29</v>
       </c>
-      <c r="AB26" s="3" t="n">
+      <c r="AC26" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="AC26" s="3" t="n">
+      <c r="AD26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD26" s="2" t="inlineStr">
+      <c r="AE26" s="2" t="inlineStr">
         <is>
           <t>10.1021/jp806513t</t>
         </is>
@@ -2827,10 +2872,11 @@
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="inlineStr"/>
       <c r="AB27" s="2" t="inlineStr"/>
-      <c r="AC27" s="3" t="n">
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="3" t="n">
         <v>2.04</v>
       </c>
-      <c r="AD27" s="2" t="inlineStr">
+      <c r="AE27" s="2" t="inlineStr">
         <is>
           <t>10.1016/S0022-0248(02)01729-3</t>
         </is>
@@ -2909,10 +2955,11 @@
       <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" s="2" t="inlineStr"/>
       <c r="AB28" s="2" t="inlineStr"/>
-      <c r="AC28" s="3" t="n">
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD28" s="2" t="inlineStr">
+      <c r="AE28" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.7.4485</t>
         </is>
@@ -2991,10 +3038,11 @@
       <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="inlineStr"/>
       <c r="AB29" s="2" t="inlineStr"/>
-      <c r="AC29" s="3" t="n">
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="AD29" s="2" t="inlineStr">
+      <c r="AE29" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -3069,10 +3117,11 @@
       <c r="Z30" s="2" t="inlineStr"/>
       <c r="AA30" s="2" t="inlineStr"/>
       <c r="AB30" s="2" t="inlineStr"/>
-      <c r="AC30" s="3" t="n">
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="3" t="n">
         <v>1.55</v>
       </c>
-      <c r="AD30" s="2" t="inlineStr">
+      <c r="AE30" s="2" t="inlineStr">
         <is>
           <t>10.1002/zaac.200900004</t>
         </is>
@@ -3155,10 +3204,11 @@
       <c r="Z31" s="2" t="inlineStr"/>
       <c r="AA31" s="2" t="inlineStr"/>
       <c r="AB31" s="2" t="inlineStr"/>
-      <c r="AC31" s="3" t="n">
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD31" s="2" t="inlineStr">
+      <c r="AE31" s="2" t="inlineStr">
         <is>
           <t>10.1111/j.1151-2916.1990.tb06541.x</t>
         </is>
@@ -3248,15 +3298,18 @@
         <v>2.44</v>
       </c>
       <c r="AA32" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB32" s="3" t="n">
         <v>2.19</v>
       </c>
-      <c r="AB32" s="3" t="n">
+      <c r="AC32" s="3" t="n">
         <v>2.09</v>
       </c>
-      <c r="AC32" s="3" t="n">
+      <c r="AD32" s="3" t="n">
         <v>2.23</v>
       </c>
-      <c r="AD32" s="2" t="inlineStr">
+      <c r="AE32" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -3346,15 +3399,18 @@
         <v>6.8</v>
       </c>
       <c r="AA33" s="3" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AB33" s="3" t="n">
         <v>6.24</v>
       </c>
-      <c r="AB33" s="3" t="n">
+      <c r="AC33" s="3" t="n">
         <v>6.25</v>
       </c>
-      <c r="AC33" s="3" t="n">
+      <c r="AD33" s="3" t="n">
         <v>6.11</v>
       </c>
-      <c r="AD33" s="2" t="inlineStr">
+      <c r="AE33" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.1633965</t>
         </is>
@@ -3429,7 +3485,7 @@
         <v>2.29</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>2.5</v>
@@ -3444,15 +3500,18 @@
         <v>2.73</v>
       </c>
       <c r="AA34" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB34" s="3" t="n">
         <v>2.44</v>
       </c>
-      <c r="AB34" s="3" t="n">
+      <c r="AC34" s="3" t="n">
         <v>2.42</v>
       </c>
-      <c r="AC34" s="3" t="n">
+      <c r="AD34" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="AD34" s="2" t="inlineStr">
+      <c r="AE34" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -3527,10 +3586,11 @@
       <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" s="2" t="inlineStr"/>
       <c r="AB35" s="2" t="inlineStr"/>
-      <c r="AC35" s="3" t="n">
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="3" t="n">
         <v>7.89</v>
       </c>
-      <c r="AD35" s="2" t="inlineStr">
+      <c r="AE35" s="2" t="inlineStr">
         <is>
           <t>10.1111/jace.12757</t>
         </is>
@@ -3554,7 +3614,7 @@
         <v>1.13</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>1.15</v>
@@ -3566,7 +3626,7 @@
         <v>1.21</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>1</v>
@@ -3605,10 +3665,10 @@
         <v>1.75</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>1.87</v>
@@ -3620,15 +3680,18 @@
         <v>2</v>
       </c>
       <c r="AA36" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB36" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB36" s="3" t="n">
+      <c r="AC36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC36" s="3" t="n">
+      <c r="AD36" s="3" t="n">
         <v>1.69</v>
       </c>
-      <c r="AD36" s="2" t="inlineStr">
+      <c r="AE36" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -3718,15 +3781,18 @@
         <v>14.57</v>
       </c>
       <c r="AA37" s="3" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="AB37" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="AB37" s="3" t="n">
+      <c r="AC37" s="3" t="n">
         <v>13.64</v>
       </c>
-      <c r="AC37" s="3" t="n">
+      <c r="AD37" s="3" t="n">
         <v>14.15</v>
       </c>
-      <c r="AD37" s="2" t="inlineStr">
+      <c r="AE37" s="2" t="inlineStr">
         <is>
           <t>10.1016/0030-4018(86)90186-0</t>
         </is>
@@ -3801,10 +3867,11 @@
       <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="inlineStr"/>
       <c r="AB38" s="2" t="inlineStr"/>
-      <c r="AC38" s="3" t="n">
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="AD38" s="2" t="inlineStr">
+      <c r="AE38" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -3879,10 +3946,11 @@
       <c r="Z39" s="2" t="inlineStr"/>
       <c r="AA39" s="2" t="inlineStr"/>
       <c r="AB39" s="2" t="inlineStr"/>
-      <c r="AC39" s="3" t="n">
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="3" t="n">
         <v>2.15</v>
       </c>
-      <c r="AD39" s="2" t="inlineStr">
+      <c r="AE39" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -3965,10 +4033,11 @@
       <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="inlineStr"/>
       <c r="AB40" s="2" t="inlineStr"/>
-      <c r="AC40" s="3" t="n">
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="AD40" s="2" t="inlineStr">
+      <c r="AE40" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -3992,7 +4061,7 @@
         <v>2.03</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="3" t="n">
@@ -4002,7 +4071,7 @@
         <v>2.1</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>1.93</v>
@@ -4041,20 +4110,21 @@
         <v>3.04</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="X41" s="2" t="inlineStr"/>
       <c r="Y41" s="2" t="inlineStr"/>
       <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" s="2" t="inlineStr"/>
       <c r="AB41" s="2" t="inlineStr"/>
-      <c r="AC41" s="3" t="n">
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="3" t="n">
         <v>2.47</v>
       </c>
-      <c r="AD41" s="2" t="inlineStr">
+      <c r="AE41" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -4127,7 +4197,7 @@
         <v>1.01</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>1.48</v>
@@ -4137,10 +4207,11 @@
       <c r="Z42" s="2" t="inlineStr"/>
       <c r="AA42" s="2" t="inlineStr"/>
       <c r="AB42" s="2" t="inlineStr"/>
-      <c r="AC42" s="3" t="n">
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AD42" s="2" t="inlineStr">
+      <c r="AE42" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssa.2210860164</t>
         </is>
@@ -4215,10 +4286,11 @@
       <c r="Z43" s="2" t="inlineStr"/>
       <c r="AA43" s="2" t="inlineStr"/>
       <c r="AB43" s="2" t="inlineStr"/>
-      <c r="AC43" s="3" t="n">
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="3" t="n">
         <v>3.35</v>
       </c>
-      <c r="AD43" s="2" t="inlineStr">
+      <c r="AE43" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(83)90151-8</t>
         </is>
@@ -4293,10 +4365,11 @@
       <c r="Z44" s="2" t="inlineStr"/>
       <c r="AA44" s="2" t="inlineStr"/>
       <c r="AB44" s="2" t="inlineStr"/>
-      <c r="AC44" s="3" t="n">
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="3" t="n">
         <v>1.55</v>
       </c>
-      <c r="AD44" s="2" t="inlineStr">
+      <c r="AE44" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic2004358</t>
         </is>
@@ -4371,10 +4444,11 @@
       <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" s="2" t="inlineStr"/>
       <c r="AB45" s="2" t="inlineStr"/>
-      <c r="AC45" s="3" t="n">
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD45" s="2" t="inlineStr">
+      <c r="AE45" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.inorgchem.6b01202</t>
         </is>
@@ -4457,10 +4531,11 @@
       <c r="Z46" s="2" t="inlineStr"/>
       <c r="AA46" s="2" t="inlineStr"/>
       <c r="AB46" s="2" t="inlineStr"/>
-      <c r="AC46" s="3" t="n">
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="3" t="n">
         <v>4.17</v>
       </c>
-      <c r="AD46" s="2" t="inlineStr">
+      <c r="AE46" s="2" t="inlineStr">
         <is>
           <t>10.1002/ejic.201500929</t>
         </is>
@@ -4535,10 +4610,11 @@
       <c r="Z47" s="2" t="inlineStr"/>
       <c r="AA47" s="2" t="inlineStr"/>
       <c r="AB47" s="2" t="inlineStr"/>
-      <c r="AC47" s="3" t="n">
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="3" t="n">
         <v>4.28</v>
       </c>
-      <c r="AD47" s="2" t="inlineStr">
+      <c r="AE47" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2007.08.003</t>
         </is>
@@ -4613,10 +4689,11 @@
       <c r="Z48" s="2" t="inlineStr"/>
       <c r="AA48" s="2" t="inlineStr"/>
       <c r="AB48" s="2" t="inlineStr"/>
-      <c r="AC48" s="3" t="n">
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="3" t="n">
         <v>1.96</v>
       </c>
-      <c r="AD48" s="2" t="inlineStr">
+      <c r="AE48" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2015.08.012</t>
         </is>
@@ -4689,20 +4766,21 @@
         <v>2.21</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X49" s="2" t="inlineStr"/>
       <c r="Y49" s="2" t="inlineStr"/>
       <c r="Z49" s="2" t="inlineStr"/>
       <c r="AA49" s="2" t="inlineStr"/>
       <c r="AB49" s="2" t="inlineStr"/>
-      <c r="AC49" s="3" t="n">
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="3" t="n">
         <v>2.02</v>
       </c>
-      <c r="AD49" s="2" t="inlineStr">
+      <c r="AE49" s="2" t="inlineStr">
         <is>
           <t>10.1039/c7dt04178k</t>
         </is>
@@ -4785,10 +4863,11 @@
       <c r="Z50" s="2" t="inlineStr"/>
       <c r="AA50" s="2" t="inlineStr"/>
       <c r="AB50" s="2" t="inlineStr"/>
-      <c r="AC50" s="3" t="n">
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="3" t="n">
         <v>1.77</v>
       </c>
-      <c r="AD50" s="2" t="inlineStr">
+      <c r="AE50" s="2" t="inlineStr">
         <is>
           <t>10.1039/c7dt04178k</t>
         </is>
@@ -4863,10 +4942,11 @@
       <c r="Z51" s="2" t="inlineStr"/>
       <c r="AA51" s="2" t="inlineStr"/>
       <c r="AB51" s="2" t="inlineStr"/>
-      <c r="AC51" s="3" t="n">
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="3" t="n">
         <v>2.34</v>
       </c>
-      <c r="AD51" s="2" t="inlineStr">
+      <c r="AE51" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic100535q</t>
         </is>
@@ -4949,10 +5029,11 @@
       <c r="Z52" s="2" t="inlineStr"/>
       <c r="AA52" s="2" t="inlineStr"/>
       <c r="AB52" s="2" t="inlineStr"/>
-      <c r="AC52" s="3" t="n">
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="3" t="n">
         <v>3.71</v>
       </c>
-      <c r="AD52" s="2" t="inlineStr">
+      <c r="AE52" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.materresbull.2014.11.032</t>
         </is>
@@ -5028,17 +5109,18 @@
         <v>7.57</v>
       </c>
       <c r="W53" s="3" t="n">
-        <v>7.42</v>
+        <v>7.43</v>
       </c>
       <c r="X53" s="2" t="inlineStr"/>
       <c r="Y53" s="2" t="inlineStr"/>
       <c r="Z53" s="2" t="inlineStr"/>
       <c r="AA53" s="2" t="inlineStr"/>
       <c r="AB53" s="2" t="inlineStr"/>
-      <c r="AC53" s="3" t="n">
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AD53" s="2" t="inlineStr">
+      <c r="AE53" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.9.2679</t>
         </is>
@@ -5113,10 +5195,11 @@
       <c r="Z54" s="2" t="inlineStr"/>
       <c r="AA54" s="2" t="inlineStr"/>
       <c r="AB54" s="2" t="inlineStr"/>
-      <c r="AC54" s="3" t="n">
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="3" t="n">
         <v>2.47</v>
       </c>
-      <c r="AD54" s="2" t="inlineStr">
+      <c r="AE54" s="2" t="inlineStr">
         <is>
           <t>10.1039/c7ra05022d</t>
         </is>
@@ -5191,10 +5274,11 @@
       <c r="Z55" s="2" t="inlineStr"/>
       <c r="AA55" s="2" t="inlineStr"/>
       <c r="AB55" s="2" t="inlineStr"/>
-      <c r="AC55" s="3" t="n">
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD55" s="2" t="inlineStr">
+      <c r="AE55" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.chemmater.7b02475</t>
         </is>
@@ -5269,10 +5353,11 @@
       <c r="Z56" s="2" t="inlineStr"/>
       <c r="AA56" s="2" t="inlineStr"/>
       <c r="AB56" s="2" t="inlineStr"/>
-      <c r="AC56" s="3" t="n">
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="3" t="n">
         <v>1.72</v>
       </c>
-      <c r="AD56" s="2" t="inlineStr">
+      <c r="AE56" s="2" t="inlineStr">
         <is>
           <t>10.1039/c7ra05022d</t>
         </is>
@@ -5355,10 +5440,11 @@
       <c r="Z57" s="2" t="inlineStr"/>
       <c r="AA57" s="2" t="inlineStr"/>
       <c r="AB57" s="2" t="inlineStr"/>
-      <c r="AC57" s="3" t="n">
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD57" s="2" t="inlineStr">
+      <c r="AE57" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2007.03.021</t>
         </is>
@@ -5394,7 +5480,7 @@
         <v>6.79</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>6.87</v>
+        <v>6.86</v>
       </c>
       <c r="J58" s="3" t="n">
         <v>6.77</v>
@@ -5447,10 +5533,11 @@
       <c r="Z58" s="2" t="inlineStr"/>
       <c r="AA58" s="2" t="inlineStr"/>
       <c r="AB58" s="2" t="inlineStr"/>
-      <c r="AC58" s="3" t="n">
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="AD58" s="2" t="inlineStr">
+      <c r="AE58" s="2" t="inlineStr">
         <is>
           <t>10.1201/9781420050196</t>
         </is>
@@ -5525,10 +5612,11 @@
       <c r="Z59" s="2" t="inlineStr"/>
       <c r="AA59" s="2" t="inlineStr"/>
       <c r="AB59" s="2" t="inlineStr"/>
-      <c r="AC59" s="3" t="n">
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="AD59" s="2" t="inlineStr">
+      <c r="AE59" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssc.201300375</t>
         </is>
@@ -5603,10 +5691,11 @@
       <c r="Z60" s="2" t="inlineStr"/>
       <c r="AA60" s="2" t="inlineStr"/>
       <c r="AB60" s="2" t="inlineStr"/>
-      <c r="AC60" s="3" t="n">
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="3" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD60" s="2" t="inlineStr">
+      <c r="AE60" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic502939g</t>
         </is>
@@ -5681,7 +5770,7 @@
         <v>4.29</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="W61" s="3" t="n">
         <v>3.09</v>
@@ -5696,13 +5785,16 @@
         <v>4.54</v>
       </c>
       <c r="AA61" s="3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AB61" s="3" t="n">
         <v>4.07</v>
       </c>
-      <c r="AB61" s="2" t="inlineStr"/>
-      <c r="AC61" s="3" t="n">
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="AD61" s="2" t="inlineStr">
+      <c r="AE61" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.81.245123</t>
         </is>
@@ -5777,7 +5869,7 @@
         <v>3.31</v>
       </c>
       <c r="V62" s="3" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="W62" s="3" t="n">
         <v>3.54</v>
@@ -5792,15 +5884,18 @@
         <v>4.26</v>
       </c>
       <c r="AA62" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AB62" s="3" t="n">
         <v>3.84</v>
       </c>
-      <c r="AB62" s="3" t="n">
+      <c r="AC62" s="3" t="n">
         <v>3.78</v>
       </c>
-      <c r="AC62" s="3" t="n">
+      <c r="AD62" s="3" t="n">
         <v>3.81</v>
       </c>
-      <c r="AD62" s="2" t="inlineStr">
+      <c r="AE62" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-0248(90)90701-L</t>
         </is>
@@ -5875,10 +5970,11 @@
       <c r="Z63" s="2" t="inlineStr"/>
       <c r="AA63" s="2" t="inlineStr"/>
       <c r="AB63" s="2" t="inlineStr"/>
-      <c r="AC63" s="3" t="n">
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="AD63" s="2" t="inlineStr">
+      <c r="AE63" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic100535q</t>
         </is>
@@ -5953,7 +6049,7 @@
         <v>2.89</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="W64" s="3" t="n">
         <v>3.14</v>
@@ -5968,13 +6064,16 @@
         <v>3.85</v>
       </c>
       <c r="AA64" s="3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB64" s="3" t="n">
         <v>3.49</v>
       </c>
-      <c r="AB64" s="2" t="inlineStr"/>
-      <c r="AC64" s="3" t="n">
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="3" t="n">
         <v>3.42</v>
       </c>
-      <c r="AD64" s="2" t="inlineStr">
+      <c r="AE64" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-0248(90)90701-L</t>
         </is>
@@ -6049,10 +6148,11 @@
       <c r="Z65" s="2" t="inlineStr"/>
       <c r="AA65" s="2" t="inlineStr"/>
       <c r="AB65" s="2" t="inlineStr"/>
-      <c r="AC65" s="3" t="n">
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD65" s="2" t="inlineStr">
+      <c r="AE65" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.1498865</t>
         </is>
@@ -6141,12 +6241,15 @@
       <c r="Z66" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AA66" s="3" t="n">
+        <v>3.44</v>
+      </c>
       <c r="AB66" s="2" t="inlineStr"/>
-      <c r="AC66" s="3" t="n">
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="AD66" s="2" t="inlineStr">
+      <c r="AE66" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.cap.2016.12.013</t>
         </is>
@@ -6224,7 +6327,7 @@
         <v>2.98</v>
       </c>
       <c r="W67" s="3" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="X67" s="3" t="n">
         <v>2.75</v>
@@ -6239,12 +6342,15 @@
         <v>2.79</v>
       </c>
       <c r="AB67" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AC67" s="3" t="n">
         <v>2.52</v>
       </c>
-      <c r="AC67" s="3" t="n">
+      <c r="AD67" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="AD67" s="2" t="inlineStr">
+      <c r="AE67" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRev.163.219</t>
         </is>
@@ -6319,10 +6425,11 @@
       <c r="Z68" s="2" t="inlineStr"/>
       <c r="AA68" s="2" t="inlineStr"/>
       <c r="AB68" s="2" t="inlineStr"/>
-      <c r="AC68" s="3" t="n">
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="3" t="n">
         <v>2.95</v>
       </c>
-      <c r="AD68" s="2" t="inlineStr">
+      <c r="AE68" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm2015143</t>
         </is>
@@ -6397,10 +6504,10 @@
         <v>0.28</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>0.79</v>
+        <v>0.35</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X69" s="3" t="n">
         <v>0.25</v>
@@ -6411,12 +6518,15 @@
       <c r="Z69" s="3" t="n">
         <v>0.58</v>
       </c>
-      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AA69" s="3" t="n">
+        <v>0.37</v>
+      </c>
       <c r="AB69" s="2" t="inlineStr"/>
-      <c r="AC69" s="3" t="n">
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="3" t="n">
         <v>0.23</v>
       </c>
-      <c r="AD69" s="2" t="inlineStr">
+      <c r="AE69" s="2" t="inlineStr">
         <is>
           <t>10.1021/ja507890u</t>
         </is>
@@ -6499,10 +6609,11 @@
       <c r="Z70" s="2" t="inlineStr"/>
       <c r="AA70" s="2" t="inlineStr"/>
       <c r="AB70" s="2" t="inlineStr"/>
-      <c r="AC70" s="3" t="n">
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="AD70" s="2" t="inlineStr">
+      <c r="AE70" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic051240o</t>
         </is>
@@ -6580,7 +6691,7 @@
         <v>10.33</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>10.89</v>
@@ -6592,13 +6703,16 @@
         <v>11.61</v>
       </c>
       <c r="AA71" s="3" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="AB71" s="3" t="n">
         <v>10.82</v>
       </c>
-      <c r="AB71" s="2" t="inlineStr"/>
-      <c r="AC71" s="3" t="n">
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="3" t="n">
         <v>10.59</v>
       </c>
-      <c r="AD71" s="2" t="inlineStr">
+      <c r="AE71" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -6691,12 +6805,15 @@
         <v>3.98</v>
       </c>
       <c r="AB72" s="3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AC72" s="3" t="n">
         <v>3.83</v>
       </c>
-      <c r="AC72" s="3" t="n">
+      <c r="AD72" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AD72" s="2" t="inlineStr">
+      <c r="AE72" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.59.10071</t>
         </is>
@@ -6786,15 +6903,18 @@
         <v>3.26</v>
       </c>
       <c r="AA73" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB73" s="3" t="n">
         <v>2.96</v>
       </c>
-      <c r="AB73" s="3" t="n">
+      <c r="AC73" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="AC73" s="3" t="n">
+      <c r="AD73" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="AD73" s="2" t="inlineStr">
+      <c r="AE73" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -6873,10 +6993,11 @@
       <c r="Z74" s="2" t="inlineStr"/>
       <c r="AA74" s="2" t="inlineStr"/>
       <c r="AB74" s="2" t="inlineStr"/>
-      <c r="AC74" s="3" t="n">
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="3" t="n">
         <v>3.42</v>
       </c>
-      <c r="AD74" s="2" t="inlineStr">
+      <c r="AE74" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.solidstatesciences.2014.01.010</t>
         </is>
@@ -6951,10 +7072,11 @@
       <c r="Z75" s="2" t="inlineStr"/>
       <c r="AA75" s="2" t="inlineStr"/>
       <c r="AB75" s="2" t="inlineStr"/>
-      <c r="AC75" s="3" t="n">
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AD75" s="2" t="inlineStr">
+      <c r="AE75" s="2" t="inlineStr">
         <is>
           <t>10.1016/0301-0104(77)85033-7</t>
         </is>
@@ -7029,10 +7151,11 @@
       <c r="Z76" s="2" t="inlineStr"/>
       <c r="AA76" s="2" t="inlineStr"/>
       <c r="AB76" s="2" t="inlineStr"/>
-      <c r="AC76" s="3" t="n">
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="AD76" s="2" t="inlineStr">
+      <c r="AE76" s="2" t="inlineStr">
         <is>
           <t>10.1016/S1872-2067(15)60974-3</t>
         </is>
@@ -7107,10 +7230,11 @@
       <c r="Z77" s="2" t="inlineStr"/>
       <c r="AA77" s="2" t="inlineStr"/>
       <c r="AB77" s="2" t="inlineStr"/>
-      <c r="AC77" s="3" t="n">
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="3" t="n">
         <v>1.45</v>
       </c>
-      <c r="AD77" s="2" t="inlineStr">
+      <c r="AE77" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -7197,12 +7321,15 @@
       <c r="Z78" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="AA78" s="2" t="inlineStr"/>
+      <c r="AA78" s="3" t="n">
+        <v>0.45</v>
+      </c>
       <c r="AB78" s="2" t="inlineStr"/>
-      <c r="AC78" s="3" t="n">
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="3" t="n">
         <v>0.22</v>
       </c>
-      <c r="AD78" s="2" t="inlineStr">
+      <c r="AE78" s="2" t="inlineStr">
         <is>
           <t>10.1038/s41598-017-07211-x</t>
         </is>
@@ -7291,12 +7418,15 @@
       <c r="Z79" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="AA79" s="2" t="inlineStr"/>
+      <c r="AA79" s="3" t="n">
+        <v>0.44</v>
+      </c>
       <c r="AB79" s="2" t="inlineStr"/>
-      <c r="AC79" s="3" t="n">
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="AD79" s="2" t="inlineStr">
+      <c r="AE79" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.46.1553</t>
         </is>
@@ -7379,10 +7509,11 @@
       <c r="Z80" s="2" t="inlineStr"/>
       <c r="AA80" s="2" t="inlineStr"/>
       <c r="AB80" s="2" t="inlineStr"/>
-      <c r="AC80" s="3" t="n">
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="AD80" s="2" t="inlineStr">
+      <c r="AE80" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2011.11.013</t>
         </is>
@@ -7457,10 +7588,11 @@
       <c r="Z81" s="2" t="inlineStr"/>
       <c r="AA81" s="2" t="inlineStr"/>
       <c r="AB81" s="2" t="inlineStr"/>
-      <c r="AC81" s="3" t="n">
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="3" t="n">
         <v>3.94</v>
       </c>
-      <c r="AD81" s="2" t="inlineStr">
+      <c r="AE81" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.molcata.2015.02.022</t>
         </is>
@@ -7484,7 +7616,7 @@
         <v>2.27</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="3" t="n">
@@ -7494,7 +7626,7 @@
         <v>2.4</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="J82" s="3" t="n">
         <v>1.47</v>
@@ -7536,17 +7668,18 @@
         <v>3.21</v>
       </c>
       <c r="W82" s="3" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="X82" s="2" t="inlineStr"/>
       <c r="Y82" s="2" t="inlineStr"/>
       <c r="Z82" s="2" t="inlineStr"/>
       <c r="AA82" s="2" t="inlineStr"/>
       <c r="AB82" s="2" t="inlineStr"/>
-      <c r="AC82" s="3" t="n">
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD82" s="2" t="inlineStr">
+      <c r="AE82" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.4813486</t>
         </is>
@@ -7621,7 +7754,7 @@
         <v>0.87</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="W83" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -7635,12 +7768,15 @@
       <c r="Z83" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="AA83" s="2" t="inlineStr"/>
+      <c r="AA83" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="AB83" s="2" t="inlineStr"/>
-      <c r="AC83" s="3" t="n">
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="AD83" s="2" t="inlineStr">
+      <c r="AE83" s="2" t="inlineStr">
         <is>
           <t>10.1002/zaac.200400256</t>
         </is>
@@ -7725,10 +7861,11 @@
       <c r="Z84" s="2" t="inlineStr"/>
       <c r="AA84" s="2" t="inlineStr"/>
       <c r="AB84" s="2" t="inlineStr"/>
-      <c r="AC84" s="3" t="n">
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="3" t="n">
         <v>2.92</v>
       </c>
-      <c r="AD84" s="2" t="inlineStr">
+      <c r="AE84" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -7806,7 +7943,7 @@
         <v>3.43</v>
       </c>
       <c r="W85" s="3" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="X85" s="3" t="n">
         <v>3.77</v>
@@ -7817,12 +7954,15 @@
       <c r="Z85" s="3" t="n">
         <v>4.09</v>
       </c>
-      <c r="AA85" s="2" t="inlineStr"/>
+      <c r="AA85" s="3" t="n">
+        <v>3.79</v>
+      </c>
       <c r="AB85" s="2" t="inlineStr"/>
-      <c r="AC85" s="3" t="n">
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="3" t="n">
         <v>3.46</v>
       </c>
-      <c r="AD85" s="2" t="inlineStr">
+      <c r="AE85" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -7846,7 +7986,7 @@
         <v>1.48</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="F86" s="3" t="n">
         <v>1.5</v>
@@ -7911,12 +8051,15 @@
       <c r="Z86" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="AA86" s="2" t="inlineStr"/>
+      <c r="AA86" s="3" t="n">
+        <v>2.38</v>
+      </c>
       <c r="AB86" s="2" t="inlineStr"/>
-      <c r="AC86" s="3" t="n">
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="3" t="n">
         <v>1.89</v>
       </c>
-      <c r="AD86" s="2" t="inlineStr">
+      <c r="AE86" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -7940,7 +8083,7 @@
         <v>1.81</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="3" t="n">
@@ -7950,7 +8093,7 @@
         <v>1.97</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="J87" s="3" t="n">
         <v>1.55</v>
@@ -7989,20 +8132,21 @@
         <v>2.92</v>
       </c>
       <c r="V87" s="3" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="W87" s="3" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="X87" s="2" t="inlineStr"/>
       <c r="Y87" s="2" t="inlineStr"/>
       <c r="Z87" s="2" t="inlineStr"/>
       <c r="AA87" s="2" t="inlineStr"/>
       <c r="AB87" s="2" t="inlineStr"/>
-      <c r="AC87" s="3" t="n">
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="3" t="n">
         <v>1.95</v>
       </c>
-      <c r="AD87" s="2" t="inlineStr">
+      <c r="AE87" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -8036,7 +8180,7 @@
         <v>1.85</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J88" s="3" t="n">
         <v>1.38</v>
@@ -8075,20 +8219,21 @@
         <v>3.19</v>
       </c>
       <c r="V88" s="3" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="W88" s="3" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="X88" s="2" t="inlineStr"/>
       <c r="Y88" s="2" t="inlineStr"/>
       <c r="Z88" s="2" t="inlineStr"/>
       <c r="AA88" s="2" t="inlineStr"/>
       <c r="AB88" s="2" t="inlineStr"/>
-      <c r="AC88" s="3" t="n">
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="3" t="n">
         <v>1.89</v>
       </c>
-      <c r="AD88" s="2" t="inlineStr">
+      <c r="AE88" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -8164,17 +8309,18 @@
         <v>1.62</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X89" s="2" t="inlineStr"/>
       <c r="Y89" s="2" t="inlineStr"/>
       <c r="Z89" s="2" t="inlineStr"/>
       <c r="AA89" s="2" t="inlineStr"/>
       <c r="AB89" s="2" t="inlineStr"/>
-      <c r="AC89" s="3" t="n">
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD89" s="2" t="inlineStr">
+      <c r="AE89" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -8257,10 +8403,11 @@
       <c r="Z90" s="2" t="inlineStr"/>
       <c r="AA90" s="2" t="inlineStr"/>
       <c r="AB90" s="2" t="inlineStr"/>
-      <c r="AC90" s="3" t="n">
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD90" s="2" t="inlineStr">
+      <c r="AE90" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -8333,7 +8480,7 @@
         <v>2.62</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="W91" s="3" t="n">
         <v>2.2</v>
@@ -8343,10 +8490,11 @@
       <c r="Z91" s="2" t="inlineStr"/>
       <c r="AA91" s="2" t="inlineStr"/>
       <c r="AB91" s="2" t="inlineStr"/>
-      <c r="AC91" s="3" t="n">
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="AD91" s="2" t="inlineStr">
+      <c r="AE91" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -8424,7 +8572,7 @@
         <v>6.72</v>
       </c>
       <c r="W92" s="3" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
       <c r="X92" s="3" t="n">
         <v>6.66</v>
@@ -8436,15 +8584,18 @@
         <v>7</v>
       </c>
       <c r="AA92" s="3" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="AB92" s="3" t="n">
         <v>6.51</v>
       </c>
-      <c r="AB92" s="3" t="n">
+      <c r="AC92" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="AC92" s="3" t="n">
+      <c r="AD92" s="3" t="n">
         <v>6.36</v>
       </c>
-      <c r="AD92" s="2" t="inlineStr">
+      <c r="AE92" s="2" t="inlineStr">
         <is>
           <t>10.1088/0953-8984/20/7/075233</t>
         </is>
@@ -8540,9 +8691,12 @@
         <v>6.54</v>
       </c>
       <c r="AC93" s="3" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="AD93" s="3" t="n">
         <v>5.96</v>
       </c>
-      <c r="AD93" s="2" t="inlineStr">
+      <c r="AE93" s="2" t="inlineStr">
         <is>
           <t>10.1088/0953-8984/20/7/075233</t>
         </is>
@@ -8617,7 +8771,7 @@
         <v>1.89</v>
       </c>
       <c r="V94" s="3" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="W94" s="3" t="n">
         <v>2.18</v>
@@ -8638,9 +8792,12 @@
         <v>2.05</v>
       </c>
       <c r="AC94" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD94" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD94" s="2" t="inlineStr">
+      <c r="AE94" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -8664,7 +8821,7 @@
         <v>4.12</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="F95" s="3" t="n">
         <v>4.12</v>
@@ -8676,7 +8833,7 @@
         <v>4.15</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="J95" s="3" t="n">
         <v>4.15</v>
@@ -8715,10 +8872,10 @@
         <v>5.83</v>
       </c>
       <c r="V95" s="3" t="n">
-        <v>6</v>
+        <v>5.97</v>
       </c>
       <c r="W95" s="3" t="n">
-        <v>5.98</v>
+        <v>5.96</v>
       </c>
       <c r="X95" s="3" t="n">
         <v>5.82</v>
@@ -8730,15 +8887,18 @@
         <v>6.04</v>
       </c>
       <c r="AA95" s="3" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="AB95" s="3" t="n">
         <v>5.64</v>
       </c>
-      <c r="AB95" s="3" t="n">
+      <c r="AC95" s="3" t="n">
         <v>5.66</v>
       </c>
-      <c r="AC95" s="3" t="n">
+      <c r="AD95" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AD95" s="2" t="inlineStr">
+      <c r="AE95" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -8821,10 +8981,11 @@
       <c r="Z96" s="2" t="inlineStr"/>
       <c r="AA96" s="2" t="inlineStr"/>
       <c r="AB96" s="2" t="inlineStr"/>
-      <c r="AC96" s="3" t="n">
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="3" t="n">
         <v>0.46</v>
       </c>
-      <c r="AD96" s="2" t="inlineStr">
+      <c r="AE96" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -8900,17 +9061,18 @@
         <v>0.86</v>
       </c>
       <c r="W97" s="3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="X97" s="2" t="inlineStr"/>
       <c r="Y97" s="2" t="inlineStr"/>
       <c r="Z97" s="2" t="inlineStr"/>
       <c r="AA97" s="2" t="inlineStr"/>
       <c r="AB97" s="2" t="inlineStr"/>
-      <c r="AC97" s="3" t="n">
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD97" s="2" t="inlineStr">
+      <c r="AE97" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -8993,10 +9155,11 @@
       <c r="Z98" s="2" t="inlineStr"/>
       <c r="AA98" s="2" t="inlineStr"/>
       <c r="AB98" s="2" t="inlineStr"/>
-      <c r="AC98" s="3" t="n">
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="AD98" s="2" t="inlineStr">
+      <c r="AE98" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -9071,10 +9234,11 @@
       <c r="Z99" s="2" t="inlineStr"/>
       <c r="AA99" s="2" t="inlineStr"/>
       <c r="AB99" s="2" t="inlineStr"/>
-      <c r="AC99" s="3" t="n">
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="3" t="n">
         <v>2.32</v>
       </c>
-      <c r="AD99" s="2" t="inlineStr">
+      <c r="AE99" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jcrysgro.2015.10.032</t>
         </is>
@@ -9157,10 +9321,11 @@
       <c r="Z100" s="2" t="inlineStr"/>
       <c r="AA100" s="2" t="inlineStr"/>
       <c r="AB100" s="2" t="inlineStr"/>
-      <c r="AC100" s="3" t="n">
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD100" s="2" t="inlineStr">
+      <c r="AE100" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevLett.89.157601</t>
         </is>
@@ -9249,12 +9414,15 @@
       <c r="Z101" s="3" t="n">
         <v>9.42</v>
       </c>
-      <c r="AA101" s="2" t="inlineStr"/>
+      <c r="AA101" s="3" t="n">
+        <v>8.58</v>
+      </c>
       <c r="AB101" s="2" t="inlineStr"/>
-      <c r="AC101" s="3" t="n">
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="AD101" s="2" t="inlineStr">
+      <c r="AE101" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.9.2679</t>
         </is>
@@ -9278,7 +9446,7 @@
         <v>4.94</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="3" t="n">
@@ -9327,20 +9495,21 @@
         <v>9.970000000000001</v>
       </c>
       <c r="V102" s="3" t="n">
-        <v>8.01</v>
+        <v>8.02</v>
       </c>
       <c r="W102" s="3" t="n">
-        <v>7.7</v>
+        <v>7.69</v>
       </c>
       <c r="X102" s="2" t="inlineStr"/>
       <c r="Y102" s="2" t="inlineStr"/>
       <c r="Z102" s="2" t="inlineStr"/>
       <c r="AA102" s="2" t="inlineStr"/>
       <c r="AB102" s="2" t="inlineStr"/>
-      <c r="AC102" s="3" t="n">
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AD102" s="2" t="inlineStr">
+      <c r="AE102" s="2" t="inlineStr">
         <is>
           <t>10.1016/0169-4332(93)90365-I</t>
         </is>
@@ -9418,7 +9587,7 @@
         <v>10.94</v>
       </c>
       <c r="W103" s="3" t="n">
-        <v>10.6</v>
+        <v>10.61</v>
       </c>
       <c r="X103" s="3" t="n">
         <v>11.39</v>
@@ -9430,15 +9599,18 @@
         <v>12.72</v>
       </c>
       <c r="AA103" s="3" t="n">
-        <v>12.13</v>
+        <v>11.52</v>
       </c>
       <c r="AB103" s="3" t="n">
         <v>12.13</v>
       </c>
       <c r="AC103" s="3" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="AD103" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="AD103" s="2" t="inlineStr">
+      <c r="AE103" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.5.662</t>
         </is>
@@ -9521,10 +9693,11 @@
       <c r="Z104" s="2" t="inlineStr"/>
       <c r="AA104" s="2" t="inlineStr"/>
       <c r="AB104" s="2" t="inlineStr"/>
-      <c r="AC104" s="3" t="n">
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="AD104" s="2" t="inlineStr">
+      <c r="AE104" s="2" t="inlineStr">
         <is>
           <t>10.1021/jacs.7b05746</t>
         </is>
@@ -9609,10 +9782,11 @@
       <c r="Z105" s="2" t="inlineStr"/>
       <c r="AA105" s="2" t="inlineStr"/>
       <c r="AB105" s="2" t="inlineStr"/>
-      <c r="AC105" s="3" t="n">
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="AD105" s="2" t="inlineStr">
+      <c r="AE105" s="2" t="inlineStr">
         <is>
           <t>10.1515/znb-2003-0124</t>
         </is>
@@ -9702,15 +9876,18 @@
         <v>7.5</v>
       </c>
       <c r="AA106" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AB106" s="3" t="n">
         <v>6.97</v>
       </c>
-      <c r="AB106" s="3" t="n">
+      <c r="AC106" s="3" t="n">
         <v>6.95</v>
       </c>
-      <c r="AC106" s="3" t="n">
+      <c r="AD106" s="3" t="n">
         <v>6.88</v>
       </c>
-      <c r="AD106" s="2" t="inlineStr">
+      <c r="AE106" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-0248(90)90701-L</t>
         </is>
@@ -9785,7 +9962,7 @@
         <v>3.91</v>
       </c>
       <c r="V107" s="3" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="W107" s="3" t="n">
         <v>3.83</v>
@@ -9800,15 +9977,18 @@
         <v>4.93</v>
       </c>
       <c r="AA107" s="3" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AB107" s="3" t="n">
         <v>4.49</v>
       </c>
-      <c r="AB107" s="3" t="n">
+      <c r="AC107" s="3" t="n">
         <v>4.46</v>
       </c>
-      <c r="AC107" s="3" t="n">
+      <c r="AD107" s="3" t="n">
         <v>4.43</v>
       </c>
-      <c r="AD107" s="2" t="inlineStr">
+      <c r="AE107" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-0248(90)90701-L</t>
         </is>
@@ -9898,15 +10078,18 @@
         <v>4.34</v>
       </c>
       <c r="AA108" s="3" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AB108" s="3" t="n">
         <v>3.97</v>
       </c>
-      <c r="AB108" s="3" t="n">
+      <c r="AC108" s="3" t="n">
         <v>3.84</v>
       </c>
-      <c r="AC108" s="3" t="n">
+      <c r="AD108" s="3" t="n">
         <v>3.85</v>
       </c>
-      <c r="AD108" s="2" t="inlineStr">
+      <c r="AE108" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-0248(90)90701-L</t>
         </is>
@@ -9981,10 +10164,11 @@
       <c r="Z109" s="2" t="inlineStr"/>
       <c r="AA109" s="2" t="inlineStr"/>
       <c r="AB109" s="2" t="inlineStr"/>
-      <c r="AC109" s="3" t="n">
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="AD109" s="2" t="inlineStr">
+      <c r="AE109" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic034551c</t>
         </is>
@@ -10067,10 +10251,11 @@
       <c r="Z110" s="2" t="inlineStr"/>
       <c r="AA110" s="2" t="inlineStr"/>
       <c r="AB110" s="2" t="inlineStr"/>
-      <c r="AC110" s="3" t="n">
+      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AD110" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="AD110" s="2" t="inlineStr">
+      <c r="AE110" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic062120z</t>
         </is>
@@ -10094,7 +10279,7 @@
         <v>2.67</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="3" t="n">
@@ -10143,7 +10328,7 @@
         <v>4.45</v>
       </c>
       <c r="V111" s="3" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="W111" s="3" t="n">
         <v>4.25</v>
@@ -10153,10 +10338,11 @@
       <c r="Z111" s="2" t="inlineStr"/>
       <c r="AA111" s="2" t="inlineStr"/>
       <c r="AB111" s="2" t="inlineStr"/>
-      <c r="AC111" s="3" t="n">
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="3" t="n">
         <v>3.58</v>
       </c>
-      <c r="AD111" s="2" t="inlineStr">
+      <c r="AE111" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.118188</t>
         </is>
@@ -10234,7 +10420,7 @@
         <v>1.02</v>
       </c>
       <c r="W112" s="3" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="X112" s="3" t="n">
         <v>0.9</v>
@@ -10245,12 +10431,15 @@
       <c r="Z112" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="AA112" s="2" t="inlineStr"/>
+      <c r="AA112" s="3" t="n">
+        <v>0.93</v>
+      </c>
       <c r="AB112" s="2" t="inlineStr"/>
-      <c r="AC112" s="3" t="n">
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AD112" s="2" t="inlineStr">
+      <c r="AE112" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -10333,10 +10522,11 @@
       <c r="Z113" s="2" t="inlineStr"/>
       <c r="AA113" s="2" t="inlineStr"/>
       <c r="AB113" s="2" t="inlineStr"/>
-      <c r="AC113" s="3" t="n">
+      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AD113" s="3" t="n">
         <v>3.31</v>
       </c>
-      <c r="AD113" s="2" t="inlineStr">
+      <c r="AE113" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(93)90124-A</t>
         </is>
@@ -10419,10 +10609,11 @@
       <c r="Z114" s="2" t="inlineStr"/>
       <c r="AA114" s="2" t="inlineStr"/>
       <c r="AB114" s="2" t="inlineStr"/>
-      <c r="AC114" s="3" t="n">
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="AD114" s="2" t="inlineStr">
+      <c r="AE114" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssa.200406870</t>
         </is>
@@ -10505,10 +10696,11 @@
       <c r="Z115" s="2" t="inlineStr"/>
       <c r="AA115" s="2" t="inlineStr"/>
       <c r="AB115" s="2" t="inlineStr"/>
-      <c r="AC115" s="3" t="n">
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="3" t="n">
         <v>1.45</v>
       </c>
-      <c r="AD115" s="2" t="inlineStr">
+      <c r="AE115" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.1845582</t>
         </is>
@@ -10587,10 +10779,11 @@
       <c r="Z116" s="2" t="inlineStr"/>
       <c r="AA116" s="2" t="inlineStr"/>
       <c r="AB116" s="2" t="inlineStr"/>
-      <c r="AC116" s="3" t="n">
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD116" s="2" t="inlineStr">
+      <c r="AE116" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -10663,7 +10856,7 @@
         <v>2.21</v>
       </c>
       <c r="V117" s="3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W117" s="3" t="n">
         <v>1.34</v>
@@ -10673,10 +10866,11 @@
       <c r="Z117" s="2" t="inlineStr"/>
       <c r="AA117" s="2" t="inlineStr"/>
       <c r="AB117" s="2" t="inlineStr"/>
-      <c r="AC117" s="3" t="n">
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="3" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD117" s="2" t="inlineStr">
+      <c r="AE117" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -10712,7 +10906,7 @@
         <v>2.37</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>2.08</v>
@@ -10754,7 +10948,7 @@
         <v>3.72</v>
       </c>
       <c r="W118" s="3" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="X118" s="3" t="n">
         <v>3.88</v>
@@ -10765,12 +10959,15 @@
       <c r="Z118" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="AA118" s="2" t="inlineStr"/>
+      <c r="AA118" s="3" t="n">
+        <v>3.88</v>
+      </c>
       <c r="AB118" s="2" t="inlineStr"/>
-      <c r="AC118" s="3" t="n">
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="3" t="n">
         <v>3.47</v>
       </c>
-      <c r="AD118" s="2" t="inlineStr">
+      <c r="AE118" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -10845,10 +11042,11 @@
       <c r="Z119" s="2" t="inlineStr"/>
       <c r="AA119" s="2" t="inlineStr"/>
       <c r="AB119" s="2" t="inlineStr"/>
-      <c r="AC119" s="3" t="n">
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="3" t="n">
         <v>2.44</v>
       </c>
-      <c r="AD119" s="2" t="inlineStr">
+      <c r="AE119" s="2" t="inlineStr">
         <is>
           <t>10.1143/JJAP.19.103</t>
         </is>
@@ -10931,10 +11129,11 @@
       <c r="Z120" s="2" t="inlineStr"/>
       <c r="AA120" s="2" t="inlineStr"/>
       <c r="AB120" s="2" t="inlineStr"/>
-      <c r="AC120" s="3" t="n">
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="3" t="n">
         <v>1.55</v>
       </c>
-      <c r="AD120" s="2" t="inlineStr">
+      <c r="AE120" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -11010,17 +11209,18 @@
         <v>1.82</v>
       </c>
       <c r="W121" s="3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X121" s="2" t="inlineStr"/>
       <c r="Y121" s="2" t="inlineStr"/>
       <c r="Z121" s="2" t="inlineStr"/>
       <c r="AA121" s="2" t="inlineStr"/>
       <c r="AB121" s="2" t="inlineStr"/>
-      <c r="AC121" s="3" t="n">
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="AD121" s="2" t="inlineStr">
+      <c r="AE121" s="2" t="inlineStr">
         <is>
           <t>10.1088/0953-8984/2/28/003</t>
         </is>
@@ -11044,7 +11244,7 @@
         <v>0.23</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="3" t="n">
@@ -11054,7 +11254,7 @@
         <v>0.33</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="J122" s="3" t="n">
         <v>0.32</v>
@@ -11093,20 +11293,21 @@
         <v>1.13</v>
       </c>
       <c r="V122" s="3" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="W122" s="3" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="X122" s="2" t="inlineStr"/>
       <c r="Y122" s="2" t="inlineStr"/>
       <c r="Z122" s="2" t="inlineStr"/>
       <c r="AA122" s="2" t="inlineStr"/>
       <c r="AB122" s="2" t="inlineStr"/>
-      <c r="AC122" s="3" t="n">
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD122" s="2" t="inlineStr">
+      <c r="AE122" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -11196,15 +11397,18 @@
         <v>2.97</v>
       </c>
       <c r="AA123" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB123" s="3" t="n">
         <v>2.58</v>
       </c>
-      <c r="AB123" s="3" t="n">
+      <c r="AC123" s="3" t="n">
         <v>2.56</v>
       </c>
-      <c r="AC123" s="3" t="n">
+      <c r="AD123" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="AD123" s="2" t="inlineStr">
+      <c r="AE123" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -11279,10 +11483,11 @@
       <c r="Z124" s="2" t="inlineStr"/>
       <c r="AA124" s="2" t="inlineStr"/>
       <c r="AB124" s="2" t="inlineStr"/>
-      <c r="AC124" s="3" t="n">
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="3" t="n">
         <v>0.46</v>
       </c>
-      <c r="AD124" s="2" t="inlineStr">
+      <c r="AE124" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -11357,10 +11562,11 @@
       <c r="Z125" s="2" t="inlineStr"/>
       <c r="AA125" s="2" t="inlineStr"/>
       <c r="AB125" s="2" t="inlineStr"/>
-      <c r="AC125" s="3" t="n">
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD125" s="2" t="inlineStr">
+      <c r="AE125" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm701995d</t>
         </is>
@@ -11450,15 +11656,18 @@
         <v>2.33</v>
       </c>
       <c r="AA126" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB126" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AB126" s="3" t="n">
+      <c r="AC126" s="3" t="n">
         <v>1.88</v>
       </c>
-      <c r="AC126" s="3" t="n">
+      <c r="AD126" s="3" t="n">
         <v>1.74</v>
       </c>
-      <c r="AD126" s="2" t="inlineStr">
+      <c r="AE126" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -11548,15 +11757,18 @@
         <v>2.39</v>
       </c>
       <c r="AA127" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB127" s="3" t="n">
         <v>2.08</v>
       </c>
-      <c r="AB127" s="3" t="n">
+      <c r="AC127" s="3" t="n">
         <v>1.96</v>
       </c>
-      <c r="AC127" s="3" t="n">
+      <c r="AD127" s="3" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD127" s="2" t="inlineStr">
+      <c r="AE127" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -11639,10 +11851,11 @@
       <c r="Z128" s="2" t="inlineStr"/>
       <c r="AA128" s="2" t="inlineStr"/>
       <c r="AB128" s="2" t="inlineStr"/>
-      <c r="AC128" s="3" t="n">
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="3" t="n">
         <v>1.55</v>
       </c>
-      <c r="AD128" s="2" t="inlineStr">
+      <c r="AE128" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -11725,10 +11938,11 @@
       <c r="Z129" s="2" t="inlineStr"/>
       <c r="AA129" s="2" t="inlineStr"/>
       <c r="AB129" s="2" t="inlineStr"/>
-      <c r="AC129" s="3" t="n">
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="3" t="n">
         <v>2.09</v>
       </c>
-      <c r="AD129" s="2" t="inlineStr">
+      <c r="AE129" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -11752,7 +11966,7 @@
         <v>0.11</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="3" t="n">
@@ -11762,7 +11976,7 @@
         <v>0.11</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="J130" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -11801,20 +12015,21 @@
         <v>0.73</v>
       </c>
       <c r="V130" s="3" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="W130" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="X130" s="2" t="inlineStr"/>
       <c r="Y130" s="2" t="inlineStr"/>
       <c r="Z130" s="2" t="inlineStr"/>
       <c r="AA130" s="2" t="inlineStr"/>
       <c r="AB130" s="2" t="inlineStr"/>
-      <c r="AC130" s="3" t="n">
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="3" t="n">
         <v>0.26</v>
       </c>
-      <c r="AD130" s="2" t="inlineStr">
+      <c r="AE130" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -11838,7 +12053,7 @@
         <v>1.03</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="3" t="n">
@@ -11893,10 +12108,11 @@
       <c r="Z131" s="2" t="inlineStr"/>
       <c r="AA131" s="2" t="inlineStr"/>
       <c r="AB131" s="2" t="inlineStr"/>
-      <c r="AC131" s="3" t="n">
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="AD131" s="2" t="inlineStr">
+      <c r="AE131" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm049249w</t>
         </is>
@@ -11977,10 +12193,11 @@
       <c r="Z132" s="2" t="inlineStr"/>
       <c r="AA132" s="2" t="inlineStr"/>
       <c r="AB132" s="2" t="inlineStr"/>
-      <c r="AC132" s="3" t="n">
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="AD132" s="2" t="inlineStr">
+      <c r="AE132" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -12055,10 +12272,10 @@
         <v>2.06</v>
       </c>
       <c r="V133" s="3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W133" s="3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X133" s="3" t="n">
         <v>1.76</v>
@@ -12070,15 +12287,18 @@
         <v>2.19</v>
       </c>
       <c r="AA133" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB133" s="3" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB133" s="3" t="n">
+      <c r="AC133" s="3" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC133" s="3" t="n">
+      <c r="AD133" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="AD133" s="2" t="inlineStr">
+      <c r="AE133" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -12157,10 +12377,11 @@
       <c r="Z134" s="2" t="inlineStr"/>
       <c r="AA134" s="2" t="inlineStr"/>
       <c r="AB134" s="2" t="inlineStr"/>
-      <c r="AC134" s="3" t="n">
+      <c r="AC134" s="2" t="inlineStr"/>
+      <c r="AD134" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="AD134" s="2" t="inlineStr">
+      <c r="AE134" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.340078</t>
         </is>
@@ -12243,10 +12464,11 @@
       <c r="Z135" s="2" t="inlineStr"/>
       <c r="AA135" s="2" t="inlineStr"/>
       <c r="AB135" s="2" t="inlineStr"/>
-      <c r="AC135" s="3" t="n">
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="3" t="n">
         <v>2.19</v>
       </c>
-      <c r="AD135" s="2" t="inlineStr">
+      <c r="AE135" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.chemmater.5b04231</t>
         </is>
@@ -12319,7 +12541,7 @@
         <v>4.08</v>
       </c>
       <c r="V136" s="3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="W136" s="3" t="n">
         <v>3.03</v>
@@ -12329,10 +12551,11 @@
       <c r="Z136" s="2" t="inlineStr"/>
       <c r="AA136" s="2" t="inlineStr"/>
       <c r="AB136" s="2" t="inlineStr"/>
-      <c r="AC136" s="3" t="n">
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="AD136" s="2" t="inlineStr">
+      <c r="AE136" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.chemmater.5b04231</t>
         </is>
@@ -12407,10 +12630,11 @@
       <c r="Z137" s="2" t="inlineStr"/>
       <c r="AA137" s="2" t="inlineStr"/>
       <c r="AB137" s="2" t="inlineStr"/>
-      <c r="AC137" s="3" t="n">
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="3" t="n">
         <v>1.77</v>
       </c>
-      <c r="AD137" s="2" t="inlineStr">
+      <c r="AE137" s="2" t="inlineStr">
         <is>
           <t>10.1002/(SICI)1521-3749(199808)624:8&lt;1285::AID-ZAAC1285&gt;3.0.CO;2-5</t>
         </is>
@@ -12434,7 +12658,7 @@
         <v>0.89</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="3" t="n">
@@ -12489,10 +12713,11 @@
       <c r="Z138" s="2" t="inlineStr"/>
       <c r="AA138" s="2" t="inlineStr"/>
       <c r="AB138" s="2" t="inlineStr"/>
-      <c r="AC138" s="3" t="n">
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="AD138" s="2" t="inlineStr">
+      <c r="AE138" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.59.7925</t>
         </is>
@@ -12516,7 +12741,7 @@
         <v>1.09</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="3" t="n">
@@ -12526,7 +12751,7 @@
         <v>1.08</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="J139" s="3" t="n">
         <v>0.98</v>
@@ -12571,10 +12796,11 @@
       <c r="Z139" s="2" t="inlineStr"/>
       <c r="AA139" s="2" t="inlineStr"/>
       <c r="AB139" s="2" t="inlineStr"/>
-      <c r="AC139" s="3" t="n">
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="3" t="n">
         <v>2.04</v>
       </c>
-      <c r="AD139" s="2" t="inlineStr">
+      <c r="AE139" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.59.7925</t>
         </is>
@@ -12608,7 +12834,7 @@
         <v>0.82</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J140" s="3" t="n">
         <v>0.71</v>
@@ -12653,10 +12879,11 @@
       <c r="Z140" s="2" t="inlineStr"/>
       <c r="AA140" s="2" t="inlineStr"/>
       <c r="AB140" s="2" t="inlineStr"/>
-      <c r="AC140" s="3" t="n">
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="AD140" s="2" t="inlineStr">
+      <c r="AE140" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.59.7925</t>
         </is>
@@ -12731,10 +12958,11 @@
       <c r="Z141" s="2" t="inlineStr"/>
       <c r="AA141" s="2" t="inlineStr"/>
       <c r="AB141" s="2" t="inlineStr"/>
-      <c r="AC141" s="3" t="n">
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="AD141" s="2" t="inlineStr">
+      <c r="AE141" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic001346d</t>
         </is>
@@ -12809,10 +13037,11 @@
       <c r="Z142" s="2" t="inlineStr"/>
       <c r="AA142" s="2" t="inlineStr"/>
       <c r="AB142" s="2" t="inlineStr"/>
-      <c r="AC142" s="3" t="n">
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="3" t="n">
         <v>2.56</v>
       </c>
-      <c r="AD142" s="2" t="inlineStr">
+      <c r="AE142" s="2" t="inlineStr">
         <is>
           <t>10.1021/cg800054x</t>
         </is>
@@ -12885,7 +13114,7 @@
         <v>3.06</v>
       </c>
       <c r="V143" s="3" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="W143" s="3" t="n">
         <v>2.85</v>
@@ -12895,10 +13124,11 @@
       <c r="Z143" s="2" t="inlineStr"/>
       <c r="AA143" s="2" t="inlineStr"/>
       <c r="AB143" s="2" t="inlineStr"/>
-      <c r="AC143" s="3" t="n">
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="AD143" s="2" t="inlineStr">
+      <c r="AE143" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.jpcc.6b02175</t>
         </is>
@@ -12981,10 +13211,11 @@
       <c r="Z144" s="2" t="inlineStr"/>
       <c r="AA144" s="2" t="inlineStr"/>
       <c r="AB144" s="2" t="inlineStr"/>
-      <c r="AC144" s="3" t="n">
+      <c r="AC144" s="2" t="inlineStr"/>
+      <c r="AD144" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="AD144" s="2" t="inlineStr">
+      <c r="AE144" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.jpcc.6b02175</t>
         </is>
@@ -13018,7 +13249,7 @@
         <v>1.97</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="J145" s="3" t="n">
         <v>1.89</v>
@@ -13060,17 +13291,18 @@
         <v>3.53</v>
       </c>
       <c r="W145" s="3" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="X145" s="2" t="inlineStr"/>
       <c r="Y145" s="2" t="inlineStr"/>
       <c r="Z145" s="2" t="inlineStr"/>
       <c r="AA145" s="2" t="inlineStr"/>
       <c r="AB145" s="2" t="inlineStr"/>
-      <c r="AC145" s="3" t="n">
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD145" s="2" t="inlineStr">
+      <c r="AE145" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -13143,7 +13375,7 @@
         <v>2.23</v>
       </c>
       <c r="V146" s="3" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="W146" s="3" t="n">
         <v>2.9</v>
@@ -13153,10 +13385,11 @@
       <c r="Z146" s="2" t="inlineStr"/>
       <c r="AA146" s="2" t="inlineStr"/>
       <c r="AB146" s="2" t="inlineStr"/>
-      <c r="AC146" s="3" t="n">
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AD146" s="2" t="inlineStr">
+      <c r="AE146" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -13231,10 +13464,11 @@
       <c r="Z147" s="2" t="inlineStr"/>
       <c r="AA147" s="2" t="inlineStr"/>
       <c r="AB147" s="2" t="inlineStr"/>
-      <c r="AC147" s="3" t="n">
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="3" t="n">
         <v>2.44</v>
       </c>
-      <c r="AD147" s="2" t="inlineStr">
+      <c r="AE147" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic001346d</t>
         </is>
@@ -13309,10 +13543,11 @@
       <c r="Z148" s="2" t="inlineStr"/>
       <c r="AA148" s="2" t="inlineStr"/>
       <c r="AB148" s="2" t="inlineStr"/>
-      <c r="AC148" s="3" t="n">
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AD148" s="2" t="inlineStr">
+      <c r="AE148" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -13387,10 +13622,11 @@
       <c r="Z149" s="2" t="inlineStr"/>
       <c r="AA149" s="2" t="inlineStr"/>
       <c r="AB149" s="2" t="inlineStr"/>
-      <c r="AC149" s="3" t="n">
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD149" s="2" t="inlineStr">
+      <c r="AE149" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -13465,10 +13701,10 @@
         <v>1.44</v>
       </c>
       <c r="V150" s="3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W150" s="3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X150" s="3" t="n">
         <v>1.59</v>
@@ -13479,12 +13715,15 @@
       <c r="Z150" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AA150" s="2" t="inlineStr"/>
+      <c r="AA150" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="AB150" s="2" t="inlineStr"/>
-      <c r="AC150" s="3" t="n">
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="AD150" s="2" t="inlineStr">
+      <c r="AE150" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -13559,10 +13798,11 @@
       <c r="Z151" s="2" t="inlineStr"/>
       <c r="AA151" s="2" t="inlineStr"/>
       <c r="AB151" s="2" t="inlineStr"/>
-      <c r="AC151" s="3" t="n">
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD151" s="2" t="inlineStr">
+      <c r="AE151" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -13637,10 +13877,11 @@
       <c r="Z152" s="2" t="inlineStr"/>
       <c r="AA152" s="2" t="inlineStr"/>
       <c r="AB152" s="2" t="inlineStr"/>
-      <c r="AC152" s="3" t="n">
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="3" t="n">
         <v>1.89</v>
       </c>
-      <c r="AD152" s="2" t="inlineStr">
+      <c r="AE152" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -13715,7 +13956,7 @@
         <v>1.55</v>
       </c>
       <c r="V153" s="3" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="W153" s="3" t="n">
         <v>2.47</v>
@@ -13729,10 +13970,11 @@
       <c r="Z153" s="2" t="inlineStr"/>
       <c r="AA153" s="2" t="inlineStr"/>
       <c r="AB153" s="2" t="inlineStr"/>
-      <c r="AC153" s="3" t="n">
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AD153" s="2" t="inlineStr">
+      <c r="AE153" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -13807,10 +14049,11 @@
       <c r="Z154" s="2" t="inlineStr"/>
       <c r="AA154" s="2" t="inlineStr"/>
       <c r="AB154" s="2" t="inlineStr"/>
-      <c r="AC154" s="3" t="n">
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="3" t="n">
         <v>2.46</v>
       </c>
-      <c r="AD154" s="2" t="inlineStr">
+      <c r="AE154" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic020733f</t>
         </is>
@@ -13885,10 +14128,11 @@
       <c r="Z155" s="2" t="inlineStr"/>
       <c r="AA155" s="2" t="inlineStr"/>
       <c r="AB155" s="2" t="inlineStr"/>
-      <c r="AC155" s="3" t="n">
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="3" t="n">
         <v>2.32</v>
       </c>
-      <c r="AD155" s="2" t="inlineStr">
+      <c r="AE155" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.jpclett.5b00968</t>
         </is>
@@ -13963,10 +14207,10 @@
         <v>1.39</v>
       </c>
       <c r="V156" s="3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="W156" s="3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X156" s="3" t="n">
         <v>1.01</v>
@@ -13977,12 +14221,15 @@
       <c r="Z156" s="3" t="n">
         <v>1.36</v>
       </c>
-      <c r="AA156" s="2" t="inlineStr"/>
+      <c r="AA156" s="3" t="n">
+        <v>1.16</v>
+      </c>
       <c r="AB156" s="2" t="inlineStr"/>
-      <c r="AC156" s="3" t="n">
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD156" s="2" t="inlineStr">
+      <c r="AE156" s="2" t="inlineStr">
         <is>
           <t>10.1039/c5ra22317b</t>
         </is>
@@ -14057,10 +14304,11 @@
       <c r="Z157" s="2" t="inlineStr"/>
       <c r="AA157" s="2" t="inlineStr"/>
       <c r="AB157" s="2" t="inlineStr"/>
-      <c r="AC157" s="3" t="n">
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="AD157" s="2" t="inlineStr">
+      <c r="AE157" s="2" t="inlineStr">
         <is>
           <t>10.1039/c5ra22317b</t>
         </is>
@@ -14135,10 +14383,11 @@
       <c r="Z158" s="2" t="inlineStr"/>
       <c r="AA158" s="2" t="inlineStr"/>
       <c r="AB158" s="2" t="inlineStr"/>
-      <c r="AC158" s="3" t="n">
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="AD158" s="2" t="inlineStr">
+      <c r="AE158" s="2" t="inlineStr">
         <is>
           <t>10.1039/c5ra22317b</t>
         </is>
@@ -14172,7 +14421,7 @@
         <v>2.22</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="J159" s="3" t="n">
         <v>2.11</v>
@@ -14221,10 +14470,11 @@
       <c r="Z159" s="2" t="inlineStr"/>
       <c r="AA159" s="2" t="inlineStr"/>
       <c r="AB159" s="2" t="inlineStr"/>
-      <c r="AC159" s="3" t="n">
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="AD159" s="2" t="inlineStr">
+      <c r="AE159" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic020733f</t>
         </is>
@@ -14305,10 +14555,11 @@
       <c r="Z160" s="2" t="inlineStr"/>
       <c r="AA160" s="2" t="inlineStr"/>
       <c r="AB160" s="2" t="inlineStr"/>
-      <c r="AC160" s="3" t="n">
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="3" t="n">
         <v>2.54</v>
       </c>
-      <c r="AD160" s="2" t="inlineStr">
+      <c r="AE160" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic020733f</t>
         </is>
@@ -14389,10 +14640,11 @@
       <c r="Z161" s="2" t="inlineStr"/>
       <c r="AA161" s="2" t="inlineStr"/>
       <c r="AB161" s="2" t="inlineStr"/>
-      <c r="AC161" s="3" t="n">
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="3" t="n">
         <v>2.29</v>
       </c>
-      <c r="AD161" s="2" t="inlineStr">
+      <c r="AE161" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic011200u</t>
         </is>
@@ -14467,10 +14719,11 @@
       <c r="Z162" s="2" t="inlineStr"/>
       <c r="AA162" s="2" t="inlineStr"/>
       <c r="AB162" s="2" t="inlineStr"/>
-      <c r="AC162" s="3" t="n">
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="3" t="n">
         <v>2.05</v>
       </c>
-      <c r="AD162" s="2" t="inlineStr">
+      <c r="AE162" s="2" t="inlineStr">
         <is>
           <t>10.1016/S0925-8388(01)01987-9</t>
         </is>
@@ -14553,10 +14806,11 @@
       <c r="Z163" s="2" t="inlineStr"/>
       <c r="AA163" s="2" t="inlineStr"/>
       <c r="AB163" s="2" t="inlineStr"/>
-      <c r="AC163" s="3" t="n">
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD163" s="2" t="inlineStr">
+      <c r="AE163" s="2" t="inlineStr">
         <is>
           <t>10.1016/S0022-0248(99)00468-6</t>
         </is>
@@ -14639,10 +14893,11 @@
       <c r="Z164" s="2" t="inlineStr"/>
       <c r="AA164" s="2" t="inlineStr"/>
       <c r="AB164" s="2" t="inlineStr"/>
-      <c r="AC164" s="3" t="n">
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="3" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD164" s="2" t="inlineStr">
+      <c r="AE164" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssc.201600199</t>
         </is>
@@ -14727,10 +14982,11 @@
       <c r="Z165" s="2" t="inlineStr"/>
       <c r="AA165" s="2" t="inlineStr"/>
       <c r="AB165" s="2" t="inlineStr"/>
-      <c r="AC165" s="3" t="n">
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="AD165" s="2" t="inlineStr">
+      <c r="AE165" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssb.201700332</t>
         </is>
@@ -14804,17 +15060,18 @@
       </c>
       <c r="V166" s="2" t="inlineStr"/>
       <c r="W166" s="3" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="X166" s="2" t="inlineStr"/>
       <c r="Y166" s="2" t="inlineStr"/>
       <c r="Z166" s="2" t="inlineStr"/>
       <c r="AA166" s="2" t="inlineStr"/>
       <c r="AB166" s="2" t="inlineStr"/>
-      <c r="AC166" s="3" t="n">
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="AD166" s="2" t="inlineStr">
+      <c r="AE166" s="2" t="inlineStr">
         <is>
           <t>10.7567/JJAP.53.05FW06</t>
         </is>
@@ -14889,7 +15146,7 @@
         <v>3.51</v>
       </c>
       <c r="V167" s="3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W167" s="3" t="n">
         <v>1.47</v>
@@ -14903,12 +15160,15 @@
       <c r="Z167" s="3" t="n">
         <v>2.44</v>
       </c>
-      <c r="AA167" s="2" t="inlineStr"/>
+      <c r="AA167" s="3" t="n">
+        <v>2.07</v>
+      </c>
       <c r="AB167" s="2" t="inlineStr"/>
-      <c r="AC167" s="3" t="n">
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="AD167" s="2" t="inlineStr">
+      <c r="AE167" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -14987,10 +15247,11 @@
       <c r="Z168" s="2" t="inlineStr"/>
       <c r="AA168" s="2" t="inlineStr"/>
       <c r="AB168" s="2" t="inlineStr"/>
-      <c r="AC168" s="3" t="n">
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="AD168" s="2" t="inlineStr">
+      <c r="AE168" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.96.054108</t>
         </is>
@@ -15068,7 +15329,7 @@
         <v>0</v>
       </c>
       <c r="W169" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="X169" s="3" t="n">
         <v>0</v>
@@ -15081,10 +15342,11 @@
       </c>
       <c r="AA169" s="2" t="inlineStr"/>
       <c r="AB169" s="2" t="inlineStr"/>
-      <c r="AC169" s="3" t="n">
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD169" s="2" t="inlineStr">
+      <c r="AE169" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -15173,12 +15435,15 @@
       <c r="Z170" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA170" s="2" t="inlineStr"/>
+      <c r="AA170" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB170" s="2" t="inlineStr"/>
-      <c r="AC170" s="3" t="n">
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD170" s="2" t="inlineStr">
+      <c r="AE170" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -15202,7 +15467,7 @@
         <v>0.12</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="3" t="n">
@@ -15212,7 +15477,7 @@
         <v>0.14</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J171" s="3" t="n">
         <v>0.13</v>
@@ -15257,10 +15522,11 @@
       <c r="Z171" s="2" t="inlineStr"/>
       <c r="AA171" s="2" t="inlineStr"/>
       <c r="AB171" s="2" t="inlineStr"/>
-      <c r="AC171" s="3" t="n">
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="AD171" s="2" t="inlineStr">
+      <c r="AE171" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssc.201600199</t>
         </is>
@@ -15343,10 +15609,11 @@
       <c r="Z172" s="2" t="inlineStr"/>
       <c r="AA172" s="2" t="inlineStr"/>
       <c r="AB172" s="2" t="inlineStr"/>
-      <c r="AC172" s="3" t="n">
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="AD172" s="2" t="inlineStr">
+      <c r="AE172" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.1383984</t>
         </is>
@@ -15431,10 +15698,11 @@
       <c r="Z173" s="2" t="inlineStr"/>
       <c r="AA173" s="2" t="inlineStr"/>
       <c r="AB173" s="2" t="inlineStr"/>
-      <c r="AC173" s="3" t="n">
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="AD173" s="2" t="inlineStr">
+      <c r="AE173" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.tsf.2011.04.027</t>
         </is>
@@ -15517,10 +15785,11 @@
       <c r="Z174" s="2" t="inlineStr"/>
       <c r="AA174" s="2" t="inlineStr"/>
       <c r="AB174" s="2" t="inlineStr"/>
-      <c r="AC174" s="3" t="n">
+      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AD174" s="3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD174" s="2" t="inlineStr">
+      <c r="AE174" s="2" t="inlineStr">
         <is>
           <t>10.1016/0025-5408(77)90150-7</t>
         </is>
@@ -15595,10 +15864,11 @@
       <c r="Z175" s="2" t="inlineStr"/>
       <c r="AA175" s="2" t="inlineStr"/>
       <c r="AB175" s="2" t="inlineStr"/>
-      <c r="AC175" s="3" t="n">
+      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AD175" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="AD175" s="2" t="inlineStr">
+      <c r="AE175" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.3490219</t>
         </is>
@@ -15681,10 +15951,11 @@
       <c r="Z176" s="2" t="inlineStr"/>
       <c r="AA176" s="2" t="inlineStr"/>
       <c r="AB176" s="2" t="inlineStr"/>
-      <c r="AC176" s="3" t="n">
+      <c r="AC176" s="2" t="inlineStr"/>
+      <c r="AD176" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="AD176" s="2" t="inlineStr">
+      <c r="AE176" s="2" t="inlineStr">
         <is>
           <t>10.1016/S1001-0521(07)60096-5</t>
         </is>
@@ -15759,10 +16030,11 @@
       <c r="Z177" s="2" t="inlineStr"/>
       <c r="AA177" s="2" t="inlineStr"/>
       <c r="AB177" s="2" t="inlineStr"/>
-      <c r="AC177" s="3" t="n">
+      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AD177" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD177" s="2" t="inlineStr">
+      <c r="AE177" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -15835,20 +16107,21 @@
         <v>0.64</v>
       </c>
       <c r="V178" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="W178" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="X178" s="2" t="inlineStr"/>
       <c r="Y178" s="2" t="inlineStr"/>
       <c r="Z178" s="2" t="inlineStr"/>
       <c r="AA178" s="2" t="inlineStr"/>
       <c r="AB178" s="2" t="inlineStr"/>
-      <c r="AC178" s="3" t="n">
+      <c r="AC178" s="2" t="inlineStr"/>
+      <c r="AD178" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="AD178" s="2" t="inlineStr">
+      <c r="AE178" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -15923,10 +16196,11 @@
       <c r="Z179" s="2" t="inlineStr"/>
       <c r="AA179" s="2" t="inlineStr"/>
       <c r="AB179" s="2" t="inlineStr"/>
-      <c r="AC179" s="3" t="n">
+      <c r="AC179" s="2" t="inlineStr"/>
+      <c r="AD179" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="AD179" s="2" t="inlineStr">
+      <c r="AE179" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -16001,10 +16275,11 @@
       <c r="Z180" s="2" t="inlineStr"/>
       <c r="AA180" s="2" t="inlineStr"/>
       <c r="AB180" s="2" t="inlineStr"/>
-      <c r="AC180" s="3" t="n">
+      <c r="AC180" s="2" t="inlineStr"/>
+      <c r="AD180" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD180" s="2" t="inlineStr">
+      <c r="AE180" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.3656760</t>
         </is>
@@ -16087,10 +16362,11 @@
       <c r="Z181" s="2" t="inlineStr"/>
       <c r="AA181" s="2" t="inlineStr"/>
       <c r="AB181" s="2" t="inlineStr"/>
-      <c r="AC181" s="3" t="n">
+      <c r="AC181" s="2" t="inlineStr"/>
+      <c r="AD181" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="AD181" s="2" t="inlineStr">
+      <c r="AE181" s="2" t="inlineStr">
         <is>
           <t>10.1002/aenm.201200538</t>
         </is>
@@ -16173,10 +16449,11 @@
       <c r="Z182" s="2" t="inlineStr"/>
       <c r="AA182" s="2" t="inlineStr"/>
       <c r="AB182" s="2" t="inlineStr"/>
-      <c r="AC182" s="3" t="n">
+      <c r="AC182" s="2" t="inlineStr"/>
+      <c r="AD182" s="3" t="n">
         <v>0.29</v>
       </c>
-      <c r="AD182" s="2" t="inlineStr">
+      <c r="AE182" s="2" t="inlineStr">
         <is>
           <t>10.1039/C4TA01957A</t>
         </is>
@@ -16261,12 +16538,15 @@
       <c r="Z183" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="AA183" s="2" t="inlineStr"/>
+      <c r="AA183" s="3" t="n">
+        <v>3.93</v>
+      </c>
       <c r="AB183" s="2" t="inlineStr"/>
-      <c r="AC183" s="3" t="n">
+      <c r="AC183" s="2" t="inlineStr"/>
+      <c r="AD183" s="3" t="n">
         <v>2.99</v>
       </c>
-      <c r="AD183" s="2" t="inlineStr">
+      <c r="AE183" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.2200398</t>
         </is>
@@ -16345,10 +16625,11 @@
       <c r="Z184" s="2" t="inlineStr"/>
       <c r="AA184" s="2" t="inlineStr"/>
       <c r="AB184" s="2" t="inlineStr"/>
-      <c r="AC184" s="3" t="n">
+      <c r="AC184" s="2" t="inlineStr"/>
+      <c r="AD184" s="3" t="n">
         <v>3.45</v>
       </c>
-      <c r="AD184" s="2" t="inlineStr">
+      <c r="AE184" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.optcom.2007.11.031</t>
         </is>
@@ -16421,7 +16702,7 @@
         <v>2.65</v>
       </c>
       <c r="V185" s="3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="W185" s="3" t="n">
         <v>1.9</v>
@@ -16431,10 +16712,11 @@
       <c r="Z185" s="2" t="inlineStr"/>
       <c r="AA185" s="2" t="inlineStr"/>
       <c r="AB185" s="2" t="inlineStr"/>
-      <c r="AC185" s="3" t="n">
+      <c r="AC185" s="2" t="inlineStr"/>
+      <c r="AD185" s="3" t="n">
         <v>2.68</v>
       </c>
-      <c r="AD185" s="2" t="inlineStr">
+      <c r="AE185" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -16509,10 +16791,11 @@
       <c r="Z186" s="2" t="inlineStr"/>
       <c r="AA186" s="2" t="inlineStr"/>
       <c r="AB186" s="2" t="inlineStr"/>
-      <c r="AC186" s="3" t="n">
+      <c r="AC186" s="2" t="inlineStr"/>
+      <c r="AD186" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD186" s="2" t="inlineStr">
+      <c r="AE186" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic050357%2B</t>
         </is>
@@ -16602,15 +16885,18 @@
         <v>3.26</v>
       </c>
       <c r="AA187" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AB187" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="AB187" s="3" t="n">
+      <c r="AC187" s="3" t="n">
         <v>2.56</v>
       </c>
-      <c r="AC187" s="3" t="n">
+      <c r="AD187" s="3" t="n">
         <v>3.07</v>
       </c>
-      <c r="AD187" s="2" t="inlineStr">
+      <c r="AE187" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -16683,20 +16969,21 @@
         <v>3.16</v>
       </c>
       <c r="V188" s="3" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="W188" s="3" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="X188" s="2" t="inlineStr"/>
       <c r="Y188" s="2" t="inlineStr"/>
       <c r="Z188" s="2" t="inlineStr"/>
       <c r="AA188" s="2" t="inlineStr"/>
       <c r="AB188" s="2" t="inlineStr"/>
-      <c r="AC188" s="3" t="n">
+      <c r="AC188" s="2" t="inlineStr"/>
+      <c r="AD188" s="3" t="n">
         <v>3.61</v>
       </c>
-      <c r="AD188" s="2" t="inlineStr">
+      <c r="AE188" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.matlet.2006.09.018</t>
         </is>
@@ -16786,15 +17073,18 @@
         <v>3.64</v>
       </c>
       <c r="AA189" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB189" s="3" t="n">
         <v>2.84</v>
       </c>
-      <c r="AB189" s="3" t="n">
+      <c r="AC189" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="AC189" s="3" t="n">
+      <c r="AD189" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="AD189" s="2" t="inlineStr">
+      <c r="AE189" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -16879,12 +17169,15 @@
       <c r="Z190" s="3" t="n">
         <v>3.29</v>
       </c>
-      <c r="AA190" s="2" t="inlineStr"/>
+      <c r="AA190" s="3" t="n">
+        <v>2.84</v>
+      </c>
       <c r="AB190" s="2" t="inlineStr"/>
-      <c r="AC190" s="3" t="n">
+      <c r="AC190" s="2" t="inlineStr"/>
+      <c r="AD190" s="3" t="n">
         <v>2.55</v>
       </c>
-      <c r="AD190" s="2" t="inlineStr">
+      <c r="AE190" s="2" t="inlineStr">
         <is>
           <t>10.1021/jp2087225</t>
         </is>
@@ -16963,10 +17256,11 @@
       <c r="Z191" s="2" t="inlineStr"/>
       <c r="AA191" s="2" t="inlineStr"/>
       <c r="AB191" s="2" t="inlineStr"/>
-      <c r="AC191" s="3" t="n">
+      <c r="AC191" s="2" t="inlineStr"/>
+      <c r="AD191" s="3" t="n">
         <v>2.51</v>
       </c>
-      <c r="AD191" s="2" t="inlineStr">
+      <c r="AE191" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -17047,10 +17341,11 @@
       <c r="Z192" s="2" t="inlineStr"/>
       <c r="AA192" s="2" t="inlineStr"/>
       <c r="AB192" s="2" t="inlineStr"/>
-      <c r="AC192" s="3" t="n">
+      <c r="AC192" s="2" t="inlineStr"/>
+      <c r="AD192" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD192" s="2" t="inlineStr">
+      <c r="AE192" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -17129,10 +17424,11 @@
       <c r="Z193" s="2" t="inlineStr"/>
       <c r="AA193" s="2" t="inlineStr"/>
       <c r="AB193" s="2" t="inlineStr"/>
-      <c r="AC193" s="3" t="n">
+      <c r="AC193" s="2" t="inlineStr"/>
+      <c r="AD193" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="AD193" s="2" t="inlineStr">
+      <c r="AE193" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -17207,7 +17503,7 @@
         <v>3.21</v>
       </c>
       <c r="V194" s="3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="W194" s="3" t="n">
         <v>2.27</v>
@@ -17222,15 +17518,18 @@
         <v>3.45</v>
       </c>
       <c r="AA194" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB194" s="3" t="n">
         <v>2.95</v>
       </c>
-      <c r="AB194" s="3" t="n">
+      <c r="AC194" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="AC194" s="3" t="n">
+      <c r="AD194" s="3" t="n">
         <v>3.12</v>
       </c>
-      <c r="AD194" s="2" t="inlineStr">
+      <c r="AE194" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -17311,10 +17610,11 @@
       <c r="Z195" s="2" t="inlineStr"/>
       <c r="AA195" s="2" t="inlineStr"/>
       <c r="AB195" s="2" t="inlineStr"/>
-      <c r="AC195" s="3" t="n">
+      <c r="AC195" s="2" t="inlineStr"/>
+      <c r="AD195" s="3" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD195" s="2" t="inlineStr">
+      <c r="AE195" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -17397,10 +17697,11 @@
       <c r="Z196" s="2" t="inlineStr"/>
       <c r="AA196" s="2" t="inlineStr"/>
       <c r="AB196" s="2" t="inlineStr"/>
-      <c r="AC196" s="3" t="n">
+      <c r="AC196" s="2" t="inlineStr"/>
+      <c r="AD196" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="AD196" s="2" t="inlineStr">
+      <c r="AE196" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -17479,10 +17780,11 @@
       <c r="Z197" s="2" t="inlineStr"/>
       <c r="AA197" s="2" t="inlineStr"/>
       <c r="AB197" s="2" t="inlineStr"/>
-      <c r="AC197" s="3" t="n">
+      <c r="AC197" s="2" t="inlineStr"/>
+      <c r="AD197" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="AD197" s="2" t="inlineStr">
+      <c r="AE197" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.matchemphys.2014.05.012</t>
         </is>
@@ -17563,12 +17865,15 @@
       <c r="Z198" s="3" t="n">
         <v>5.09</v>
       </c>
-      <c r="AA198" s="2" t="inlineStr"/>
+      <c r="AA198" s="3" t="n">
+        <v>4.62</v>
+      </c>
       <c r="AB198" s="2" t="inlineStr"/>
-      <c r="AC198" s="3" t="n">
+      <c r="AC198" s="2" t="inlineStr"/>
+      <c r="AD198" s="3" t="n">
         <v>2.34</v>
       </c>
-      <c r="AD198" s="2" t="inlineStr">
+      <c r="AE198" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.ijhydene.2005.08.015</t>
         </is>
@@ -17643,10 +17948,11 @@
       <c r="Z199" s="2" t="inlineStr"/>
       <c r="AA199" s="2" t="inlineStr"/>
       <c r="AB199" s="2" t="inlineStr"/>
-      <c r="AC199" s="3" t="n">
+      <c r="AC199" s="2" t="inlineStr"/>
+      <c r="AD199" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="AD199" s="2" t="inlineStr">
+      <c r="AE199" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -17736,15 +18042,18 @@
         <v>4.87</v>
       </c>
       <c r="AA200" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB200" s="3" t="n">
         <v>3.92</v>
       </c>
-      <c r="AB200" s="3" t="n">
+      <c r="AC200" s="3" t="n">
         <v>3.61</v>
       </c>
-      <c r="AC200" s="3" t="n">
+      <c r="AD200" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="AD200" s="2" t="inlineStr">
+      <c r="AE200" s="2" t="inlineStr">
         <is>
           <t>10.1016/S1466-6049(01)00006-X</t>
         </is>
@@ -17834,15 +18143,18 @@
         <v>2.04</v>
       </c>
       <c r="AA201" s="3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB201" s="3" t="n">
         <v>1.87</v>
       </c>
-      <c r="AB201" s="3" t="n">
+      <c r="AC201" s="3" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC201" s="3" t="n">
+      <c r="AD201" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD201" s="2" t="inlineStr">
+      <c r="AE201" s="2" t="inlineStr">
         <is>
           <t>10.1039/C3EE40621K</t>
         </is>
@@ -17866,7 +18178,7 @@
         <v>0.31</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="F202" s="3" t="n">
         <v>0.31</v>
@@ -17917,7 +18229,7 @@
         <v>1.12</v>
       </c>
       <c r="V202" s="3" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="W202" s="3" t="n">
         <v>0.41</v>
@@ -17933,10 +18245,11 @@
       </c>
       <c r="AA202" s="2" t="inlineStr"/>
       <c r="AB202" s="2" t="inlineStr"/>
-      <c r="AC202" s="3" t="n">
+      <c r="AC202" s="2" t="inlineStr"/>
+      <c r="AD202" s="3" t="n">
         <v>0.37</v>
       </c>
-      <c r="AD202" s="2" t="inlineStr">
+      <c r="AE202" s="2" t="inlineStr">
         <is>
           <t>10.1088/0031-8949/4/3/010</t>
         </is>
@@ -18019,10 +18332,11 @@
       <c r="Z203" s="2" t="inlineStr"/>
       <c r="AA203" s="2" t="inlineStr"/>
       <c r="AB203" s="2" t="inlineStr"/>
-      <c r="AC203" s="3" t="n">
+      <c r="AC203" s="2" t="inlineStr"/>
+      <c r="AD203" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="AD203" s="2" t="inlineStr">
+      <c r="AE203" s="2" t="inlineStr">
         <is>
           <t>10.1016/S0927-0248(01)00053-8</t>
         </is>
@@ -18096,17 +18410,18 @@
       </c>
       <c r="V204" s="2" t="inlineStr"/>
       <c r="W204" s="3" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="X204" s="2" t="inlineStr"/>
       <c r="Y204" s="2" t="inlineStr"/>
       <c r="Z204" s="2" t="inlineStr"/>
       <c r="AA204" s="2" t="inlineStr"/>
       <c r="AB204" s="2" t="inlineStr"/>
-      <c r="AC204" s="3" t="n">
+      <c r="AC204" s="2" t="inlineStr"/>
+      <c r="AD204" s="3" t="n">
         <v>3.44</v>
       </c>
-      <c r="AD204" s="2" t="inlineStr">
+      <c r="AE204" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.1609254</t>
         </is>
@@ -18196,15 +18511,18 @@
         <v>1.89</v>
       </c>
       <c r="AA205" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB205" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB205" s="3" t="n">
+      <c r="AC205" s="3" t="n">
         <v>1.59</v>
       </c>
-      <c r="AC205" s="3" t="n">
+      <c r="AD205" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AD205" s="2" t="inlineStr">
+      <c r="AE205" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -18294,15 +18612,18 @@
         <v>3.86</v>
       </c>
       <c r="AA206" s="3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AB206" s="3" t="n">
         <v>3.51</v>
-      </c>
-      <c r="AB206" s="3" t="n">
-        <v>3.5</v>
       </c>
       <c r="AC206" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AD206" s="2" t="inlineStr">
+      <c r="AD206" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE206" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -18326,7 +18647,7 @@
         <v>1.49</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="F207" s="3" t="n">
         <v>1.45</v>
@@ -18377,10 +18698,10 @@
         <v>2.74</v>
       </c>
       <c r="V207" s="3" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="W207" s="3" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="X207" s="3" t="n">
         <v>2.29</v>
@@ -18392,15 +18713,18 @@
         <v>2.48</v>
       </c>
       <c r="AA207" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB207" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="AB207" s="3" t="n">
+      <c r="AC207" s="3" t="n">
         <v>2.24</v>
       </c>
-      <c r="AC207" s="3" t="n">
+      <c r="AD207" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="AD207" s="2" t="inlineStr">
+      <c r="AE207" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -18483,10 +18807,11 @@
       <c r="Z208" s="2" t="inlineStr"/>
       <c r="AA208" s="2" t="inlineStr"/>
       <c r="AB208" s="2" t="inlineStr"/>
-      <c r="AC208" s="3" t="n">
+      <c r="AC208" s="2" t="inlineStr"/>
+      <c r="AD208" s="3" t="n">
         <v>2.54</v>
       </c>
-      <c r="AD208" s="2" t="inlineStr">
+      <c r="AE208" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.2358192</t>
         </is>
@@ -18575,12 +18900,15 @@
       <c r="Z209" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AA209" s="2" t="inlineStr"/>
+      <c r="AA209" s="3" t="n">
+        <v>1.06</v>
+      </c>
       <c r="AB209" s="2" t="inlineStr"/>
-      <c r="AC209" s="3" t="n">
+      <c r="AC209" s="2" t="inlineStr"/>
+      <c r="AD209" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="AD209" s="2" t="inlineStr">
+      <c r="AE209" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -18656,17 +18984,18 @@
         <v>1.86</v>
       </c>
       <c r="W210" s="3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X210" s="2" t="inlineStr"/>
       <c r="Y210" s="2" t="inlineStr"/>
       <c r="Z210" s="2" t="inlineStr"/>
       <c r="AA210" s="2" t="inlineStr"/>
       <c r="AB210" s="2" t="inlineStr"/>
-      <c r="AC210" s="3" t="n">
+      <c r="AC210" s="2" t="inlineStr"/>
+      <c r="AD210" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD210" s="2" t="inlineStr">
+      <c r="AE210" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -18745,10 +19074,11 @@
       <c r="Z211" s="2" t="inlineStr"/>
       <c r="AA211" s="2" t="inlineStr"/>
       <c r="AB211" s="2" t="inlineStr"/>
-      <c r="AC211" s="3" t="n">
+      <c r="AC211" s="2" t="inlineStr"/>
+      <c r="AD211" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD211" s="2" t="inlineStr">
+      <c r="AE211" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -18837,12 +19167,15 @@
       <c r="Z212" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="AA212" s="2" t="inlineStr"/>
+      <c r="AA212" s="3" t="n">
+        <v>0.83</v>
+      </c>
       <c r="AB212" s="2" t="inlineStr"/>
-      <c r="AC212" s="3" t="n">
+      <c r="AC212" s="2" t="inlineStr"/>
+      <c r="AD212" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="AD212" s="2" t="inlineStr">
+      <c r="AE212" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -18866,7 +19199,7 @@
         <v>0.39</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="3" t="n">
@@ -18876,7 +19209,7 @@
         <v>0.49</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="J213" s="3" t="n">
         <v>0.48</v>
@@ -18923,10 +19256,11 @@
       <c r="Z213" s="2" t="inlineStr"/>
       <c r="AA213" s="2" t="inlineStr"/>
       <c r="AB213" s="2" t="inlineStr"/>
-      <c r="AC213" s="3" t="n">
+      <c r="AC213" s="2" t="inlineStr"/>
+      <c r="AD213" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="AD213" s="2" t="inlineStr">
+      <c r="AE213" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.3.2581</t>
         </is>
@@ -19001,10 +19335,11 @@
       <c r="Z214" s="2" t="inlineStr"/>
       <c r="AA214" s="2" t="inlineStr"/>
       <c r="AB214" s="2" t="inlineStr"/>
-      <c r="AC214" s="3" t="n">
+      <c r="AC214" s="2" t="inlineStr"/>
+      <c r="AD214" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="AD214" s="2" t="inlineStr">
+      <c r="AE214" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.3.2581</t>
         </is>
@@ -19093,12 +19428,15 @@
       <c r="Z215" s="3" t="n">
         <v>5.44</v>
       </c>
-      <c r="AA215" s="2" t="inlineStr"/>
+      <c r="AA215" s="3" t="n">
+        <v>4.69</v>
+      </c>
       <c r="AB215" s="2" t="inlineStr"/>
-      <c r="AC215" s="3" t="n">
+      <c r="AC215" s="2" t="inlineStr"/>
+      <c r="AD215" s="3" t="n">
         <v>5.35</v>
       </c>
-      <c r="AD215" s="2" t="inlineStr">
+      <c r="AE215" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -19122,7 +19460,7 @@
         <v>0.59</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="F216" s="2" t="inlineStr"/>
       <c r="G216" s="3" t="n">
@@ -19132,7 +19470,7 @@
         <v>0.64</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="J216" s="3" t="n">
         <v>0.62</v>
@@ -19171,20 +19509,21 @@
         <v>1.37</v>
       </c>
       <c r="V216" s="3" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W216" s="3" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="X216" s="2" t="inlineStr"/>
       <c r="Y216" s="2" t="inlineStr"/>
       <c r="Z216" s="2" t="inlineStr"/>
       <c r="AA216" s="2" t="inlineStr"/>
       <c r="AB216" s="2" t="inlineStr"/>
-      <c r="AC216" s="3" t="n">
+      <c r="AC216" s="2" t="inlineStr"/>
+      <c r="AD216" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="AD216" s="2" t="inlineStr">
+      <c r="AE216" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -19259,7 +19598,7 @@
         <v>4.04</v>
       </c>
       <c r="V217" s="3" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="W217" s="3" t="n">
         <v>2.35</v>
@@ -19269,10 +19608,11 @@
       <c r="Z217" s="2" t="inlineStr"/>
       <c r="AA217" s="2" t="inlineStr"/>
       <c r="AB217" s="2" t="inlineStr"/>
-      <c r="AC217" s="3" t="n">
+      <c r="AC217" s="2" t="inlineStr"/>
+      <c r="AD217" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="AD217" s="2" t="inlineStr">
+      <c r="AE217" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic401548a</t>
         </is>
@@ -19296,7 +19636,7 @@
         <v>3.86</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="3" t="n">
@@ -19345,7 +19685,7 @@
         <v>7.48</v>
       </c>
       <c r="V218" s="3" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="W218" s="3" t="n">
         <v>4.96</v>
@@ -19355,10 +19695,11 @@
       <c r="Z218" s="2" t="inlineStr"/>
       <c r="AA218" s="2" t="inlineStr"/>
       <c r="AB218" s="2" t="inlineStr"/>
-      <c r="AC218" s="3" t="n">
+      <c r="AC218" s="2" t="inlineStr"/>
+      <c r="AD218" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AD218" s="2" t="inlineStr">
+      <c r="AE218" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.tsf.2004.01.110</t>
         </is>
@@ -19433,7 +19774,7 @@
         <v>2.07</v>
       </c>
       <c r="V219" s="3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="W219" s="3" t="n">
         <v>1.44</v>
@@ -19451,12 +19792,15 @@
         <v>1.78</v>
       </c>
       <c r="AB219" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC219" s="3" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC219" s="3" t="n">
+      <c r="AD219" s="3" t="n">
         <v>1.96</v>
       </c>
-      <c r="AD219" s="2" t="inlineStr">
+      <c r="AE219" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(65)90043-0</t>
         </is>
@@ -19545,12 +19889,15 @@
       <c r="Z220" s="3" t="n">
         <v>1.37</v>
       </c>
-      <c r="AA220" s="2" t="inlineStr"/>
+      <c r="AA220" s="3" t="n">
+        <v>1.17</v>
+      </c>
       <c r="AB220" s="2" t="inlineStr"/>
-      <c r="AC220" s="3" t="n">
+      <c r="AC220" s="2" t="inlineStr"/>
+      <c r="AD220" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="AD220" s="2" t="inlineStr">
+      <c r="AE220" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(65)90043-0</t>
         </is>
@@ -19635,10 +19982,11 @@
       <c r="Z221" s="2" t="inlineStr"/>
       <c r="AA221" s="2" t="inlineStr"/>
       <c r="AB221" s="2" t="inlineStr"/>
-      <c r="AC221" s="3" t="n">
+      <c r="AC221" s="2" t="inlineStr"/>
+      <c r="AD221" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AD221" s="2" t="inlineStr">
+      <c r="AE221" s="2" t="inlineStr">
         <is>
           <t>10.1201/9781420050196</t>
         </is>
@@ -19713,10 +20061,11 @@
       <c r="Z222" s="2" t="inlineStr"/>
       <c r="AA222" s="2" t="inlineStr"/>
       <c r="AB222" s="2" t="inlineStr"/>
-      <c r="AC222" s="3" t="n">
+      <c r="AC222" s="2" t="inlineStr"/>
+      <c r="AD222" s="3" t="n">
         <v>1.45</v>
       </c>
-      <c r="AD222" s="2" t="inlineStr">
+      <c r="AE222" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2006.11.018</t>
         </is>
@@ -19799,10 +20148,11 @@
       <c r="Z223" s="2" t="inlineStr"/>
       <c r="AA223" s="2" t="inlineStr"/>
       <c r="AB223" s="2" t="inlineStr"/>
-      <c r="AC223" s="3" t="n">
+      <c r="AC223" s="2" t="inlineStr"/>
+      <c r="AD223" s="3" t="n">
         <v>2.79</v>
       </c>
-      <c r="AD223" s="2" t="inlineStr">
+      <c r="AE223" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -19878,17 +20228,18 @@
         <v>1.97</v>
       </c>
       <c r="W224" s="3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X224" s="2" t="inlineStr"/>
       <c r="Y224" s="2" t="inlineStr"/>
       <c r="Z224" s="2" t="inlineStr"/>
       <c r="AA224" s="2" t="inlineStr"/>
       <c r="AB224" s="2" t="inlineStr"/>
-      <c r="AC224" s="3" t="n">
+      <c r="AC224" s="2" t="inlineStr"/>
+      <c r="AD224" s="3" t="n">
         <v>1.99</v>
       </c>
-      <c r="AD224" s="2" t="inlineStr">
+      <c r="AE224" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -19966,7 +20317,7 @@
         <v>2.22</v>
       </c>
       <c r="W225" s="3" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="X225" s="3" t="n">
         <v>2.51</v>
@@ -19977,12 +20328,15 @@
       <c r="Z225" s="3" t="n">
         <v>2.98</v>
       </c>
-      <c r="AA225" s="2" t="inlineStr"/>
+      <c r="AA225" s="3" t="n">
+        <v>2.58</v>
+      </c>
       <c r="AB225" s="2" t="inlineStr"/>
-      <c r="AC225" s="3" t="n">
+      <c r="AC225" s="2" t="inlineStr"/>
+      <c r="AD225" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="AD225" s="2" t="inlineStr">
+      <c r="AE225" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -20058,17 +20412,18 @@
         <v>1.39</v>
       </c>
       <c r="W226" s="3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X226" s="2" t="inlineStr"/>
       <c r="Y226" s="2" t="inlineStr"/>
       <c r="Z226" s="2" t="inlineStr"/>
       <c r="AA226" s="2" t="inlineStr"/>
       <c r="AB226" s="2" t="inlineStr"/>
-      <c r="AC226" s="3" t="n">
+      <c r="AC226" s="2" t="inlineStr"/>
+      <c r="AD226" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="AD226" s="2" t="inlineStr">
+      <c r="AE226" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -20151,10 +20506,11 @@
       <c r="Z227" s="2" t="inlineStr"/>
       <c r="AA227" s="2" t="inlineStr"/>
       <c r="AB227" s="2" t="inlineStr"/>
-      <c r="AC227" s="3" t="n">
+      <c r="AC227" s="2" t="inlineStr"/>
+      <c r="AD227" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="AD227" s="2" t="inlineStr">
+      <c r="AE227" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -20178,7 +20534,7 @@
         <v>1.18</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="3" t="n">
@@ -20227,7 +20583,7 @@
         <v>3.58</v>
       </c>
       <c r="V228" s="3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="W228" s="3" t="n">
         <v>2.3</v>
@@ -20237,10 +20593,11 @@
       <c r="Z228" s="2" t="inlineStr"/>
       <c r="AA228" s="2" t="inlineStr"/>
       <c r="AB228" s="2" t="inlineStr"/>
-      <c r="AC228" s="3" t="n">
+      <c r="AC228" s="2" t="inlineStr"/>
+      <c r="AD228" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD228" s="2" t="inlineStr">
+      <c r="AE228" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.71.235109</t>
         </is>
@@ -20329,12 +20686,15 @@
       <c r="Z229" s="3" t="n">
         <v>3.03</v>
       </c>
-      <c r="AA229" s="2" t="inlineStr"/>
+      <c r="AA229" s="3" t="n">
+        <v>2.68</v>
+      </c>
       <c r="AB229" s="2" t="inlineStr"/>
-      <c r="AC229" s="3" t="n">
+      <c r="AC229" s="2" t="inlineStr"/>
+      <c r="AD229" s="3" t="n">
         <v>2.03</v>
       </c>
-      <c r="AD229" s="2" t="inlineStr">
+      <c r="AE229" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -20424,15 +20784,18 @@
         <v>0.36</v>
       </c>
       <c r="AA230" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB230" s="3" t="n">
         <v>0.14</v>
       </c>
-      <c r="AB230" s="3" t="n">
+      <c r="AC230" s="3" t="n">
         <v>0.09</v>
       </c>
-      <c r="AC230" s="3" t="n">
+      <c r="AD230" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="AD230" s="2" t="inlineStr">
+      <c r="AE230" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -20515,10 +20878,11 @@
       <c r="Z231" s="2" t="inlineStr"/>
       <c r="AA231" s="2" t="inlineStr"/>
       <c r="AB231" s="2" t="inlineStr"/>
-      <c r="AC231" s="3" t="n">
+      <c r="AC231" s="2" t="inlineStr"/>
+      <c r="AD231" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="AD231" s="2" t="inlineStr">
+      <c r="AE231" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic800370r</t>
         </is>
@@ -20603,10 +20967,11 @@
       <c r="Z232" s="2" t="inlineStr"/>
       <c r="AA232" s="2" t="inlineStr"/>
       <c r="AB232" s="2" t="inlineStr"/>
-      <c r="AC232" s="3" t="n">
+      <c r="AC232" s="2" t="inlineStr"/>
+      <c r="AD232" s="3" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD232" s="2" t="inlineStr">
+      <c r="AE232" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssa.2211180228</t>
         </is>
@@ -20691,10 +21056,11 @@
       <c r="Z233" s="2" t="inlineStr"/>
       <c r="AA233" s="2" t="inlineStr"/>
       <c r="AB233" s="2" t="inlineStr"/>
-      <c r="AC233" s="3" t="n">
+      <c r="AC233" s="2" t="inlineStr"/>
+      <c r="AD233" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="AD233" s="2" t="inlineStr">
+      <c r="AE233" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssa.2211180228</t>
         </is>
@@ -20769,10 +21135,11 @@
       <c r="Z234" s="2" t="inlineStr"/>
       <c r="AA234" s="2" t="inlineStr"/>
       <c r="AB234" s="2" t="inlineStr"/>
-      <c r="AC234" s="3" t="n">
+      <c r="AC234" s="2" t="inlineStr"/>
+      <c r="AD234" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="AD234" s="2" t="inlineStr">
+      <c r="AE234" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.3698334</t>
         </is>
@@ -20847,10 +21214,11 @@
       <c r="Z235" s="2" t="inlineStr"/>
       <c r="AA235" s="2" t="inlineStr"/>
       <c r="AB235" s="2" t="inlineStr"/>
-      <c r="AC235" s="3" t="n">
+      <c r="AC235" s="2" t="inlineStr"/>
+      <c r="AD235" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD235" s="2" t="inlineStr">
+      <c r="AE235" s="2" t="inlineStr">
         <is>
           <t>10.1142/S0218625X13500583</t>
         </is>
@@ -20940,15 +21308,18 @@
         <v>0.82</v>
       </c>
       <c r="AA236" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB236" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="AB236" s="3" t="n">
+      <c r="AC236" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="AC236" s="3" t="n">
+      <c r="AD236" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="AD236" s="2" t="inlineStr">
+      <c r="AE236" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.363660</t>
         </is>
@@ -21024,17 +21395,18 @@
         <v>2.31</v>
       </c>
       <c r="W237" s="3" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="X237" s="2" t="inlineStr"/>
       <c r="Y237" s="2" t="inlineStr"/>
       <c r="Z237" s="2" t="inlineStr"/>
       <c r="AA237" s="2" t="inlineStr"/>
       <c r="AB237" s="2" t="inlineStr"/>
-      <c r="AC237" s="3" t="n">
+      <c r="AC237" s="2" t="inlineStr"/>
+      <c r="AD237" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD237" s="2" t="inlineStr">
+      <c r="AE237" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm701995d</t>
         </is>
@@ -21109,10 +21481,11 @@
       <c r="Z238" s="2" t="inlineStr"/>
       <c r="AA238" s="2" t="inlineStr"/>
       <c r="AB238" s="2" t="inlineStr"/>
-      <c r="AC238" s="3" t="n">
+      <c r="AC238" s="2" t="inlineStr"/>
+      <c r="AD238" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD238" s="2" t="inlineStr">
+      <c r="AE238" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm701995d</t>
         </is>
@@ -21201,12 +21574,15 @@
       <c r="Z239" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="AA239" s="2" t="inlineStr"/>
+      <c r="AA239" s="3" t="n">
+        <v>0.76</v>
+      </c>
       <c r="AB239" s="2" t="inlineStr"/>
-      <c r="AC239" s="3" t="n">
+      <c r="AC239" s="2" t="inlineStr"/>
+      <c r="AD239" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="AD239" s="2" t="inlineStr">
+      <c r="AE239" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.77.245207</t>
         </is>
@@ -21296,15 +21672,18 @@
         <v>1.72</v>
       </c>
       <c r="AA240" s="3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB240" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="AB240" s="3" t="n">
+      <c r="AC240" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="AC240" s="3" t="n">
+      <c r="AD240" s="3" t="n">
         <v>1.42</v>
       </c>
-      <c r="AD240" s="2" t="inlineStr">
+      <c r="AE240" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -21382,7 +21761,7 @@
         <v>3.52</v>
       </c>
       <c r="W241" s="3" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="X241" s="3" t="n">
         <v>4.03</v>
@@ -21394,15 +21773,18 @@
         <v>4.51</v>
       </c>
       <c r="AA241" s="3" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="AB241" s="3" t="n">
         <v>4.09</v>
       </c>
       <c r="AC241" s="3" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AD241" s="3" t="n">
         <v>3.12</v>
       </c>
-      <c r="AD241" s="2" t="inlineStr">
+      <c r="AE241" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.cgd.7b00214</t>
         </is>
@@ -21485,10 +21867,11 @@
       <c r="Z242" s="2" t="inlineStr"/>
       <c r="AA242" s="2" t="inlineStr"/>
       <c r="AB242" s="2" t="inlineStr"/>
-      <c r="AC242" s="3" t="n">
+      <c r="AC242" s="2" t="inlineStr"/>
+      <c r="AD242" s="3" t="n">
         <v>2.09</v>
       </c>
-      <c r="AD242" s="2" t="inlineStr">
+      <c r="AE242" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.optmat.2013.10.046</t>
         </is>
@@ -21578,15 +21961,18 @@
         <v>0.88</v>
       </c>
       <c r="AA243" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB243" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="AB243" s="3" t="n">
+      <c r="AC243" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="AC243" s="3" t="n">
+      <c r="AD243" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="AD243" s="2" t="inlineStr">
+      <c r="AE243" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -21661,10 +22047,11 @@
       <c r="Z244" s="2" t="inlineStr"/>
       <c r="AA244" s="2" t="inlineStr"/>
       <c r="AB244" s="2" t="inlineStr"/>
-      <c r="AC244" s="3" t="n">
+      <c r="AC244" s="2" t="inlineStr"/>
+      <c r="AD244" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD244" s="2" t="inlineStr">
+      <c r="AE244" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm701995d</t>
         </is>
@@ -21739,10 +22126,11 @@
       <c r="Z245" s="2" t="inlineStr"/>
       <c r="AA245" s="2" t="inlineStr"/>
       <c r="AB245" s="2" t="inlineStr"/>
-      <c r="AC245" s="3" t="n">
+      <c r="AC245" s="2" t="inlineStr"/>
+      <c r="AD245" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD245" s="2" t="inlineStr">
+      <c r="AE245" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm701995d</t>
         </is>
@@ -21817,10 +22205,11 @@
       <c r="Z246" s="2" t="inlineStr"/>
       <c r="AA246" s="2" t="inlineStr"/>
       <c r="AB246" s="2" t="inlineStr"/>
-      <c r="AC246" s="3" t="n">
+      <c r="AC246" s="2" t="inlineStr"/>
+      <c r="AD246" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD246" s="2" t="inlineStr">
+      <c r="AE246" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm701995d</t>
         </is>
@@ -21893,20 +22282,21 @@
         <v>0.27</v>
       </c>
       <c r="V247" s="3" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="W247" s="3" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="X247" s="2" t="inlineStr"/>
       <c r="Y247" s="2" t="inlineStr"/>
       <c r="Z247" s="2" t="inlineStr"/>
       <c r="AA247" s="2" t="inlineStr"/>
       <c r="AB247" s="2" t="inlineStr"/>
-      <c r="AC247" s="3" t="n">
+      <c r="AC247" s="2" t="inlineStr"/>
+      <c r="AD247" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="AD247" s="2" t="inlineStr">
+      <c r="AE247" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -21981,10 +22371,11 @@
       <c r="Z248" s="2" t="inlineStr"/>
       <c r="AA248" s="2" t="inlineStr"/>
       <c r="AB248" s="2" t="inlineStr"/>
-      <c r="AC248" s="3" t="n">
+      <c r="AC248" s="2" t="inlineStr"/>
+      <c r="AD248" s="3" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD248" s="2" t="inlineStr">
+      <c r="AE248" s="2" t="inlineStr">
         <is>
           <t>10.1002/(SICI)1521-3749(199808)624:8&lt;1285::AID-ZAAC1285&gt;3.0.CO;2-5</t>
         </is>
@@ -22059,10 +22450,11 @@
       <c r="Z249" s="2" t="inlineStr"/>
       <c r="AA249" s="2" t="inlineStr"/>
       <c r="AB249" s="2" t="inlineStr"/>
-      <c r="AC249" s="3" t="n">
+      <c r="AC249" s="2" t="inlineStr"/>
+      <c r="AD249" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="AD249" s="2" t="inlineStr">
+      <c r="AE249" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm00034a029</t>
         </is>
@@ -22137,10 +22529,11 @@
       <c r="Z250" s="2" t="inlineStr"/>
       <c r="AA250" s="2" t="inlineStr"/>
       <c r="AB250" s="2" t="inlineStr"/>
-      <c r="AC250" s="3" t="n">
+      <c r="AC250" s="2" t="inlineStr"/>
+      <c r="AD250" s="3" t="n">
         <v>2.63</v>
       </c>
-      <c r="AD250" s="2" t="inlineStr">
+      <c r="AE250" s="2" t="inlineStr">
         <is>
           <t>10.1002/(SICI)1099-0682(199802)1998:2&lt;283::AID-EJIC283&gt;3.0.CO;2-L</t>
         </is>
@@ -22225,10 +22618,11 @@
       <c r="Z251" s="2" t="inlineStr"/>
       <c r="AA251" s="2" t="inlineStr"/>
       <c r="AB251" s="2" t="inlineStr"/>
-      <c r="AC251" s="3" t="n">
+      <c r="AC251" s="2" t="inlineStr"/>
+      <c r="AD251" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AD251" s="2" t="inlineStr">
+      <c r="AE251" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -22303,10 +22697,11 @@
       <c r="Z252" s="2" t="inlineStr"/>
       <c r="AA252" s="2" t="inlineStr"/>
       <c r="AB252" s="2" t="inlineStr"/>
-      <c r="AC252" s="3" t="n">
+      <c r="AC252" s="2" t="inlineStr"/>
+      <c r="AD252" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="AD252" s="2" t="inlineStr">
+      <c r="AE252" s="2" t="inlineStr">
         <is>
           <t>10.1021/ja034121l</t>
         </is>
@@ -22381,10 +22776,11 @@
       <c r="Z253" s="2" t="inlineStr"/>
       <c r="AA253" s="2" t="inlineStr"/>
       <c r="AB253" s="2" t="inlineStr"/>
-      <c r="AC253" s="3" t="n">
+      <c r="AC253" s="2" t="inlineStr"/>
+      <c r="AD253" s="3" t="n">
         <v>3.05</v>
       </c>
-      <c r="AD253" s="2" t="inlineStr">
+      <c r="AE253" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2004.12.024</t>
         </is>
@@ -22459,10 +22855,11 @@
       <c r="Z254" s="2" t="inlineStr"/>
       <c r="AA254" s="2" t="inlineStr"/>
       <c r="AB254" s="2" t="inlineStr"/>
-      <c r="AC254" s="3" t="n">
+      <c r="AC254" s="2" t="inlineStr"/>
+      <c r="AD254" s="3" t="n">
         <v>2.85</v>
       </c>
-      <c r="AD254" s="2" t="inlineStr">
+      <c r="AE254" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic050087v</t>
         </is>
@@ -22537,10 +22934,11 @@
       <c r="Z255" s="2" t="inlineStr"/>
       <c r="AA255" s="2" t="inlineStr"/>
       <c r="AB255" s="2" t="inlineStr"/>
-      <c r="AC255" s="3" t="n">
+      <c r="AC255" s="2" t="inlineStr"/>
+      <c r="AD255" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="AD255" s="2" t="inlineStr">
+      <c r="AE255" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -22615,10 +23013,11 @@
       <c r="Z256" s="2" t="inlineStr"/>
       <c r="AA256" s="2" t="inlineStr"/>
       <c r="AB256" s="2" t="inlineStr"/>
-      <c r="AC256" s="3" t="n">
+      <c r="AC256" s="2" t="inlineStr"/>
+      <c r="AD256" s="3" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD256" s="2" t="inlineStr">
+      <c r="AE256" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -22701,10 +23100,11 @@
       <c r="Z257" s="2" t="inlineStr"/>
       <c r="AA257" s="2" t="inlineStr"/>
       <c r="AB257" s="2" t="inlineStr"/>
-      <c r="AC257" s="3" t="n">
+      <c r="AC257" s="2" t="inlineStr"/>
+      <c r="AD257" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AD257" s="2" t="inlineStr">
+      <c r="AE257" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2009.02.020</t>
         </is>
@@ -22789,10 +23189,11 @@
       <c r="Z258" s="2" t="inlineStr"/>
       <c r="AA258" s="2" t="inlineStr"/>
       <c r="AB258" s="2" t="inlineStr"/>
-      <c r="AC258" s="3" t="n">
+      <c r="AC258" s="2" t="inlineStr"/>
+      <c r="AD258" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD258" s="2" t="inlineStr">
+      <c r="AE258" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -22871,10 +23272,11 @@
       <c r="Z259" s="2" t="inlineStr"/>
       <c r="AA259" s="2" t="inlineStr"/>
       <c r="AB259" s="2" t="inlineStr"/>
-      <c r="AC259" s="3" t="n">
+      <c r="AC259" s="2" t="inlineStr"/>
+      <c r="AD259" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="AD259" s="2" t="inlineStr">
+      <c r="AE259" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -22949,10 +23351,11 @@
       <c r="Z260" s="2" t="inlineStr"/>
       <c r="AA260" s="2" t="inlineStr"/>
       <c r="AB260" s="2" t="inlineStr"/>
-      <c r="AC260" s="3" t="n">
+      <c r="AC260" s="2" t="inlineStr"/>
+      <c r="AD260" s="3" t="n">
         <v>2.51</v>
       </c>
-      <c r="AD260" s="2" t="inlineStr">
+      <c r="AE260" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2009.02.020</t>
         </is>
@@ -23035,10 +23438,11 @@
       <c r="Z261" s="2" t="inlineStr"/>
       <c r="AA261" s="2" t="inlineStr"/>
       <c r="AB261" s="2" t="inlineStr"/>
-      <c r="AC261" s="3" t="n">
+      <c r="AC261" s="2" t="inlineStr"/>
+      <c r="AD261" s="3" t="n">
         <v>3.02</v>
       </c>
-      <c r="AD261" s="2" t="inlineStr">
+      <c r="AE261" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2008.11.017</t>
         </is>
@@ -23121,10 +23525,11 @@
       <c r="Z262" s="2" t="inlineStr"/>
       <c r="AA262" s="2" t="inlineStr"/>
       <c r="AB262" s="2" t="inlineStr"/>
-      <c r="AC262" s="3" t="n">
+      <c r="AC262" s="2" t="inlineStr"/>
+      <c r="AD262" s="3" t="n">
         <v>1.71</v>
       </c>
-      <c r="AD262" s="2" t="inlineStr">
+      <c r="AE262" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jallcom.2018.02.331</t>
         </is>
@@ -23199,10 +23604,11 @@
       <c r="Z263" s="2" t="inlineStr"/>
       <c r="AA263" s="2" t="inlineStr"/>
       <c r="AB263" s="2" t="inlineStr"/>
-      <c r="AC263" s="3" t="n">
+      <c r="AC263" s="2" t="inlineStr"/>
+      <c r="AD263" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD263" s="2" t="inlineStr">
+      <c r="AE263" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2010.05.003</t>
         </is>
@@ -23277,10 +23683,10 @@
         <v>6.68</v>
       </c>
       <c r="V264" s="3" t="n">
-        <v>6.98</v>
+        <v>6.99</v>
       </c>
       <c r="W264" s="3" t="n">
-        <v>6.94</v>
+        <v>6.93</v>
       </c>
       <c r="X264" s="3" t="n">
         <v>7.34</v>
@@ -23292,15 +23698,18 @@
         <v>8.08</v>
       </c>
       <c r="AA264" s="3" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="AB264" s="3" t="n">
         <v>7.57</v>
       </c>
-      <c r="AB264" s="3" t="n">
+      <c r="AC264" s="3" t="n">
         <v>7.41</v>
       </c>
-      <c r="AC264" s="3" t="n">
+      <c r="AD264" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD264" s="2" t="inlineStr">
+      <c r="AE264" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevLett.19.496</t>
         </is>
@@ -23390,15 +23799,18 @@
         <v>9.359999999999999</v>
       </c>
       <c r="AA265" s="3" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="AB265" s="3" t="n">
         <v>8.81</v>
       </c>
-      <c r="AB265" s="3" t="n">
+      <c r="AC265" s="3" t="n">
         <v>8.77</v>
       </c>
-      <c r="AC265" s="3" t="n">
+      <c r="AD265" s="3" t="n">
         <v>8.69</v>
       </c>
-      <c r="AD265" s="2" t="inlineStr">
+      <c r="AE265" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRev.166.599</t>
         </is>
@@ -23479,10 +23891,11 @@
       <c r="Z266" s="2" t="inlineStr"/>
       <c r="AA266" s="2" t="inlineStr"/>
       <c r="AB266" s="2" t="inlineStr"/>
-      <c r="AC266" s="3" t="n">
+      <c r="AC266" s="2" t="inlineStr"/>
+      <c r="AD266" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="AD266" s="2" t="inlineStr">
+      <c r="AE266" s="2" t="inlineStr">
         <is>
           <t>10.1039/C4RA12541J</t>
         </is>
@@ -23557,10 +23970,11 @@
       <c r="Z267" s="2" t="inlineStr"/>
       <c r="AA267" s="2" t="inlineStr"/>
       <c r="AB267" s="2" t="inlineStr"/>
-      <c r="AC267" s="3" t="n">
+      <c r="AC267" s="2" t="inlineStr"/>
+      <c r="AD267" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD267" s="2" t="inlineStr">
+      <c r="AE267" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2012.08.039</t>
         </is>
@@ -23635,10 +24049,11 @@
       <c r="Z268" s="2" t="inlineStr"/>
       <c r="AA268" s="2" t="inlineStr"/>
       <c r="AB268" s="2" t="inlineStr"/>
-      <c r="AC268" s="3" t="n">
+      <c r="AC268" s="2" t="inlineStr"/>
+      <c r="AD268" s="3" t="n">
         <v>2.95</v>
       </c>
-      <c r="AD268" s="2" t="inlineStr">
+      <c r="AE268" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic050561x</t>
         </is>
@@ -23713,7 +24128,7 @@
         <v>10.38</v>
       </c>
       <c r="V269" s="3" t="n">
-        <v>11.17</v>
+        <v>11.16</v>
       </c>
       <c r="W269" s="3" t="n">
         <v>11.03</v>
@@ -23728,15 +24143,18 @@
         <v>12</v>
       </c>
       <c r="AA269" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AB269" s="3" t="n">
         <v>11.15</v>
       </c>
-      <c r="AB269" s="3" t="n">
+      <c r="AC269" s="3" t="n">
         <v>10.92</v>
       </c>
-      <c r="AC269" s="3" t="n">
+      <c r="AD269" s="3" t="n">
         <v>11.59</v>
       </c>
-      <c r="AD269" s="2" t="inlineStr">
+      <c r="AE269" s="2" t="inlineStr">
         <is>
           <t>10.1016/0030-4018(86)90186-0</t>
         </is>
@@ -23825,12 +24243,15 @@
       <c r="Z270" s="3" t="n">
         <v>4.66</v>
       </c>
-      <c r="AA270" s="2" t="inlineStr"/>
+      <c r="AA270" s="3" t="n">
+        <v>4.13</v>
+      </c>
       <c r="AB270" s="2" t="inlineStr"/>
-      <c r="AC270" s="3" t="n">
+      <c r="AC270" s="2" t="inlineStr"/>
+      <c r="AD270" s="3" t="n">
         <v>3.64</v>
       </c>
-      <c r="AD270" s="2" t="inlineStr">
+      <c r="AE270" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.74.155130</t>
         </is>
@@ -23911,12 +24332,15 @@
       <c r="Z271" s="3" t="n">
         <v>6.58</v>
       </c>
-      <c r="AA271" s="2" t="inlineStr"/>
+      <c r="AA271" s="3" t="n">
+        <v>6.1</v>
+      </c>
       <c r="AB271" s="2" t="inlineStr"/>
-      <c r="AC271" s="3" t="n">
+      <c r="AC271" s="2" t="inlineStr"/>
+      <c r="AD271" s="3" t="n">
         <v>5.34</v>
       </c>
-      <c r="AD271" s="2" t="inlineStr">
+      <c r="AE271" s="2" t="inlineStr">
         <is>
           <t>10.1143/JPSJ.69.3451</t>
         </is>
@@ -23991,10 +24415,11 @@
       <c r="Z272" s="2" t="inlineStr"/>
       <c r="AA272" s="2" t="inlineStr"/>
       <c r="AB272" s="2" t="inlineStr"/>
-      <c r="AC272" s="3" t="n">
+      <c r="AC272" s="2" t="inlineStr"/>
+      <c r="AD272" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="AD272" s="2" t="inlineStr">
+      <c r="AE272" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.1364656</t>
         </is>
@@ -24069,10 +24494,11 @@
       <c r="Z273" s="2" t="inlineStr"/>
       <c r="AA273" s="2" t="inlineStr"/>
       <c r="AB273" s="2" t="inlineStr"/>
-      <c r="AC273" s="3" t="n">
+      <c r="AC273" s="2" t="inlineStr"/>
+      <c r="AD273" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="AD273" s="2" t="inlineStr">
+      <c r="AE273" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.1456240</t>
         </is>
@@ -24147,10 +24573,11 @@
       <c r="Z274" s="2" t="inlineStr"/>
       <c r="AA274" s="2" t="inlineStr"/>
       <c r="AB274" s="2" t="inlineStr"/>
-      <c r="AC274" s="3" t="n">
+      <c r="AC274" s="2" t="inlineStr"/>
+      <c r="AD274" s="3" t="n">
         <v>2.31</v>
       </c>
-      <c r="AD274" s="2" t="inlineStr">
+      <c r="AE274" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2006.09.014</t>
         </is>
@@ -24225,10 +24652,11 @@
       <c r="Z275" s="2" t="inlineStr"/>
       <c r="AA275" s="2" t="inlineStr"/>
       <c r="AB275" s="2" t="inlineStr"/>
-      <c r="AC275" s="3" t="n">
+      <c r="AC275" s="2" t="inlineStr"/>
+      <c r="AD275" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="AD275" s="2" t="inlineStr">
+      <c r="AE275" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.18.5740</t>
         </is>
@@ -24303,10 +24731,11 @@
       <c r="Z276" s="2" t="inlineStr"/>
       <c r="AA276" s="2" t="inlineStr"/>
       <c r="AB276" s="2" t="inlineStr"/>
-      <c r="AC276" s="3" t="n">
+      <c r="AC276" s="2" t="inlineStr"/>
+      <c r="AD276" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD276" s="2" t="inlineStr">
+      <c r="AE276" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.tsf.2007.10.035</t>
         </is>
@@ -24381,10 +24810,11 @@
       <c r="Z277" s="2" t="inlineStr"/>
       <c r="AA277" s="2" t="inlineStr"/>
       <c r="AB277" s="2" t="inlineStr"/>
-      <c r="AC277" s="3" t="n">
+      <c r="AC277" s="2" t="inlineStr"/>
+      <c r="AD277" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD277" s="2" t="inlineStr">
+      <c r="AE277" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.tsf.2007.10.035</t>
         </is>
@@ -24408,7 +24838,7 @@
         <v>1.02</v>
       </c>
       <c r="E278" s="3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="3" t="n">
@@ -24418,7 +24848,7 @@
         <v>1.11</v>
       </c>
       <c r="I278" s="3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="J278" s="3" t="n">
         <v>1.08</v>
@@ -24457,20 +24887,21 @@
         <v>2.1</v>
       </c>
       <c r="V278" s="3" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="W278" s="3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="X278" s="2" t="inlineStr"/>
       <c r="Y278" s="2" t="inlineStr"/>
       <c r="Z278" s="2" t="inlineStr"/>
       <c r="AA278" s="2" t="inlineStr"/>
       <c r="AB278" s="2" t="inlineStr"/>
-      <c r="AC278" s="3" t="n">
+      <c r="AC278" s="2" t="inlineStr"/>
+      <c r="AD278" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="AD278" s="2" t="inlineStr">
+      <c r="AE278" s="2" t="inlineStr">
         <is>
           <t>10.1002/anie.200801392</t>
         </is>
@@ -24553,10 +24984,11 @@
       <c r="Z279" s="2" t="inlineStr"/>
       <c r="AA279" s="2" t="inlineStr"/>
       <c r="AB279" s="2" t="inlineStr"/>
-      <c r="AC279" s="3" t="n">
+      <c r="AC279" s="2" t="inlineStr"/>
+      <c r="AD279" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="AD279" s="2" t="inlineStr">
+      <c r="AE279" s="2" t="inlineStr">
         <is>
           <t>10.1021/ja9094846</t>
         </is>
@@ -24631,7 +25063,7 @@
         <v>6.53</v>
       </c>
       <c r="V280" s="3" t="n">
-        <v>7.19</v>
+        <v>7.2</v>
       </c>
       <c r="W280" s="3" t="n">
         <v>7.14</v>
@@ -24646,15 +25078,18 @@
         <v>8.369999999999999</v>
       </c>
       <c r="AA280" s="3" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="AB280" s="3" t="n">
         <v>7.61</v>
       </c>
-      <c r="AB280" s="3" t="n">
+      <c r="AC280" s="3" t="n">
         <v>7.44</v>
       </c>
-      <c r="AC280" s="3" t="n">
+      <c r="AD280" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD280" s="2" t="inlineStr">
+      <c r="AE280" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssb.19700380132</t>
         </is>
@@ -24744,15 +25179,18 @@
         <v>10.38</v>
       </c>
       <c r="AA281" s="3" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="AB281" s="3" t="n">
         <v>9.369999999999999</v>
       </c>
-      <c r="AB281" s="3" t="n">
+      <c r="AC281" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="AC281" s="3" t="n">
+      <c r="AD281" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD281" s="2" t="inlineStr">
+      <c r="AE281" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssb.19700380132</t>
         </is>
@@ -24776,7 +25214,7 @@
         <v>0.9</v>
       </c>
       <c r="E282" s="3" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="F282" s="3" t="n">
         <v>0.92</v>
@@ -24827,7 +25265,7 @@
         <v>7.61</v>
       </c>
       <c r="V282" s="3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W282" s="3" t="n">
         <v>2.03</v>
@@ -24841,12 +25279,15 @@
       <c r="Z282" s="3" t="n">
         <v>4.28</v>
       </c>
-      <c r="AA282" s="2" t="inlineStr"/>
+      <c r="AA282" s="3" t="n">
+        <v>3.62</v>
+      </c>
       <c r="AB282" s="2" t="inlineStr"/>
-      <c r="AC282" s="3" t="n">
+      <c r="AC282" s="2" t="inlineStr"/>
+      <c r="AD282" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD282" s="2" t="inlineStr">
+      <c r="AE282" s="2" t="inlineStr">
         <is>
           <t>10.1016/S0038-1098(02)00325-3</t>
         </is>
@@ -24936,15 +25377,18 @@
         <v>15.84</v>
       </c>
       <c r="AA283" s="3" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="AB283" s="3" t="n">
         <v>14.53</v>
       </c>
-      <c r="AB283" s="3" t="n">
+      <c r="AC283" s="3" t="n">
         <v>14.52</v>
       </c>
-      <c r="AC283" s="3" t="n">
+      <c r="AD283" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="AD283" s="2" t="inlineStr">
+      <c r="AE283" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(67)90280-6</t>
         </is>
@@ -25027,10 +25471,11 @@
       <c r="Z284" s="2" t="inlineStr"/>
       <c r="AA284" s="2" t="inlineStr"/>
       <c r="AB284" s="2" t="inlineStr"/>
-      <c r="AC284" s="3" t="n">
+      <c r="AC284" s="2" t="inlineStr"/>
+      <c r="AD284" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="AD284" s="2" t="inlineStr">
+      <c r="AE284" s="2" t="inlineStr">
         <is>
           <t>10.1021/cg050076c</t>
         </is>
@@ -25116,15 +25561,18 @@
         <v>6.69</v>
       </c>
       <c r="AA285" s="3" t="n">
-        <v>5.65</v>
+        <v>5.88</v>
       </c>
       <c r="AB285" s="3" t="n">
         <v>5.65</v>
       </c>
       <c r="AC285" s="3" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD285" s="3" t="n">
         <v>4.94</v>
       </c>
-      <c r="AD285" s="2" t="inlineStr">
+      <c r="AE285" s="2" t="inlineStr">
         <is>
           <t>10.1143/JPSJ.57.367</t>
         </is>
@@ -25199,10 +25647,11 @@
       <c r="Z286" s="2" t="inlineStr"/>
       <c r="AA286" s="2" t="inlineStr"/>
       <c r="AB286" s="2" t="inlineStr"/>
-      <c r="AC286" s="3" t="n">
+      <c r="AC286" s="2" t="inlineStr"/>
+      <c r="AD286" s="3" t="n">
         <v>4.27</v>
       </c>
-      <c r="AD286" s="2" t="inlineStr">
+      <c r="AE286" s="2" t="inlineStr">
         <is>
           <t>10.1039/C0DT01272F</t>
         </is>
@@ -25277,10 +25726,11 @@
       <c r="Z287" s="2" t="inlineStr"/>
       <c r="AA287" s="2" t="inlineStr"/>
       <c r="AB287" s="2" t="inlineStr"/>
-      <c r="AC287" s="3" t="n">
+      <c r="AC287" s="2" t="inlineStr"/>
+      <c r="AD287" s="3" t="n">
         <v>3.01</v>
       </c>
-      <c r="AD287" s="2" t="inlineStr">
+      <c r="AE287" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.1478139</t>
         </is>
@@ -25353,7 +25803,7 @@
         <v>2.4</v>
       </c>
       <c r="V288" s="3" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="W288" s="3" t="n">
         <v>0.23</v>
@@ -25363,10 +25813,11 @@
       <c r="Z288" s="2" t="inlineStr"/>
       <c r="AA288" s="2" t="inlineStr"/>
       <c r="AB288" s="2" t="inlineStr"/>
-      <c r="AC288" s="3" t="n">
+      <c r="AC288" s="2" t="inlineStr"/>
+      <c r="AD288" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="AD288" s="2" t="inlineStr">
+      <c r="AE288" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.73.115110</t>
         </is>
@@ -25449,10 +25900,11 @@
       <c r="Z289" s="2" t="inlineStr"/>
       <c r="AA289" s="2" t="inlineStr"/>
       <c r="AB289" s="2" t="inlineStr"/>
-      <c r="AC289" s="3" t="n">
+      <c r="AC289" s="2" t="inlineStr"/>
+      <c r="AD289" s="3" t="n">
         <v>3.78</v>
       </c>
-      <c r="AD289" s="2" t="inlineStr">
+      <c r="AE289" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.346951</t>
         </is>
@@ -25535,10 +25987,11 @@
       <c r="Z290" s="2" t="inlineStr"/>
       <c r="AA290" s="2" t="inlineStr"/>
       <c r="AB290" s="2" t="inlineStr"/>
-      <c r="AC290" s="3" t="n">
+      <c r="AC290" s="2" t="inlineStr"/>
+      <c r="AD290" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="AD290" s="2" t="inlineStr">
+      <c r="AE290" s="2" t="inlineStr">
         <is>
           <t>10.1021/jp004386b</t>
         </is>
@@ -25628,15 +26081,18 @@
         <v>1.95</v>
       </c>
       <c r="AA291" s="3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB291" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB291" s="3" t="n">
+      <c r="AC291" s="3" t="n">
         <v>1.66</v>
       </c>
-      <c r="AC291" s="3" t="n">
+      <c r="AD291" s="3" t="n">
         <v>1.61</v>
       </c>
-      <c r="AD291" s="2" t="inlineStr">
+      <c r="AE291" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.49.11452</t>
         </is>
@@ -25726,15 +26182,18 @@
         <v>2.51</v>
       </c>
       <c r="AA292" s="3" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AB292" s="3" t="n">
         <v>2.11</v>
       </c>
       <c r="AC292" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD292" s="3" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD292" s="2" t="inlineStr">
+      <c r="AE292" s="2" t="inlineStr">
         <is>
           <t>10.1016/S0022-0248(98)00984-1</t>
         </is>
@@ -25824,15 +26283,18 @@
         <v>2.26</v>
       </c>
       <c r="AA293" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB293" s="3" t="n">
         <v>2.04</v>
       </c>
-      <c r="AB293" s="3" t="n">
+      <c r="AC293" s="3" t="n">
         <v>2.02</v>
       </c>
-      <c r="AC293" s="3" t="n">
+      <c r="AD293" s="3" t="n">
         <v>2.04</v>
       </c>
-      <c r="AD293" s="2" t="inlineStr">
+      <c r="AE293" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.37.7140</t>
         </is>
@@ -25925,12 +26387,15 @@
         <v>0.6</v>
       </c>
       <c r="AB294" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC294" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="AC294" s="3" t="n">
+      <c r="AD294" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AD294" s="2" t="inlineStr">
+      <c r="AE294" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRev.109.1916</t>
         </is>
@@ -26020,15 +26485,18 @@
         <v>0.72</v>
       </c>
       <c r="AA295" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB295" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB295" s="3" t="n">
+      <c r="AC295" s="3" t="n">
         <v>0.59</v>
       </c>
-      <c r="AC295" s="3" t="n">
+      <c r="AD295" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="AD295" s="2" t="inlineStr">
+      <c r="AE295" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRev.109.1909</t>
         </is>
@@ -26103,10 +26571,10 @@
         <v>0.09</v>
       </c>
       <c r="V296" s="3" t="n">
-        <v>0.61</v>
+        <v>0.44</v>
       </c>
       <c r="W296" s="3" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="X296" s="3" t="n">
         <v>0.31</v>
@@ -26118,15 +26586,18 @@
         <v>0.5</v>
       </c>
       <c r="AA296" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AB296" s="3" t="n">
         <v>0.41</v>
       </c>
-      <c r="AB296" s="3" t="n">
+      <c r="AC296" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="AC296" s="3" t="n">
+      <c r="AD296" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="AD296" s="2" t="inlineStr">
+      <c r="AE296" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -26215,12 +26686,15 @@
       <c r="Z297" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA297" s="2" t="inlineStr"/>
+      <c r="AA297" s="3" t="n">
+        <v>0.88</v>
+      </c>
       <c r="AB297" s="2" t="inlineStr"/>
-      <c r="AC297" s="3" t="n">
+      <c r="AC297" s="2" t="inlineStr"/>
+      <c r="AD297" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="AD297" s="2" t="inlineStr">
+      <c r="AE297" s="2" t="inlineStr">
         <is>
           <t>10.1088/0022-3727/39/24/035</t>
         </is>
@@ -26310,15 +26784,18 @@
         <v>9.609999999999999</v>
       </c>
       <c r="AA298" s="3" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="AB298" s="3" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="AB298" s="3" t="n">
+      <c r="AC298" s="3" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="AC298" s="3" t="n">
+      <c r="AD298" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="AD298" s="2" t="inlineStr">
+      <c r="AE298" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.9.2679</t>
         </is>
@@ -26396,7 +26873,7 @@
         <v>11.68</v>
       </c>
       <c r="W299" s="3" t="n">
-        <v>11.53</v>
+        <v>11.54</v>
       </c>
       <c r="X299" s="3" t="n">
         <v>12.55</v>
@@ -26407,12 +26884,15 @@
       <c r="Z299" s="3" t="n">
         <v>13.83</v>
       </c>
-      <c r="AA299" s="2" t="inlineStr"/>
+      <c r="AA299" s="3" t="n">
+        <v>12.41</v>
+      </c>
       <c r="AB299" s="2" t="inlineStr"/>
-      <c r="AC299" s="3" t="n">
+      <c r="AC299" s="2" t="inlineStr"/>
+      <c r="AD299" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="AD299" s="2" t="inlineStr">
+      <c r="AE299" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssb.2220560115</t>
         </is>
@@ -26502,15 +26982,18 @@
         <v>8.83</v>
       </c>
       <c r="AA300" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB300" s="3" t="n">
         <v>7.92</v>
       </c>
-      <c r="AB300" s="3" t="n">
+      <c r="AC300" s="3" t="n">
         <v>7.91</v>
       </c>
-      <c r="AC300" s="3" t="n">
+      <c r="AD300" s="3" t="n">
         <v>7.67</v>
       </c>
-      <c r="AD300" s="2" t="inlineStr">
+      <c r="AE300" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -26591,10 +27074,11 @@
       <c r="Z301" s="2" t="inlineStr"/>
       <c r="AA301" s="2" t="inlineStr"/>
       <c r="AB301" s="2" t="inlineStr"/>
-      <c r="AC301" s="3" t="n">
+      <c r="AC301" s="2" t="inlineStr"/>
+      <c r="AD301" s="3" t="n">
         <v>2.41</v>
       </c>
-      <c r="AD301" s="2" t="inlineStr">
+      <c r="AE301" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssb.2221060110</t>
         </is>
@@ -26683,12 +27167,15 @@
       <c r="Z302" s="3" t="n">
         <v>4.55</v>
       </c>
-      <c r="AA302" s="2" t="inlineStr"/>
+      <c r="AA302" s="3" t="n">
+        <v>4.11</v>
+      </c>
       <c r="AB302" s="2" t="inlineStr"/>
-      <c r="AC302" s="3" t="n">
+      <c r="AC302" s="2" t="inlineStr"/>
+      <c r="AD302" s="3" t="n">
         <v>3.49</v>
       </c>
-      <c r="AD302" s="2" t="inlineStr">
+      <c r="AE302" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -26777,10 +27264,11 @@
       </c>
       <c r="AA303" s="2" t="inlineStr"/>
       <c r="AB303" s="2" t="inlineStr"/>
-      <c r="AC303" s="3" t="n">
+      <c r="AC303" s="2" t="inlineStr"/>
+      <c r="AD303" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="AD303" s="2" t="inlineStr">
+      <c r="AE303" s="2" t="inlineStr">
         <is>
           <t>10.1021/j100393a010</t>
         </is>
@@ -26804,7 +27292,7 @@
         <v>0.75</v>
       </c>
       <c r="E304" s="3" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="F304" s="3" t="n">
         <v>0.76</v>
@@ -26855,10 +27343,10 @@
         <v>1.37</v>
       </c>
       <c r="V304" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="W304" s="3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X304" s="3" t="n">
         <v>1.21</v>
@@ -26870,15 +27358,18 @@
         <v>1.24</v>
       </c>
       <c r="AA304" s="3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AB304" s="3" t="n">
         <v>1.17</v>
       </c>
       <c r="AC304" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD304" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="AD304" s="2" t="inlineStr">
+      <c r="AE304" s="2" t="inlineStr">
         <is>
           <t>10.1021/j100393a010</t>
         </is>
@@ -26902,7 +27393,7 @@
         <v>0.71</v>
       </c>
       <c r="E305" s="3" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="F305" s="3" t="n">
         <v>0.7</v>
@@ -26914,7 +27405,7 @@
         <v>0.74</v>
       </c>
       <c r="I305" s="3" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="J305" s="3" t="n">
         <v>0.71</v>
@@ -26953,10 +27444,10 @@
         <v>1.07</v>
       </c>
       <c r="V305" s="3" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="W305" s="3" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="X305" s="3" t="n">
         <v>1.03</v>
@@ -26967,12 +27458,15 @@
       <c r="Z305" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="AA305" s="2" t="inlineStr"/>
+      <c r="AA305" s="3" t="n">
+        <v>1.01</v>
+      </c>
       <c r="AB305" s="2" t="inlineStr"/>
-      <c r="AC305" s="3" t="n">
+      <c r="AC305" s="2" t="inlineStr"/>
+      <c r="AD305" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="AD305" s="2" t="inlineStr">
+      <c r="AE305" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssb.2220940132</t>
         </is>
@@ -27055,10 +27549,11 @@
       <c r="Z306" s="2" t="inlineStr"/>
       <c r="AA306" s="2" t="inlineStr"/>
       <c r="AB306" s="2" t="inlineStr"/>
-      <c r="AC306" s="3" t="n">
+      <c r="AC306" s="2" t="inlineStr"/>
+      <c r="AD306" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AD306" s="2" t="inlineStr">
+      <c r="AE306" s="2" t="inlineStr">
         <is>
           <t>10.1039/B110254K</t>
         </is>
@@ -27151,12 +27646,15 @@
         <v>1.83</v>
       </c>
       <c r="AB307" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC307" s="3" t="n">
         <v>1.66</v>
       </c>
-      <c r="AC307" s="3" t="n">
+      <c r="AD307" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AD307" s="2" t="inlineStr">
+      <c r="AE307" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -27231,10 +27729,11 @@
       <c r="Z308" s="2" t="inlineStr"/>
       <c r="AA308" s="2" t="inlineStr"/>
       <c r="AB308" s="2" t="inlineStr"/>
-      <c r="AC308" s="3" t="n">
+      <c r="AC308" s="2" t="inlineStr"/>
+      <c r="AD308" s="3" t="n">
         <v>1.95</v>
       </c>
-      <c r="AD308" s="2" t="inlineStr">
+      <c r="AE308" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -27309,10 +27808,11 @@
       <c r="Z309" s="2" t="inlineStr"/>
       <c r="AA309" s="2" t="inlineStr"/>
       <c r="AB309" s="2" t="inlineStr"/>
-      <c r="AC309" s="3" t="n">
+      <c r="AC309" s="2" t="inlineStr"/>
+      <c r="AD309" s="3" t="n">
         <v>3.51</v>
       </c>
-      <c r="AD309" s="2" t="inlineStr">
+      <c r="AE309" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jssc.2017.03.017</t>
         </is>
@@ -27385,7 +27885,7 @@
         <v>0.84</v>
       </c>
       <c r="V310" s="3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W310" s="3" t="n">
         <v>1.42</v>
@@ -27395,10 +27895,11 @@
       <c r="Z310" s="2" t="inlineStr"/>
       <c r="AA310" s="2" t="inlineStr"/>
       <c r="AB310" s="2" t="inlineStr"/>
-      <c r="AC310" s="3" t="n">
+      <c r="AC310" s="2" t="inlineStr"/>
+      <c r="AD310" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="AD310" s="2" t="inlineStr">
+      <c r="AE310" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -27473,10 +27974,11 @@
       <c r="Z311" s="2" t="inlineStr"/>
       <c r="AA311" s="2" t="inlineStr"/>
       <c r="AB311" s="2" t="inlineStr"/>
-      <c r="AC311" s="3" t="n">
+      <c r="AC311" s="2" t="inlineStr"/>
+      <c r="AD311" s="3" t="n">
         <v>2.23</v>
       </c>
-      <c r="AD311" s="2" t="inlineStr">
+      <c r="AE311" s="2" t="inlineStr">
         <is>
           <t>10.1002/anie.200801392</t>
         </is>
@@ -27566,15 +28068,18 @@
         <v>7.89</v>
       </c>
       <c r="AA312" s="3" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="AB312" s="3" t="n">
         <v>7.13</v>
       </c>
-      <c r="AB312" s="3" t="n">
+      <c r="AC312" s="3" t="n">
         <v>6.97</v>
       </c>
-      <c r="AC312" s="3" t="n">
+      <c r="AD312" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="AD312" s="2" t="inlineStr">
+      <c r="AE312" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevLett.19.496</t>
         </is>
@@ -27664,15 +28169,18 @@
         <v>9.470000000000001</v>
       </c>
       <c r="AA313" s="3" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="AB313" s="3" t="n">
         <v>8.49</v>
       </c>
-      <c r="AB313" s="3" t="n">
+      <c r="AC313" s="3" t="n">
         <v>8.44</v>
       </c>
-      <c r="AC313" s="3" t="n">
+      <c r="AD313" s="3" t="n">
         <v>8.75</v>
       </c>
-      <c r="AD313" s="2" t="inlineStr">
+      <c r="AE313" s="2" t="inlineStr">
         <is>
           <t>10.1143/JPSJ.24.1286</t>
         </is>
@@ -27747,10 +28255,10 @@
         <v>12.86</v>
       </c>
       <c r="V314" s="3" t="n">
-        <v>11.07</v>
+        <v>11.06</v>
       </c>
       <c r="W314" s="3" t="n">
-        <v>10.76</v>
+        <v>10.77</v>
       </c>
       <c r="X314" s="3" t="n">
         <v>11.69</v>
@@ -27762,15 +28270,18 @@
         <v>12.97</v>
       </c>
       <c r="AA314" s="3" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="AB314" s="3" t="n">
         <v>11.94</v>
       </c>
-      <c r="AB314" s="3" t="n">
+      <c r="AC314" s="3" t="n">
         <v>11.92</v>
       </c>
-      <c r="AC314" s="3" t="n">
+      <c r="AD314" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="AD314" s="2" t="inlineStr">
+      <c r="AE314" s="2" t="inlineStr">
         <is>
           <t>10.1143/JPSJ.26.1427</t>
         </is>
@@ -27848,7 +28359,7 @@
         <v>5.66</v>
       </c>
       <c r="W315" s="3" t="n">
-        <v>6.52</v>
+        <v>6.51</v>
       </c>
       <c r="X315" s="3" t="n">
         <v>6.04</v>
@@ -27860,15 +28371,18 @@
         <v>6.67</v>
       </c>
       <c r="AA315" s="3" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AB315" s="3" t="n">
         <v>5.99</v>
       </c>
-      <c r="AB315" s="3" t="n">
+      <c r="AC315" s="3" t="n">
         <v>5.65</v>
       </c>
-      <c r="AC315" s="3" t="n">
+      <c r="AD315" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="AD315" s="2" t="inlineStr">
+      <c r="AE315" s="2" t="inlineStr">
         <is>
           <t>10.1143/JPSJ.26.1427</t>
         </is>
@@ -27943,10 +28457,11 @@
       <c r="Z316" s="2" t="inlineStr"/>
       <c r="AA316" s="2" t="inlineStr"/>
       <c r="AB316" s="2" t="inlineStr"/>
-      <c r="AC316" s="3" t="n">
+      <c r="AC316" s="2" t="inlineStr"/>
+      <c r="AD316" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AD316" s="2" t="inlineStr">
+      <c r="AE316" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jcrysgro.2007.10.030</t>
         </is>
@@ -28021,10 +28536,11 @@
       <c r="Z317" s="2" t="inlineStr"/>
       <c r="AA317" s="2" t="inlineStr"/>
       <c r="AB317" s="2" t="inlineStr"/>
-      <c r="AC317" s="3" t="n">
+      <c r="AC317" s="2" t="inlineStr"/>
+      <c r="AD317" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD317" s="2" t="inlineStr">
+      <c r="AE317" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.materresbull.2005.12.006</t>
         </is>
@@ -28099,10 +28615,11 @@
       <c r="Z318" s="2" t="inlineStr"/>
       <c r="AA318" s="2" t="inlineStr"/>
       <c r="AB318" s="2" t="inlineStr"/>
-      <c r="AC318" s="3" t="n">
+      <c r="AC318" s="2" t="inlineStr"/>
+      <c r="AD318" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AD318" s="2" t="inlineStr">
+      <c r="AE318" s="2" t="inlineStr">
         <is>
           <t>10.1021/jp004386b</t>
         </is>
@@ -28169,10 +28686,11 @@
       <c r="Z319" s="2" t="inlineStr"/>
       <c r="AA319" s="2" t="inlineStr"/>
       <c r="AB319" s="2" t="inlineStr"/>
-      <c r="AC319" s="3" t="n">
+      <c r="AC319" s="2" t="inlineStr"/>
+      <c r="AD319" s="3" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD319" s="2" t="inlineStr">
+      <c r="AE319" s="2" t="inlineStr">
         <is>
           <t>10.1006/jssc.2001.9222</t>
         </is>
@@ -28247,7 +28765,7 @@
         <v>21.5</v>
       </c>
       <c r="V320" s="3" t="n">
-        <v>20.13</v>
+        <v>20.12</v>
       </c>
       <c r="W320" s="3" t="n">
         <v>19.59</v>
@@ -28262,15 +28780,18 @@
         <v>23.33</v>
       </c>
       <c r="AA320" s="3" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="AB320" s="3" t="n">
         <v>22.74</v>
       </c>
-      <c r="AB320" s="3" t="n">
+      <c r="AC320" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="AC320" s="3" t="n">
+      <c r="AD320" s="3" t="n">
         <v>21.48</v>
       </c>
-      <c r="AD320" s="2" t="inlineStr">
+      <c r="AE320" s="2" t="inlineStr">
         <is>
           <t>10.1016/0030-4018(86)90186-0</t>
         </is>
@@ -28294,7 +28815,7 @@
         <v>0.67</v>
       </c>
       <c r="E321" s="3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="F321" s="3" t="n">
         <v>0.65</v>
@@ -28306,7 +28827,7 @@
         <v>0.7</v>
       </c>
       <c r="I321" s="3" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J321" s="3" t="n">
         <v>0.66</v>
@@ -28345,10 +28866,10 @@
         <v>1.17</v>
       </c>
       <c r="V321" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W321" s="3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="X321" s="3" t="n">
         <v>1.06</v>
@@ -28359,12 +28880,15 @@
       <c r="Z321" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AA321" s="2" t="inlineStr"/>
+      <c r="AA321" s="3" t="n">
+        <v>1.06</v>
+      </c>
       <c r="AB321" s="2" t="inlineStr"/>
-      <c r="AC321" s="3" t="n">
+      <c r="AC321" s="2" t="inlineStr"/>
+      <c r="AD321" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="AD321" s="2" t="inlineStr">
+      <c r="AE321" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic501733z</t>
         </is>
@@ -28388,7 +28912,7 @@
         <v>0.76</v>
       </c>
       <c r="E322" s="3" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="F322" s="3" t="n">
         <v>0.73</v>
@@ -28400,7 +28924,7 @@
         <v>0.78</v>
       </c>
       <c r="I322" s="3" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="J322" s="3" t="n">
         <v>0.71</v>
@@ -28439,10 +28963,10 @@
         <v>1.21</v>
       </c>
       <c r="V322" s="3" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="W322" s="3" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="X322" s="3" t="n">
         <v>1.14</v>
@@ -28453,12 +28977,15 @@
       <c r="Z322" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="AA322" s="2" t="inlineStr"/>
+      <c r="AA322" s="3" t="n">
+        <v>1.17</v>
+      </c>
       <c r="AB322" s="2" t="inlineStr"/>
-      <c r="AC322" s="3" t="n">
+      <c r="AC322" s="2" t="inlineStr"/>
+      <c r="AD322" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="AD322" s="2" t="inlineStr">
+      <c r="AE322" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic501733z</t>
         </is>
@@ -28547,12 +29074,15 @@
       <c r="Z323" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="AA323" s="2" t="inlineStr"/>
+      <c r="AA323" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AB323" s="2" t="inlineStr"/>
-      <c r="AC323" s="3" t="n">
+      <c r="AC323" s="2" t="inlineStr"/>
+      <c r="AD323" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="AD323" s="2" t="inlineStr">
+      <c r="AE323" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic501733z</t>
         </is>
@@ -28627,7 +29157,7 @@
         <v>0.1</v>
       </c>
       <c r="V324" s="3" t="n">
-        <v>0.37</v>
+        <v>0.28</v>
       </c>
       <c r="W324" s="3" t="n">
         <v>0.6</v>
@@ -28648,9 +29178,12 @@
         <v>0.22</v>
       </c>
       <c r="AC324" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AD324" s="3" t="n">
         <v>0.31</v>
       </c>
-      <c r="AD324" s="2" t="inlineStr">
+      <c r="AE324" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -28725,10 +29258,11 @@
       <c r="Z325" s="2" t="inlineStr"/>
       <c r="AA325" s="2" t="inlineStr"/>
       <c r="AB325" s="2" t="inlineStr"/>
-      <c r="AC325" s="3" t="n">
+      <c r="AC325" s="2" t="inlineStr"/>
+      <c r="AD325" s="3" t="n">
         <v>5.87</v>
       </c>
-      <c r="AD325" s="2" t="inlineStr">
+      <c r="AE325" s="2" t="inlineStr">
         <is>
           <t>10.1002/chem.201601149</t>
         </is>
@@ -28804,17 +29338,18 @@
         <v>4.1</v>
       </c>
       <c r="W326" s="3" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="X326" s="2" t="inlineStr"/>
       <c r="Y326" s="2" t="inlineStr"/>
       <c r="Z326" s="2" t="inlineStr"/>
       <c r="AA326" s="2" t="inlineStr"/>
       <c r="AB326" s="2" t="inlineStr"/>
-      <c r="AC326" s="3" t="n">
+      <c r="AC326" s="2" t="inlineStr"/>
+      <c r="AD326" s="3" t="n">
         <v>3.98</v>
       </c>
-      <c r="AD326" s="2" t="inlineStr">
+      <c r="AE326" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssb.2220570157</t>
         </is>
@@ -28887,20 +29422,21 @@
         <v>5.78</v>
       </c>
       <c r="V327" s="3" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="W327" s="3" t="n">
-        <v>5.29</v>
+        <v>5.3</v>
       </c>
       <c r="X327" s="2" t="inlineStr"/>
       <c r="Y327" s="2" t="inlineStr"/>
       <c r="Z327" s="2" t="inlineStr"/>
       <c r="AA327" s="2" t="inlineStr"/>
       <c r="AB327" s="2" t="inlineStr"/>
-      <c r="AC327" s="3" t="n">
+      <c r="AC327" s="2" t="inlineStr"/>
+      <c r="AD327" s="3" t="n">
         <v>4.86</v>
       </c>
-      <c r="AD327" s="2" t="inlineStr">
+      <c r="AE327" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -28975,10 +29511,11 @@
       <c r="Z328" s="2" t="inlineStr"/>
       <c r="AA328" s="2" t="inlineStr"/>
       <c r="AB328" s="2" t="inlineStr"/>
-      <c r="AC328" s="3" t="n">
+      <c r="AC328" s="2" t="inlineStr"/>
+      <c r="AD328" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD328" s="2" t="inlineStr">
+      <c r="AE328" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.inorgchem.5b01135</t>
         </is>
@@ -29053,10 +29590,11 @@
       <c r="Z329" s="2" t="inlineStr"/>
       <c r="AA329" s="2" t="inlineStr"/>
       <c r="AB329" s="2" t="inlineStr"/>
-      <c r="AC329" s="3" t="n">
+      <c r="AC329" s="2" t="inlineStr"/>
+      <c r="AD329" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD329" s="2" t="inlineStr">
+      <c r="AE329" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.cgd.5b00418</t>
         </is>
@@ -29092,7 +29630,7 @@
         <v>4.43</v>
       </c>
       <c r="I330" s="3" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="J330" s="3" t="n">
         <v>4.15</v>
@@ -29134,7 +29672,7 @@
         <v>6.68</v>
       </c>
       <c r="W330" s="3" t="n">
-        <v>6.39</v>
+        <v>6.38</v>
       </c>
       <c r="X330" s="3" t="n">
         <v>6.92</v>
@@ -29146,15 +29684,18 @@
         <v>7.73</v>
       </c>
       <c r="AA330" s="3" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="AB330" s="3" t="n">
         <v>7.09</v>
       </c>
-      <c r="AB330" s="3" t="n">
+      <c r="AC330" s="3" t="n">
         <v>6.95</v>
       </c>
-      <c r="AC330" s="3" t="n">
+      <c r="AD330" s="3" t="n">
         <v>5.68</v>
       </c>
-      <c r="AD330" s="2" t="inlineStr">
+      <c r="AE330" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -29229,7 +29770,7 @@
         <v>3.3</v>
       </c>
       <c r="V331" s="3" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="W331" s="3" t="n">
         <v>3.81</v>
@@ -29243,12 +29784,15 @@
       <c r="Z331" s="3" t="n">
         <v>3.46</v>
       </c>
-      <c r="AA331" s="2" t="inlineStr"/>
+      <c r="AA331" s="3" t="n">
+        <v>3.19</v>
+      </c>
       <c r="AB331" s="2" t="inlineStr"/>
-      <c r="AC331" s="3" t="n">
+      <c r="AC331" s="2" t="inlineStr"/>
+      <c r="AD331" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="AD331" s="2" t="inlineStr">
+      <c r="AE331" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.4939269</t>
         </is>
@@ -29272,7 +29816,7 @@
         <v>2.69</v>
       </c>
       <c r="E332" s="3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="F332" s="2" t="inlineStr"/>
       <c r="G332" s="3" t="n">
@@ -29282,7 +29826,7 @@
         <v>2.72</v>
       </c>
       <c r="I332" s="3" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="J332" s="3" t="n">
         <v>2.62</v>
@@ -29321,20 +29865,21 @@
         <v>5.4</v>
       </c>
       <c r="V332" s="3" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="W332" s="3" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="X332" s="2" t="inlineStr"/>
       <c r="Y332" s="2" t="inlineStr"/>
       <c r="Z332" s="2" t="inlineStr"/>
       <c r="AA332" s="2" t="inlineStr"/>
       <c r="AB332" s="2" t="inlineStr"/>
-      <c r="AC332" s="3" t="n">
+      <c r="AC332" s="2" t="inlineStr"/>
+      <c r="AD332" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="AD332" s="2" t="inlineStr">
+      <c r="AE332" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.optmat.2014.03.019</t>
         </is>
@@ -29424,15 +29969,18 @@
         <v>0.59</v>
       </c>
       <c r="AA333" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB333" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="AB333" s="3" t="n">
+      <c r="AC333" s="3" t="n">
         <v>0.26</v>
       </c>
-      <c r="AC333" s="3" t="n">
+      <c r="AD333" s="3" t="n">
         <v>0.29</v>
       </c>
-      <c r="AD333" s="2" t="inlineStr">
+      <c r="AE333" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -29507,7 +30055,7 @@
         <v>0.98</v>
       </c>
       <c r="V334" s="3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="W334" s="3" t="n">
         <v>0.53</v>
@@ -29522,15 +30070,18 @@
         <v>0.52</v>
       </c>
       <c r="AA334" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB334" s="3" t="n">
         <v>0.43</v>
       </c>
-      <c r="AB334" s="3" t="n">
+      <c r="AC334" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="AC334" s="3" t="n">
+      <c r="AD334" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="AD334" s="2" t="inlineStr">
+      <c r="AE334" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -29605,10 +30156,11 @@
       <c r="Z335" s="2" t="inlineStr"/>
       <c r="AA335" s="2" t="inlineStr"/>
       <c r="AB335" s="2" t="inlineStr"/>
-      <c r="AC335" s="3" t="n">
+      <c r="AC335" s="2" t="inlineStr"/>
+      <c r="AD335" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="AD335" s="2" t="inlineStr">
+      <c r="AE335" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.inorgchem.5b01135</t>
         </is>
@@ -29686,7 +30238,7 @@
         <v>1.17</v>
       </c>
       <c r="W336" s="3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X336" s="3" t="n">
         <v>0.91</v>
@@ -29698,15 +30250,18 @@
         <v>0.96</v>
       </c>
       <c r="AA336" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB336" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="AB336" s="3" t="n">
+      <c r="AC336" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="AC336" s="3" t="n">
+      <c r="AD336" s="3" t="n">
         <v>0.19</v>
       </c>
-      <c r="AD336" s="2" t="inlineStr">
+      <c r="AE336" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -29730,7 +30285,7 @@
         <v>3.14</v>
       </c>
       <c r="E337" s="3" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="F337" s="2" t="inlineStr"/>
       <c r="G337" s="3" t="n">
@@ -29740,7 +30295,7 @@
         <v>3.2</v>
       </c>
       <c r="I337" s="3" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="J337" s="3" t="n">
         <v>3.01</v>
@@ -29785,10 +30340,11 @@
       <c r="Z337" s="2" t="inlineStr"/>
       <c r="AA337" s="2" t="inlineStr"/>
       <c r="AB337" s="2" t="inlineStr"/>
-      <c r="AC337" s="3" t="n">
+      <c r="AC337" s="2" t="inlineStr"/>
+      <c r="AD337" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AD337" s="2" t="inlineStr">
+      <c r="AE337" s="2" t="inlineStr">
         <is>
           <t>10.1016/S0955-2219(03)00099-2</t>
         </is>
@@ -29863,10 +30419,11 @@
       <c r="Z338" s="2" t="inlineStr"/>
       <c r="AA338" s="2" t="inlineStr"/>
       <c r="AB338" s="2" t="inlineStr"/>
-      <c r="AC338" s="3" t="n">
+      <c r="AC338" s="2" t="inlineStr"/>
+      <c r="AD338" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD338" s="2" t="inlineStr">
+      <c r="AE338" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(65)90140-X</t>
         </is>
@@ -29939,20 +30496,21 @@
         <v>1.47</v>
       </c>
       <c r="V339" s="3" t="n">
-        <v>0.29</v>
+        <v>0.19</v>
       </c>
       <c r="W339" s="3" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="X339" s="2" t="inlineStr"/>
       <c r="Y339" s="2" t="inlineStr"/>
       <c r="Z339" s="2" t="inlineStr"/>
       <c r="AA339" s="2" t="inlineStr"/>
       <c r="AB339" s="2" t="inlineStr"/>
-      <c r="AC339" s="3" t="n">
+      <c r="AC339" s="2" t="inlineStr"/>
+      <c r="AD339" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="AD339" s="2" t="inlineStr">
+      <c r="AE339" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(65)90140-X</t>
         </is>
@@ -30025,20 +30583,21 @@
         <v>0.97</v>
       </c>
       <c r="V340" s="3" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="W340" s="3" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="X340" s="2" t="inlineStr"/>
       <c r="Y340" s="2" t="inlineStr"/>
       <c r="Z340" s="2" t="inlineStr"/>
       <c r="AA340" s="2" t="inlineStr"/>
       <c r="AB340" s="2" t="inlineStr"/>
-      <c r="AC340" s="3" t="n">
+      <c r="AC340" s="2" t="inlineStr"/>
+      <c r="AD340" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="AD340" s="2" t="inlineStr">
+      <c r="AE340" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(65)90140-X</t>
         </is>
@@ -30111,20 +30670,21 @@
         <v>0.2</v>
       </c>
       <c r="V341" s="3" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="W341" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="X341" s="2" t="inlineStr"/>
       <c r="Y341" s="2" t="inlineStr"/>
       <c r="Z341" s="2" t="inlineStr"/>
       <c r="AA341" s="2" t="inlineStr"/>
       <c r="AB341" s="2" t="inlineStr"/>
-      <c r="AC341" s="3" t="n">
+      <c r="AC341" s="2" t="inlineStr"/>
+      <c r="AD341" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="AD341" s="2" t="inlineStr">
+      <c r="AE341" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(83)90061-6</t>
         </is>
@@ -30199,10 +30759,11 @@
       <c r="Z342" s="2" t="inlineStr"/>
       <c r="AA342" s="2" t="inlineStr"/>
       <c r="AB342" s="2" t="inlineStr"/>
-      <c r="AC342" s="3" t="n">
+      <c r="AC342" s="2" t="inlineStr"/>
+      <c r="AD342" s="3" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD342" s="2" t="inlineStr">
+      <c r="AE342" s="2" t="inlineStr">
         <is>
           <t>10.1002/(SICI)1521-3749(199808)624:8&lt;1285::AID-ZAAC1285&gt;3.0.CO;2-5</t>
         </is>
@@ -30277,10 +30838,11 @@
       <c r="Z343" s="2" t="inlineStr"/>
       <c r="AA343" s="2" t="inlineStr"/>
       <c r="AB343" s="2" t="inlineStr"/>
-      <c r="AC343" s="3" t="n">
+      <c r="AC343" s="2" t="inlineStr"/>
+      <c r="AD343" s="3" t="n">
         <v>2.08</v>
       </c>
-      <c r="AD343" s="2" t="inlineStr">
+      <c r="AE343" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm00034a029</t>
         </is>
@@ -30355,10 +30917,11 @@
       <c r="Z344" s="2" t="inlineStr"/>
       <c r="AA344" s="2" t="inlineStr"/>
       <c r="AB344" s="2" t="inlineStr"/>
-      <c r="AC344" s="3" t="n">
+      <c r="AC344" s="2" t="inlineStr"/>
+      <c r="AD344" s="3" t="n">
         <v>2.64</v>
       </c>
-      <c r="AD344" s="2" t="inlineStr">
+      <c r="AE344" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic025936i</t>
         </is>
@@ -30433,10 +30996,11 @@
       <c r="Z345" s="2" t="inlineStr"/>
       <c r="AA345" s="2" t="inlineStr"/>
       <c r="AB345" s="2" t="inlineStr"/>
-      <c r="AC345" s="3" t="n">
+      <c r="AC345" s="2" t="inlineStr"/>
+      <c r="AD345" s="3" t="n">
         <v>2.19</v>
       </c>
-      <c r="AD345" s="2" t="inlineStr">
+      <c r="AE345" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic025936i</t>
         </is>
@@ -30511,10 +31075,11 @@
       <c r="Z346" s="2" t="inlineStr"/>
       <c r="AA346" s="2" t="inlineStr"/>
       <c r="AB346" s="2" t="inlineStr"/>
-      <c r="AC346" s="3" t="n">
+      <c r="AC346" s="2" t="inlineStr"/>
+      <c r="AD346" s="3" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD346" s="2" t="inlineStr">
+      <c r="AE346" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic025936i</t>
         </is>
@@ -30590,17 +31155,18 @@
         <v>3.48</v>
       </c>
       <c r="W347" s="3" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="X347" s="2" t="inlineStr"/>
       <c r="Y347" s="2" t="inlineStr"/>
       <c r="Z347" s="2" t="inlineStr"/>
       <c r="AA347" s="2" t="inlineStr"/>
       <c r="AB347" s="2" t="inlineStr"/>
-      <c r="AC347" s="3" t="n">
+      <c r="AC347" s="2" t="inlineStr"/>
+      <c r="AD347" s="3" t="n">
         <v>2.19</v>
       </c>
-      <c r="AD347" s="2" t="inlineStr">
+      <c r="AE347" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -30675,10 +31241,11 @@
       <c r="Z348" s="2" t="inlineStr"/>
       <c r="AA348" s="2" t="inlineStr"/>
       <c r="AB348" s="2" t="inlineStr"/>
-      <c r="AC348" s="3" t="n">
+      <c r="AC348" s="2" t="inlineStr"/>
+      <c r="AD348" s="3" t="n">
         <v>1.43</v>
       </c>
-      <c r="AD348" s="2" t="inlineStr">
+      <c r="AE348" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -30753,10 +31320,11 @@
       <c r="Z349" s="2" t="inlineStr"/>
       <c r="AA349" s="2" t="inlineStr"/>
       <c r="AB349" s="2" t="inlineStr"/>
-      <c r="AC349" s="3" t="n">
+      <c r="AC349" s="2" t="inlineStr"/>
+      <c r="AD349" s="3" t="n">
         <v>2.19</v>
       </c>
-      <c r="AD349" s="2" t="inlineStr">
+      <c r="AE349" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic001346d</t>
         </is>
@@ -30831,10 +31399,11 @@
       <c r="Z350" s="2" t="inlineStr"/>
       <c r="AA350" s="2" t="inlineStr"/>
       <c r="AB350" s="2" t="inlineStr"/>
-      <c r="AC350" s="3" t="n">
+      <c r="AC350" s="2" t="inlineStr"/>
+      <c r="AD350" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="AD350" s="2" t="inlineStr">
+      <c r="AE350" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -30909,10 +31478,11 @@
       <c r="Z351" s="2" t="inlineStr"/>
       <c r="AA351" s="2" t="inlineStr"/>
       <c r="AB351" s="2" t="inlineStr"/>
-      <c r="AC351" s="3" t="n">
+      <c r="AC351" s="2" t="inlineStr"/>
+      <c r="AD351" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD351" s="2" t="inlineStr">
+      <c r="AE351" s="2" t="inlineStr">
         <is>
           <t>10.1006/jssc.1996.0179</t>
         </is>
@@ -30987,7 +31557,7 @@
         <v>0.79</v>
       </c>
       <c r="V352" s="3" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="W352" s="3" t="n">
         <v>1.9</v>
@@ -31001,12 +31571,15 @@
       <c r="Z352" s="3" t="n">
         <v>1.61</v>
       </c>
-      <c r="AA352" s="2" t="inlineStr"/>
+      <c r="AA352" s="3" t="n">
+        <v>1.32</v>
+      </c>
       <c r="AB352" s="2" t="inlineStr"/>
-      <c r="AC352" s="3" t="n">
+      <c r="AC352" s="2" t="inlineStr"/>
+      <c r="AD352" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="AD352" s="2" t="inlineStr">
+      <c r="AE352" s="2" t="inlineStr">
         <is>
           <t>10.1002/bbpc.19840881007</t>
         </is>
@@ -31096,15 +31669,18 @@
         <v>8.06</v>
       </c>
       <c r="AA353" s="3" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="AB353" s="3" t="n">
         <v>7.31</v>
       </c>
-      <c r="AB353" s="3" t="n">
+      <c r="AC353" s="3" t="n">
         <v>7.15</v>
       </c>
-      <c r="AC353" s="3" t="n">
+      <c r="AD353" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD353" s="2" t="inlineStr">
+      <c r="AE353" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevLett.19.496</t>
         </is>
@@ -31194,15 +31770,18 @@
         <v>9.09</v>
       </c>
       <c r="AA354" s="3" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="AB354" s="3" t="n">
         <v>8.42</v>
       </c>
-      <c r="AB354" s="3" t="n">
+      <c r="AC354" s="3" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="AC354" s="3" t="n">
+      <c r="AD354" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="AD354" s="2" t="inlineStr">
+      <c r="AE354" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRev.155.896</t>
         </is>
@@ -31277,10 +31856,11 @@
       <c r="Z355" s="2" t="inlineStr"/>
       <c r="AA355" s="2" t="inlineStr"/>
       <c r="AB355" s="2" t="inlineStr"/>
-      <c r="AC355" s="3" t="n">
+      <c r="AC355" s="2" t="inlineStr"/>
+      <c r="AD355" s="3" t="n">
         <v>1.45</v>
       </c>
-      <c r="AD355" s="2" t="inlineStr">
+      <c r="AE355" s="2" t="inlineStr">
         <is>
           <t>10.1107/S0108270100019442</t>
         </is>
@@ -31370,15 +31950,18 @@
         <v>10.9</v>
       </c>
       <c r="AA356" s="3" t="n">
-        <v>10.01</v>
+        <v>9.75</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>10.01</v>
       </c>
       <c r="AC356" s="3" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="AD356" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="AD356" s="2" t="inlineStr">
+      <c r="AE356" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRev.116.1099</t>
         </is>
@@ -31456,7 +32039,7 @@
         <v>6.06</v>
       </c>
       <c r="W357" s="3" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="X357" s="3" t="n">
         <v>6.34</v>
@@ -31468,15 +32051,18 @@
         <v>6.93</v>
       </c>
       <c r="AA357" s="3" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="AB357" s="3" t="n">
         <v>6.29</v>
       </c>
-      <c r="AB357" s="3" t="n">
+      <c r="AC357" s="3" t="n">
         <v>5.98</v>
       </c>
-      <c r="AC357" s="3" t="n">
+      <c r="AD357" s="3" t="n">
         <v>6.37</v>
       </c>
-      <c r="AD357" s="2" t="inlineStr">
+      <c r="AE357" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRev.141.797</t>
         </is>
@@ -31551,10 +32137,11 @@
       <c r="Z358" s="2" t="inlineStr"/>
       <c r="AA358" s="2" t="inlineStr"/>
       <c r="AB358" s="2" t="inlineStr"/>
-      <c r="AC358" s="3" t="n">
+      <c r="AC358" s="2" t="inlineStr"/>
+      <c r="AD358" s="3" t="n">
         <v>1.37</v>
       </c>
-      <c r="AD358" s="2" t="inlineStr">
+      <c r="AE358" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.365357</t>
         </is>
@@ -31637,10 +32224,11 @@
       <c r="Z359" s="2" t="inlineStr"/>
       <c r="AA359" s="2" t="inlineStr"/>
       <c r="AB359" s="2" t="inlineStr"/>
-      <c r="AC359" s="3" t="n">
+      <c r="AC359" s="2" t="inlineStr"/>
+      <c r="AD359" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="AD359" s="2" t="inlineStr">
+      <c r="AE359" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.365357</t>
         </is>
@@ -31716,17 +32304,18 @@
         <v>0.62</v>
       </c>
       <c r="W360" s="3" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="X360" s="2" t="inlineStr"/>
       <c r="Y360" s="2" t="inlineStr"/>
       <c r="Z360" s="2" t="inlineStr"/>
       <c r="AA360" s="2" t="inlineStr"/>
       <c r="AB360" s="2" t="inlineStr"/>
-      <c r="AC360" s="3" t="n">
+      <c r="AC360" s="2" t="inlineStr"/>
+      <c r="AD360" s="3" t="n">
         <v>1.45</v>
       </c>
-      <c r="AD360" s="2" t="inlineStr">
+      <c r="AE360" s="2" t="inlineStr">
         <is>
           <t>10.1088/0953-8984/7/21/015</t>
         </is>
@@ -31750,7 +32339,7 @@
         <v>0.37</v>
       </c>
       <c r="E361" s="3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F361" s="2" t="inlineStr"/>
       <c r="G361" s="3" t="n">
@@ -31760,7 +32349,7 @@
         <v>0.45</v>
       </c>
       <c r="I361" s="3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="J361" s="3" t="n">
         <v>0.42</v>
@@ -31799,20 +32388,21 @@
         <v>1.36</v>
       </c>
       <c r="V361" s="3" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="W361" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="X361" s="2" t="inlineStr"/>
       <c r="Y361" s="2" t="inlineStr"/>
       <c r="Z361" s="2" t="inlineStr"/>
       <c r="AA361" s="2" t="inlineStr"/>
       <c r="AB361" s="2" t="inlineStr"/>
-      <c r="AC361" s="3" t="n">
+      <c r="AC361" s="2" t="inlineStr"/>
+      <c r="AD361" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="AD361" s="2" t="inlineStr">
+      <c r="AE361" s="2" t="inlineStr">
         <is>
           <t>10.1088/0022-3719/18/32/018</t>
         </is>
@@ -31836,7 +32426,7 @@
         <v>0.08</v>
       </c>
       <c r="E362" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F362" s="2" t="inlineStr"/>
       <c r="G362" s="3" t="n">
@@ -31895,10 +32485,11 @@
       <c r="Z362" s="2" t="inlineStr"/>
       <c r="AA362" s="2" t="inlineStr"/>
       <c r="AB362" s="2" t="inlineStr"/>
-      <c r="AC362" s="3" t="n">
+      <c r="AC362" s="2" t="inlineStr"/>
+      <c r="AD362" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="AD362" s="2" t="inlineStr">
+      <c r="AE362" s="2" t="inlineStr">
         <is>
           <t>10.1016/0038-1098(96)00041-5</t>
         </is>
@@ -31973,10 +32564,11 @@
       <c r="Z363" s="2" t="inlineStr"/>
       <c r="AA363" s="2" t="inlineStr"/>
       <c r="AB363" s="2" t="inlineStr"/>
-      <c r="AC363" s="3" t="n">
+      <c r="AC363" s="2" t="inlineStr"/>
+      <c r="AD363" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="AD363" s="2" t="inlineStr">
+      <c r="AE363" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssb.2220540234</t>
         </is>
@@ -32051,10 +32643,11 @@
       <c r="Z364" s="2" t="inlineStr"/>
       <c r="AA364" s="2" t="inlineStr"/>
       <c r="AB364" s="2" t="inlineStr"/>
-      <c r="AC364" s="3" t="n">
+      <c r="AC364" s="2" t="inlineStr"/>
+      <c r="AD364" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AD364" s="2" t="inlineStr">
+      <c r="AE364" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssb.2220540234</t>
         </is>
@@ -32129,10 +32722,11 @@
       <c r="Z365" s="2" t="inlineStr"/>
       <c r="AA365" s="2" t="inlineStr"/>
       <c r="AB365" s="2" t="inlineStr"/>
-      <c r="AC365" s="3" t="n">
+      <c r="AC365" s="2" t="inlineStr"/>
+      <c r="AD365" s="3" t="n">
         <v>1.74</v>
       </c>
-      <c r="AD365" s="2" t="inlineStr">
+      <c r="AE365" s="2" t="inlineStr">
         <is>
           <t>10.1016/0040-6090(95)06577-6</t>
         </is>
@@ -32207,10 +32801,11 @@
       <c r="Z366" s="2" t="inlineStr"/>
       <c r="AA366" s="2" t="inlineStr"/>
       <c r="AB366" s="2" t="inlineStr"/>
-      <c r="AC366" s="3" t="n">
+      <c r="AC366" s="2" t="inlineStr"/>
+      <c r="AD366" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="AD366" s="2" t="inlineStr">
+      <c r="AE366" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -32299,12 +32894,15 @@
       <c r="Z367" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="AA367" s="2" t="inlineStr"/>
+      <c r="AA367" s="3" t="n">
+        <v>0.09</v>
+      </c>
       <c r="AB367" s="2" t="inlineStr"/>
-      <c r="AC367" s="3" t="n">
+      <c r="AC367" s="2" t="inlineStr"/>
+      <c r="AD367" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="AD367" s="2" t="inlineStr">
+      <c r="AE367" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -32387,10 +32985,11 @@
       <c r="Z368" s="2" t="inlineStr"/>
       <c r="AA368" s="2" t="inlineStr"/>
       <c r="AB368" s="2" t="inlineStr"/>
-      <c r="AC368" s="3" t="n">
+      <c r="AC368" s="2" t="inlineStr"/>
+      <c r="AD368" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="AD368" s="2" t="inlineStr">
+      <c r="AE368" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.optmat.2008.01.018</t>
         </is>
@@ -32465,10 +33064,11 @@
       <c r="Z369" s="2" t="inlineStr"/>
       <c r="AA369" s="2" t="inlineStr"/>
       <c r="AB369" s="2" t="inlineStr"/>
-      <c r="AC369" s="3" t="n">
+      <c r="AC369" s="2" t="inlineStr"/>
+      <c r="AD369" s="3" t="n">
         <v>2.41</v>
       </c>
-      <c r="AD369" s="2" t="inlineStr">
+      <c r="AE369" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -32546,7 +33146,7 @@
         <v>0.98</v>
       </c>
       <c r="W370" s="3" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="X370" s="3" t="n">
         <v>1.06</v>
@@ -32557,12 +33157,15 @@
       <c r="Z370" s="3" t="n">
         <v>1.38</v>
       </c>
-      <c r="AA370" s="2" t="inlineStr"/>
+      <c r="AA370" s="3" t="n">
+        <v>1.14</v>
+      </c>
       <c r="AB370" s="2" t="inlineStr"/>
-      <c r="AC370" s="3" t="n">
+      <c r="AC370" s="2" t="inlineStr"/>
+      <c r="AD370" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD370" s="2" t="inlineStr">
+      <c r="AE370" s="2" t="inlineStr">
         <is>
           <t>10.1002/zaac.200400256</t>
         </is>
@@ -32586,7 +33189,7 @@
         <v>1.52</v>
       </c>
       <c r="E371" s="3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="F371" s="2" t="inlineStr"/>
       <c r="G371" s="3" t="n">
@@ -32596,7 +33199,7 @@
         <v>1.65</v>
       </c>
       <c r="I371" s="3" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="J371" s="3" t="n">
         <v>1.58</v>
@@ -32635,20 +33238,21 @@
         <v>2.69</v>
       </c>
       <c r="V371" s="3" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="W371" s="3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X371" s="2" t="inlineStr"/>
       <c r="Y371" s="2" t="inlineStr"/>
       <c r="Z371" s="2" t="inlineStr"/>
       <c r="AA371" s="2" t="inlineStr"/>
       <c r="AB371" s="2" t="inlineStr"/>
-      <c r="AC371" s="3" t="n">
+      <c r="AC371" s="2" t="inlineStr"/>
+      <c r="AD371" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="AD371" s="2" t="inlineStr">
+      <c r="AE371" s="2" t="inlineStr">
         <is>
           <t>10.1088/0268-1242/10/8/021</t>
         </is>
@@ -32721,7 +33325,7 @@
         <v>2.09</v>
       </c>
       <c r="V372" s="3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="W372" s="3" t="n">
         <v>1.77</v>
@@ -32731,10 +33335,11 @@
       <c r="Z372" s="2" t="inlineStr"/>
       <c r="AA372" s="2" t="inlineStr"/>
       <c r="AB372" s="2" t="inlineStr"/>
-      <c r="AC372" s="3" t="n">
+      <c r="AC372" s="2" t="inlineStr"/>
+      <c r="AD372" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD372" s="2" t="inlineStr">
+      <c r="AE372" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic401086r</t>
         </is>
@@ -32768,7 +33373,7 @@
         <v>1.62</v>
       </c>
       <c r="I373" s="3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J373" s="3" t="n">
         <v>1.42</v>
@@ -32810,17 +33415,18 @@
         <v>2.1</v>
       </c>
       <c r="W373" s="3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X373" s="2" t="inlineStr"/>
       <c r="Y373" s="2" t="inlineStr"/>
       <c r="Z373" s="2" t="inlineStr"/>
       <c r="AA373" s="2" t="inlineStr"/>
       <c r="AB373" s="2" t="inlineStr"/>
-      <c r="AC373" s="3" t="n">
+      <c r="AC373" s="2" t="inlineStr"/>
+      <c r="AD373" s="3" t="n">
         <v>1.88</v>
       </c>
-      <c r="AD373" s="2" t="inlineStr">
+      <c r="AE373" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -32895,10 +33501,10 @@
         <v>1.8</v>
       </c>
       <c r="V374" s="3" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W374" s="3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X374" s="3" t="n">
         <v>0.87</v>
@@ -32910,15 +33516,18 @@
         <v>1.54</v>
       </c>
       <c r="AA374" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB374" s="3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AB374" s="3" t="n">
+      <c r="AC374" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC374" s="3" t="n">
+      <c r="AD374" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="AD374" s="2" t="inlineStr">
+      <c r="AE374" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.70.045303</t>
         </is>
@@ -32993,7 +33602,7 @@
         <v>0.74</v>
       </c>
       <c r="V375" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="W375" s="3" t="n">
         <v>0.13</v>
@@ -33008,15 +33617,18 @@
         <v>0.51</v>
       </c>
       <c r="AA375" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AB375" s="3" t="n">
         <v>0.44</v>
       </c>
-      <c r="AB375" s="3" t="n">
+      <c r="AC375" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="AC375" s="3" t="n">
+      <c r="AD375" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="AD375" s="2" t="inlineStr">
+      <c r="AE375" s="2" t="inlineStr">
         <is>
           <t>10.1088/0953-8984/15/4/304</t>
         </is>
@@ -33106,15 +33718,18 @@
         <v>0.48</v>
       </c>
       <c r="AA376" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB376" s="3" t="n">
         <v>0.43</v>
       </c>
-      <c r="AB376" s="3" t="n">
+      <c r="AC376" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="AC376" s="3" t="n">
+      <c r="AD376" s="3" t="n">
         <v>0.23</v>
       </c>
-      <c r="AD376" s="2" t="inlineStr">
+      <c r="AE376" s="2" t="inlineStr">
         <is>
           <t>10.1088/0953-8984/15/4/304</t>
         </is>
@@ -33207,12 +33822,15 @@
         <v>1.13</v>
       </c>
       <c r="AB377" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC377" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="AC377" s="3" t="n">
+      <c r="AD377" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="AD377" s="2" t="inlineStr">
+      <c r="AE377" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -33287,10 +33905,11 @@
       <c r="Z378" s="2" t="inlineStr"/>
       <c r="AA378" s="2" t="inlineStr"/>
       <c r="AB378" s="2" t="inlineStr"/>
-      <c r="AC378" s="3" t="n">
+      <c r="AC378" s="2" t="inlineStr"/>
+      <c r="AD378" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="AD378" s="2" t="inlineStr">
+      <c r="AE378" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.1652607</t>
         </is>
@@ -33314,7 +33933,7 @@
         <v>0.71</v>
       </c>
       <c r="E379" s="3" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="F379" s="2" t="inlineStr"/>
       <c r="G379" s="3" t="n">
@@ -33324,7 +33943,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I379" s="3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="J379" s="3" t="n">
         <v>0.8</v>
@@ -33364,17 +33983,18 @@
       </c>
       <c r="V379" s="2" t="inlineStr"/>
       <c r="W379" s="3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X379" s="2" t="inlineStr"/>
       <c r="Y379" s="2" t="inlineStr"/>
       <c r="Z379" s="2" t="inlineStr"/>
       <c r="AA379" s="2" t="inlineStr"/>
       <c r="AB379" s="2" t="inlineStr"/>
-      <c r="AC379" s="3" t="n">
+      <c r="AC379" s="2" t="inlineStr"/>
+      <c r="AD379" s="3" t="n">
         <v>1.45</v>
       </c>
-      <c r="AD379" s="2" t="inlineStr">
+      <c r="AE379" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -33449,10 +34069,10 @@
         <v>2.34</v>
       </c>
       <c r="V380" s="3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="W380" s="3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="X380" s="3" t="n">
         <v>2.48</v>
@@ -33464,15 +34084,18 @@
         <v>2.68</v>
       </c>
       <c r="AA380" s="3" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AB380" s="3" t="n">
         <v>2.39</v>
       </c>
       <c r="AC380" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD380" s="3" t="n">
         <v>2.42</v>
       </c>
-      <c r="AD380" s="2" t="inlineStr">
+      <c r="AE380" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -33547,10 +34170,10 @@
         <v>3.26</v>
       </c>
       <c r="V381" s="3" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="W381" s="3" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="X381" s="3" t="n">
         <v>3.41</v>
@@ -33559,14 +34182,15 @@
       <c r="Z381" s="3" t="n">
         <v>3.59</v>
       </c>
-      <c r="AA381" s="3" t="n">
+      <c r="AA381" s="2" t="inlineStr"/>
+      <c r="AB381" s="3" t="n">
         <v>3.34</v>
       </c>
-      <c r="AB381" s="2" t="inlineStr"/>
-      <c r="AC381" s="3" t="n">
+      <c r="AC381" s="2" t="inlineStr"/>
+      <c r="AD381" s="3" t="n">
         <v>3.33</v>
       </c>
-      <c r="AD381" s="2" t="inlineStr">
+      <c r="AE381" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -33649,10 +34273,11 @@
       <c r="Z382" s="2" t="inlineStr"/>
       <c r="AA382" s="2" t="inlineStr"/>
       <c r="AB382" s="2" t="inlineStr"/>
-      <c r="AC382" s="3" t="n">
+      <c r="AC382" s="2" t="inlineStr"/>
+      <c r="AD382" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="AD382" s="2" t="inlineStr">
+      <c r="AE382" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -33735,10 +34360,11 @@
       <c r="Z383" s="2" t="inlineStr"/>
       <c r="AA383" s="2" t="inlineStr"/>
       <c r="AB383" s="2" t="inlineStr"/>
-      <c r="AC383" s="3" t="n">
+      <c r="AC383" s="2" t="inlineStr"/>
+      <c r="AD383" s="3" t="n">
         <v>2.86</v>
       </c>
-      <c r="AD383" s="2" t="inlineStr">
+      <c r="AE383" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -33811,7 +34437,7 @@
         <v>10.45</v>
       </c>
       <c r="V384" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="W384" s="3" t="n">
         <v>9.07</v>
@@ -33821,10 +34447,11 @@
       <c r="Z384" s="2" t="inlineStr"/>
       <c r="AA384" s="2" t="inlineStr"/>
       <c r="AB384" s="2" t="inlineStr"/>
-      <c r="AC384" s="3" t="n">
+      <c r="AC384" s="2" t="inlineStr"/>
+      <c r="AD384" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="AD384" s="2" t="inlineStr">
+      <c r="AE384" s="2" t="inlineStr">
         <is>
           <t>10.1016/0038-1098(71)90643-0</t>
         </is>
@@ -33899,10 +34526,11 @@
       <c r="Z385" s="2" t="inlineStr"/>
       <c r="AA385" s="2" t="inlineStr"/>
       <c r="AB385" s="2" t="inlineStr"/>
-      <c r="AC385" s="3" t="n">
+      <c r="AC385" s="2" t="inlineStr"/>
+      <c r="AD385" s="3" t="n">
         <v>1.89</v>
       </c>
-      <c r="AD385" s="2" t="inlineStr">
+      <c r="AE385" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -33992,15 +34620,18 @@
         <v>0.17</v>
       </c>
       <c r="AA386" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB386" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="AB386" s="3" t="n">
+      <c r="AC386" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AC386" s="3" t="n">
+      <c r="AD386" s="3" t="n">
         <v>0.09</v>
       </c>
-      <c r="AD386" s="2" t="inlineStr">
+      <c r="AE386" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -34075,10 +34706,11 @@
       <c r="Z387" s="2" t="inlineStr"/>
       <c r="AA387" s="2" t="inlineStr"/>
       <c r="AB387" s="2" t="inlineStr"/>
-      <c r="AC387" s="3" t="n">
+      <c r="AC387" s="2" t="inlineStr"/>
+      <c r="AD387" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD387" s="2" t="inlineStr">
+      <c r="AE387" s="2" t="inlineStr">
         <is>
           <t>10.1002/crat.2170251214</t>
         </is>
@@ -34102,7 +34734,7 @@
         <v>2.22</v>
       </c>
       <c r="E388" s="3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="F388" s="2" t="inlineStr"/>
       <c r="G388" s="3" t="n">
@@ -34161,10 +34793,11 @@
       <c r="Z388" s="2" t="inlineStr"/>
       <c r="AA388" s="2" t="inlineStr"/>
       <c r="AB388" s="2" t="inlineStr"/>
-      <c r="AC388" s="3" t="n">
+      <c r="AC388" s="2" t="inlineStr"/>
+      <c r="AD388" s="3" t="n">
         <v>3.45</v>
       </c>
-      <c r="AD388" s="2" t="inlineStr">
+      <c r="AE388" s="2" t="inlineStr">
         <is>
           <t>10.1002/1521-3951(200102)223:3&lt;723::AID-PSSB723&gt;3.0.CO;2-S</t>
         </is>
@@ -34188,7 +34821,7 @@
         <v>2.9</v>
       </c>
       <c r="E389" s="3" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="F389" s="2" t="inlineStr"/>
       <c r="G389" s="3" t="n">
@@ -34198,7 +34831,7 @@
         <v>3.06</v>
       </c>
       <c r="I389" s="3" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="J389" s="3" t="n">
         <v>3.01</v>
@@ -34237,20 +34870,21 @@
         <v>4.7</v>
       </c>
       <c r="V389" s="3" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="W389" s="3" t="n">
         <v>4.33</v>
-      </c>
-      <c r="W389" s="3" t="n">
-        <v>4.32</v>
       </c>
       <c r="X389" s="2" t="inlineStr"/>
       <c r="Y389" s="2" t="inlineStr"/>
       <c r="Z389" s="2" t="inlineStr"/>
       <c r="AA389" s="2" t="inlineStr"/>
       <c r="AB389" s="2" t="inlineStr"/>
-      <c r="AC389" s="3" t="n">
+      <c r="AC389" s="2" t="inlineStr"/>
+      <c r="AD389" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="AD389" s="2" t="inlineStr">
+      <c r="AE389" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.3576118</t>
         </is>
@@ -34340,15 +34974,18 @@
         <v>4.44</v>
       </c>
       <c r="AA390" s="3" t="n">
-        <v>4.12</v>
+        <v>3.85</v>
       </c>
       <c r="AB390" s="3" t="n">
         <v>4.12</v>
       </c>
       <c r="AC390" s="3" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AD390" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="AD390" s="2" t="inlineStr">
+      <c r="AE390" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -34372,7 +35009,7 @@
         <v>0.7</v>
       </c>
       <c r="E391" s="3" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="F391" s="2" t="inlineStr"/>
       <c r="G391" s="3" t="n">
@@ -34382,7 +35019,7 @@
         <v>0.73</v>
       </c>
       <c r="I391" s="3" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="J391" s="3" t="n">
         <v>0.72</v>
@@ -34421,20 +35058,21 @@
         <v>1.34</v>
       </c>
       <c r="V391" s="3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W391" s="3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X391" s="2" t="inlineStr"/>
       <c r="Y391" s="2" t="inlineStr"/>
       <c r="Z391" s="2" t="inlineStr"/>
       <c r="AA391" s="2" t="inlineStr"/>
       <c r="AB391" s="2" t="inlineStr"/>
-      <c r="AC391" s="3" t="n">
+      <c r="AC391" s="2" t="inlineStr"/>
+      <c r="AD391" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="AD391" s="2" t="inlineStr">
+      <c r="AE391" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.solmat.2003.06.002</t>
         </is>
@@ -34458,7 +35096,7 @@
         <v>1.23</v>
       </c>
       <c r="E392" s="3" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="F392" s="3" t="n">
         <v>1.25</v>
@@ -34470,7 +35108,7 @@
         <v>1.43</v>
       </c>
       <c r="I392" s="3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="J392" s="3" t="n">
         <v>1.42</v>
@@ -34509,10 +35147,10 @@
         <v>2.67</v>
       </c>
       <c r="V392" s="3" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="W392" s="3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X392" s="3" t="n">
         <v>2.57</v>
@@ -34523,12 +35161,15 @@
       <c r="Z392" s="3" t="n">
         <v>2.84</v>
       </c>
-      <c r="AA392" s="2" t="inlineStr"/>
+      <c r="AA392" s="3" t="n">
+        <v>2.53</v>
+      </c>
       <c r="AB392" s="2" t="inlineStr"/>
-      <c r="AC392" s="3" t="n">
+      <c r="AC392" s="2" t="inlineStr"/>
+      <c r="AD392" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="AD392" s="2" t="inlineStr">
+      <c r="AE392" s="2" t="inlineStr">
         <is>
           <t>10.1039/c5ta08214e</t>
         </is>
@@ -34604,17 +35245,18 @@
         <v>1.18</v>
       </c>
       <c r="W393" s="3" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="X393" s="2" t="inlineStr"/>
       <c r="Y393" s="2" t="inlineStr"/>
       <c r="Z393" s="2" t="inlineStr"/>
       <c r="AA393" s="2" t="inlineStr"/>
       <c r="AB393" s="2" t="inlineStr"/>
-      <c r="AC393" s="3" t="n">
+      <c r="AC393" s="2" t="inlineStr"/>
+      <c r="AD393" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="AD393" s="2" t="inlineStr">
+      <c r="AE393" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -34638,7 +35280,7 @@
         <v>0.54</v>
       </c>
       <c r="E394" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="F394" s="3" t="n">
         <v>0.57</v>
@@ -34650,7 +35292,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I394" s="3" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J394" s="3" t="n">
         <v>0.66</v>
@@ -34689,10 +35331,10 @@
         <v>1.65</v>
       </c>
       <c r="V394" s="3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W394" s="3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X394" s="3" t="n">
         <v>1.54</v>
@@ -34703,12 +35345,15 @@
       <c r="Z394" s="3" t="n">
         <v>1.76</v>
       </c>
-      <c r="AA394" s="2" t="inlineStr"/>
+      <c r="AA394" s="3" t="n">
+        <v>1.53</v>
+      </c>
       <c r="AB394" s="2" t="inlineStr"/>
-      <c r="AC394" s="3" t="n">
+      <c r="AC394" s="2" t="inlineStr"/>
+      <c r="AD394" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="AD394" s="2" t="inlineStr">
+      <c r="AE394" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -34798,15 +35443,18 @@
         <v>0.03</v>
       </c>
       <c r="AA395" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB395" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="AB395" s="3" t="n">
+      <c r="AC395" s="3" t="n">
         <v>0.27</v>
       </c>
-      <c r="AC395" s="3" t="n">
+      <c r="AD395" s="3" t="n">
         <v>0.36</v>
       </c>
-      <c r="AD395" s="2" t="inlineStr">
+      <c r="AE395" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRev.184.830</t>
         </is>
@@ -34881,10 +35529,11 @@
       <c r="Z396" s="2" t="inlineStr"/>
       <c r="AA396" s="2" t="inlineStr"/>
       <c r="AB396" s="2" t="inlineStr"/>
-      <c r="AC396" s="3" t="n">
+      <c r="AC396" s="2" t="inlineStr"/>
+      <c r="AD396" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD396" s="2" t="inlineStr">
+      <c r="AE396" s="2" t="inlineStr">
         <is>
           <t>10.1039/c5ta02349a</t>
         </is>
@@ -34967,10 +35616,11 @@
       <c r="Z397" s="2" t="inlineStr"/>
       <c r="AA397" s="2" t="inlineStr"/>
       <c r="AB397" s="2" t="inlineStr"/>
-      <c r="AC397" s="3" t="n">
+      <c r="AC397" s="2" t="inlineStr"/>
+      <c r="AD397" s="3" t="n">
         <v>3.41</v>
       </c>
-      <c r="AD397" s="2" t="inlineStr">
+      <c r="AE397" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jallcom.2008.10.054</t>
         </is>
@@ -35049,10 +35699,11 @@
       <c r="Z398" s="2" t="inlineStr"/>
       <c r="AA398" s="2" t="inlineStr"/>
       <c r="AB398" s="2" t="inlineStr"/>
-      <c r="AC398" s="3" t="n">
+      <c r="AC398" s="2" t="inlineStr"/>
+      <c r="AD398" s="3" t="n">
         <v>3.26</v>
       </c>
-      <c r="AD398" s="2" t="inlineStr">
+      <c r="AE398" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jallcom.2008.10.054</t>
         </is>
@@ -35135,10 +35786,11 @@
       <c r="Z399" s="2" t="inlineStr"/>
       <c r="AA399" s="2" t="inlineStr"/>
       <c r="AB399" s="2" t="inlineStr"/>
-      <c r="AC399" s="3" t="n">
+      <c r="AC399" s="2" t="inlineStr"/>
+      <c r="AD399" s="3" t="n">
         <v>3.52</v>
       </c>
-      <c r="AD399" s="2" t="inlineStr">
+      <c r="AE399" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.materresbull.2014.11.032</t>
         </is>
@@ -35228,15 +35880,18 @@
         <v>8.720000000000001</v>
       </c>
       <c r="AA400" s="3" t="n">
-        <v>8.07</v>
+        <v>7.98</v>
       </c>
       <c r="AB400" s="3" t="n">
         <v>8.07</v>
       </c>
       <c r="AC400" s="3" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="AD400" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="AD400" s="2" t="inlineStr">
+      <c r="AE400" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.9.2679</t>
         </is>
@@ -35311,10 +35966,11 @@
       <c r="Z401" s="2" t="inlineStr"/>
       <c r="AA401" s="2" t="inlineStr"/>
       <c r="AB401" s="2" t="inlineStr"/>
-      <c r="AC401" s="3" t="n">
+      <c r="AC401" s="2" t="inlineStr"/>
+      <c r="AD401" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="AD401" s="2" t="inlineStr">
+      <c r="AE401" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.inorgchem.5b01135</t>
         </is>
@@ -35393,10 +36049,11 @@
       <c r="Z402" s="2" t="inlineStr"/>
       <c r="AA402" s="2" t="inlineStr"/>
       <c r="AB402" s="2" t="inlineStr"/>
-      <c r="AC402" s="3" t="n">
+      <c r="AC402" s="2" t="inlineStr"/>
+      <c r="AD402" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="AD402" s="2" t="inlineStr">
+      <c r="AE402" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.121761</t>
         </is>
@@ -35486,15 +36143,18 @@
         <v>12.21</v>
       </c>
       <c r="AA403" s="3" t="n">
-        <v>11.61</v>
+        <v>11.06</v>
       </c>
       <c r="AB403" s="3" t="n">
         <v>11.61</v>
       </c>
       <c r="AC403" s="3" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="AD403" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD403" s="2" t="inlineStr">
+      <c r="AE403" s="2" t="inlineStr">
         <is>
           <t>10.1364/OL.13.000814</t>
         </is>
@@ -35569,10 +36229,11 @@
       <c r="Z404" s="2" t="inlineStr"/>
       <c r="AA404" s="2" t="inlineStr"/>
       <c r="AB404" s="2" t="inlineStr"/>
-      <c r="AC404" s="3" t="n">
+      <c r="AC404" s="2" t="inlineStr"/>
+      <c r="AD404" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="AD404" s="2" t="inlineStr">
+      <c r="AE404" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssc.201300375</t>
         </is>
@@ -35651,10 +36312,11 @@
       <c r="Z405" s="2" t="inlineStr"/>
       <c r="AA405" s="2" t="inlineStr"/>
       <c r="AB405" s="2" t="inlineStr"/>
-      <c r="AC405" s="3" t="n">
+      <c r="AC405" s="2" t="inlineStr"/>
+      <c r="AD405" s="3" t="n">
         <v>3.98</v>
       </c>
-      <c r="AD405" s="2" t="inlineStr">
+      <c r="AE405" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.cej.2008.01.015</t>
         </is>
@@ -35744,15 +36406,18 @@
         <v>6.41</v>
       </c>
       <c r="AA406" s="3" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="AB406" s="3" t="n">
         <v>5.83</v>
       </c>
-      <c r="AB406" s="3" t="n">
+      <c r="AC406" s="3" t="n">
         <v>5.81</v>
       </c>
-      <c r="AC406" s="3" t="n">
+      <c r="AD406" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="AD406" s="2" t="inlineStr">
+      <c r="AE406" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.81.245123</t>
         </is>
@@ -35827,10 +36492,11 @@
       <c r="Z407" s="2" t="inlineStr"/>
       <c r="AA407" s="2" t="inlineStr"/>
       <c r="AB407" s="2" t="inlineStr"/>
-      <c r="AC407" s="3" t="n">
+      <c r="AC407" s="2" t="inlineStr"/>
+      <c r="AD407" s="3" t="n">
         <v>1.78</v>
       </c>
-      <c r="AD407" s="2" t="inlineStr">
+      <c r="AE407" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jpcs.2007.03.013</t>
         </is>
@@ -35920,15 +36586,18 @@
         <v>4.75</v>
       </c>
       <c r="AA408" s="3" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AB408" s="3" t="n">
         <v>4.34</v>
       </c>
-      <c r="AB408" s="3" t="n">
+      <c r="AC408" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="AC408" s="3" t="n">
+      <c r="AD408" s="3" t="n">
         <v>4.32</v>
       </c>
-      <c r="AD408" s="2" t="inlineStr">
+      <c r="AE408" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-0248(90)90701-L</t>
         </is>
@@ -36018,15 +36687,18 @@
         <v>4.25</v>
       </c>
       <c r="AA409" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AB409" s="3" t="n">
         <v>3.86</v>
       </c>
-      <c r="AB409" s="3" t="n">
+      <c r="AC409" s="3" t="n">
         <v>3.72</v>
       </c>
-      <c r="AC409" s="3" t="n">
+      <c r="AD409" s="3" t="n">
         <v>3.81</v>
       </c>
-      <c r="AD409" s="2" t="inlineStr">
+      <c r="AE409" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-0248(90)90701-L</t>
         </is>
@@ -36101,10 +36773,11 @@
       <c r="Z410" s="2" t="inlineStr"/>
       <c r="AA410" s="2" t="inlineStr"/>
       <c r="AB410" s="2" t="inlineStr"/>
-      <c r="AC410" s="3" t="n">
+      <c r="AC410" s="2" t="inlineStr"/>
+      <c r="AD410" s="3" t="n">
         <v>4.75</v>
       </c>
-      <c r="AD410" s="2" t="inlineStr">
+      <c r="AE410" s="2" t="inlineStr">
         <is>
           <t>10.1021/acs.inorgchem.5b01135</t>
         </is>
@@ -36179,10 +36852,11 @@
       <c r="Z411" s="2" t="inlineStr"/>
       <c r="AA411" s="2" t="inlineStr"/>
       <c r="AB411" s="2" t="inlineStr"/>
-      <c r="AC411" s="3" t="n">
+      <c r="AC411" s="2" t="inlineStr"/>
+      <c r="AD411" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AD411" s="2" t="inlineStr">
+      <c r="AE411" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic034551c</t>
         </is>
@@ -36265,10 +36939,11 @@
       <c r="Z412" s="2" t="inlineStr"/>
       <c r="AA412" s="2" t="inlineStr"/>
       <c r="AB412" s="2" t="inlineStr"/>
-      <c r="AC412" s="3" t="n">
+      <c r="AC412" s="2" t="inlineStr"/>
+      <c r="AD412" s="3" t="n">
         <v>1.99</v>
       </c>
-      <c r="AD412" s="2" t="inlineStr">
+      <c r="AE412" s="2" t="inlineStr">
         <is>
           <t>10.1107/S2052520617001123</t>
         </is>
@@ -36346,17 +37021,18 @@
         <v>3.5</v>
       </c>
       <c r="W413" s="3" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="X413" s="2" t="inlineStr"/>
       <c r="Y413" s="2" t="inlineStr"/>
       <c r="Z413" s="2" t="inlineStr"/>
       <c r="AA413" s="2" t="inlineStr"/>
       <c r="AB413" s="2" t="inlineStr"/>
-      <c r="AC413" s="3" t="n">
+      <c r="AC413" s="2" t="inlineStr"/>
+      <c r="AD413" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="AD413" s="2" t="inlineStr">
+      <c r="AE413" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.1415766</t>
         </is>
@@ -36431,10 +37107,11 @@
       <c r="Z414" s="2" t="inlineStr"/>
       <c r="AA414" s="2" t="inlineStr"/>
       <c r="AB414" s="2" t="inlineStr"/>
-      <c r="AC414" s="3" t="n">
+      <c r="AC414" s="2" t="inlineStr"/>
+      <c r="AD414" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AD414" s="2" t="inlineStr">
+      <c r="AE414" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.solidstatesciences.2005.02.010</t>
         </is>
@@ -36507,7 +37184,7 @@
         <v>4.06</v>
       </c>
       <c r="V415" s="3" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="W415" s="3" t="n">
         <v>1.62</v>
@@ -36517,10 +37194,11 @@
       <c r="Z415" s="2" t="inlineStr"/>
       <c r="AA415" s="2" t="inlineStr"/>
       <c r="AB415" s="2" t="inlineStr"/>
-      <c r="AC415" s="3" t="n">
+      <c r="AC415" s="2" t="inlineStr"/>
+      <c r="AD415" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="AD415" s="2" t="inlineStr">
+      <c r="AE415" s="2" t="inlineStr">
         <is>
           <t>10.1021/jp027593f</t>
         </is>
@@ -36603,10 +37281,11 @@
       <c r="Z416" s="2" t="inlineStr"/>
       <c r="AA416" s="2" t="inlineStr"/>
       <c r="AB416" s="2" t="inlineStr"/>
-      <c r="AC416" s="3" t="n">
+      <c r="AC416" s="2" t="inlineStr"/>
+      <c r="AD416" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AD416" s="2" t="inlineStr">
+      <c r="AE416" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(87)90081-3</t>
         </is>
@@ -36689,10 +37368,11 @@
       <c r="Z417" s="2" t="inlineStr"/>
       <c r="AA417" s="2" t="inlineStr"/>
       <c r="AB417" s="2" t="inlineStr"/>
-      <c r="AC417" s="3" t="n">
+      <c r="AC417" s="2" t="inlineStr"/>
+      <c r="AD417" s="3" t="n">
         <v>3.41</v>
       </c>
-      <c r="AD417" s="2" t="inlineStr">
+      <c r="AE417" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jcrysgro.2007.03.054</t>
         </is>
@@ -36774,15 +37454,18 @@
         <v>7.1</v>
       </c>
       <c r="AA418" s="3" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AB418" s="3" t="n">
         <v>6.69</v>
       </c>
-      <c r="AB418" s="3" t="n">
+      <c r="AC418" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC418" s="3" t="n">
+      <c r="AD418" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="AD418" s="2" t="inlineStr">
+      <c r="AE418" s="2" t="inlineStr">
         <is>
           <t>10.1016/S0020-1693(99)00597-6</t>
         </is>
@@ -36865,10 +37548,11 @@
       </c>
       <c r="AA419" s="2" t="inlineStr"/>
       <c r="AB419" s="2" t="inlineStr"/>
-      <c r="AC419" s="3" t="n">
+      <c r="AC419" s="2" t="inlineStr"/>
+      <c r="AD419" s="3" t="n">
         <v>2.22</v>
       </c>
-      <c r="AD419" s="2" t="inlineStr">
+      <c r="AE419" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic300510x</t>
         </is>
@@ -36945,10 +37629,11 @@
       <c r="Z420" s="2" t="inlineStr"/>
       <c r="AA420" s="2" t="inlineStr"/>
       <c r="AB420" s="2" t="inlineStr"/>
-      <c r="AC420" s="3" t="n">
+      <c r="AC420" s="2" t="inlineStr"/>
+      <c r="AD420" s="3" t="n">
         <v>1.65</v>
       </c>
-      <c r="AD420" s="2" t="inlineStr">
+      <c r="AE420" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic300510x</t>
         </is>
@@ -37025,10 +37710,11 @@
       <c r="Z421" s="2" t="inlineStr"/>
       <c r="AA421" s="2" t="inlineStr"/>
       <c r="AB421" s="2" t="inlineStr"/>
-      <c r="AC421" s="3" t="n">
+      <c r="AC421" s="2" t="inlineStr"/>
+      <c r="AD421" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="AD421" s="2" t="inlineStr">
+      <c r="AE421" s="2" t="inlineStr">
         <is>
           <t>10.1021/ic300510x</t>
         </is>
@@ -37052,7 +37738,7 @@
         <v>2.08</v>
       </c>
       <c r="E422" s="3" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="F422" s="3" t="n">
         <v>2.13</v>
@@ -37103,7 +37789,7 @@
         <v>5.94</v>
       </c>
       <c r="V422" s="3" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="W422" s="3" t="n">
         <v>3.7</v>
@@ -37117,12 +37803,15 @@
       <c r="Z422" s="3" t="n">
         <v>4.48</v>
       </c>
-      <c r="AA422" s="2" t="inlineStr"/>
+      <c r="AA422" s="3" t="n">
+        <v>4.02</v>
+      </c>
       <c r="AB422" s="2" t="inlineStr"/>
-      <c r="AC422" s="3" t="n">
+      <c r="AC422" s="2" t="inlineStr"/>
+      <c r="AD422" s="3" t="n">
         <v>3.03</v>
       </c>
-      <c r="AD422" s="2" t="inlineStr">
+      <c r="AE422" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.18.5606</t>
         </is>
@@ -37146,7 +37835,7 @@
         <v>1.96</v>
       </c>
       <c r="E423" s="3" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="F423" s="3" t="n">
         <v>1.99</v>
@@ -37197,7 +37886,7 @@
         <v>6.02</v>
       </c>
       <c r="V423" s="3" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="W423" s="3" t="n">
         <v>3.57</v>
@@ -37207,10 +37896,11 @@
       <c r="Z423" s="2" t="inlineStr"/>
       <c r="AA423" s="2" t="inlineStr"/>
       <c r="AB423" s="2" t="inlineStr"/>
-      <c r="AC423" s="3" t="n">
+      <c r="AC423" s="2" t="inlineStr"/>
+      <c r="AD423" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="AD423" s="2" t="inlineStr">
+      <c r="AE423" s="2" t="inlineStr">
         <is>
           <t>10.1016/0038-1098(93)90427-O</t>
         </is>
@@ -37285,10 +37975,11 @@
       <c r="Z424" s="2" t="inlineStr"/>
       <c r="AA424" s="2" t="inlineStr"/>
       <c r="AB424" s="2" t="inlineStr"/>
-      <c r="AC424" s="3" t="n">
+      <c r="AC424" s="2" t="inlineStr"/>
+      <c r="AD424" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD424" s="2" t="inlineStr">
+      <c r="AE424" s="2" t="inlineStr">
         <is>
           <t>10.1002/(SICI)1099-0682(199802)1998:2&lt;283::AID-EJIC283&gt;3.0.CO;2-L</t>
         </is>
@@ -37363,10 +38054,11 @@
       <c r="Z425" s="2" t="inlineStr"/>
       <c r="AA425" s="2" t="inlineStr"/>
       <c r="AB425" s="2" t="inlineStr"/>
-      <c r="AC425" s="3" t="n">
+      <c r="AC425" s="2" t="inlineStr"/>
+      <c r="AD425" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD425" s="2" t="inlineStr">
+      <c r="AE425" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm050412c</t>
         </is>
@@ -37441,10 +38133,11 @@
       <c r="Z426" s="2" t="inlineStr"/>
       <c r="AA426" s="2" t="inlineStr"/>
       <c r="AB426" s="2" t="inlineStr"/>
-      <c r="AC426" s="3" t="n">
+      <c r="AC426" s="2" t="inlineStr"/>
+      <c r="AD426" s="3" t="n">
         <v>2.06</v>
       </c>
-      <c r="AD426" s="2" t="inlineStr">
+      <c r="AE426" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -37519,10 +38212,11 @@
       <c r="Z427" s="2" t="inlineStr"/>
       <c r="AA427" s="2" t="inlineStr"/>
       <c r="AB427" s="2" t="inlineStr"/>
-      <c r="AC427" s="3" t="n">
+      <c r="AC427" s="2" t="inlineStr"/>
+      <c r="AD427" s="3" t="n">
         <v>1.47</v>
       </c>
-      <c r="AD427" s="2" t="inlineStr">
+      <c r="AE427" s="2" t="inlineStr">
         <is>
           <t>10.1134/S0020168511010109</t>
         </is>
@@ -37597,10 +38291,11 @@
       <c r="Z428" s="2" t="inlineStr"/>
       <c r="AA428" s="2" t="inlineStr"/>
       <c r="AB428" s="2" t="inlineStr"/>
-      <c r="AC428" s="3" t="n">
+      <c r="AC428" s="2" t="inlineStr"/>
+      <c r="AD428" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="AD428" s="2" t="inlineStr">
+      <c r="AE428" s="2" t="inlineStr">
         <is>
           <t>10.1002/zaac.200670073</t>
         </is>
@@ -37673,20 +38368,21 @@
         <v>0.18</v>
       </c>
       <c r="V429" s="3" t="n">
-        <v>0.38</v>
+        <v>0.03</v>
       </c>
       <c r="W429" s="3" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="X429" s="2" t="inlineStr"/>
       <c r="Y429" s="2" t="inlineStr"/>
       <c r="Z429" s="2" t="inlineStr"/>
       <c r="AA429" s="2" t="inlineStr"/>
       <c r="AB429" s="2" t="inlineStr"/>
-      <c r="AC429" s="3" t="n">
+      <c r="AC429" s="2" t="inlineStr"/>
+      <c r="AD429" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD429" s="2" t="inlineStr">
+      <c r="AE429" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm401737s</t>
         </is>
@@ -37761,10 +38457,11 @@
       <c r="Z430" s="2" t="inlineStr"/>
       <c r="AA430" s="2" t="inlineStr"/>
       <c r="AB430" s="2" t="inlineStr"/>
-      <c r="AC430" s="3" t="n">
+      <c r="AC430" s="2" t="inlineStr"/>
+      <c r="AD430" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="AD430" s="2" t="inlineStr">
+      <c r="AE430" s="2" t="inlineStr">
         <is>
           <t>10.1021/cg5001446</t>
         </is>
@@ -37854,15 +38551,18 @@
         <v>3.32</v>
       </c>
       <c r="AA431" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB431" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="AB431" s="3" t="n">
+      <c r="AC431" s="3" t="n">
         <v>2.41</v>
       </c>
-      <c r="AC431" s="3" t="n">
+      <c r="AD431" s="3" t="n">
         <v>2.66</v>
       </c>
-      <c r="AD431" s="2" t="inlineStr">
+      <c r="AE431" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.4874265</t>
         </is>
@@ -37952,15 +38652,18 @@
         <v>3.88</v>
       </c>
       <c r="AA432" s="3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB432" s="3" t="n">
         <v>3.54</v>
       </c>
-      <c r="AB432" s="3" t="n">
+      <c r="AC432" s="3" t="n">
         <v>3.27</v>
       </c>
-      <c r="AC432" s="3" t="n">
+      <c r="AD432" s="3" t="n">
         <v>3.23</v>
       </c>
-      <c r="AD432" s="2" t="inlineStr">
+      <c r="AE432" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -38043,10 +38746,11 @@
       <c r="Z433" s="2" t="inlineStr"/>
       <c r="AA433" s="2" t="inlineStr"/>
       <c r="AB433" s="2" t="inlineStr"/>
-      <c r="AC433" s="3" t="n">
+      <c r="AC433" s="2" t="inlineStr"/>
+      <c r="AD433" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD433" s="2" t="inlineStr">
+      <c r="AE433" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -38135,12 +38839,15 @@
       <c r="Z434" s="3" t="n">
         <v>2.63</v>
       </c>
-      <c r="AA434" s="2" t="inlineStr"/>
+      <c r="AA434" s="3" t="n">
+        <v>2.43</v>
+      </c>
       <c r="AB434" s="2" t="inlineStr"/>
-      <c r="AC434" s="3" t="n">
+      <c r="AC434" s="2" t="inlineStr"/>
+      <c r="AD434" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD434" s="2" t="inlineStr">
+      <c r="AE434" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -38229,12 +38936,15 @@
       <c r="Z435" s="3" t="n">
         <v>3.07</v>
       </c>
-      <c r="AA435" s="2" t="inlineStr"/>
+      <c r="AA435" s="3" t="n">
+        <v>2.89</v>
+      </c>
       <c r="AB435" s="2" t="inlineStr"/>
-      <c r="AC435" s="3" t="n">
+      <c r="AC435" s="2" t="inlineStr"/>
+      <c r="AD435" s="3" t="n">
         <v>2.87</v>
       </c>
-      <c r="AD435" s="2" t="inlineStr">
+      <c r="AE435" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -38309,7 +39019,7 @@
         <v>3.07</v>
       </c>
       <c r="V436" s="3" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="W436" s="3" t="n">
         <v>3.87</v>
@@ -38324,15 +39034,18 @@
         <v>3.08</v>
       </c>
       <c r="AA436" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB436" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="AB436" s="3" t="n">
+      <c r="AC436" s="3" t="n">
         <v>2.59</v>
       </c>
-      <c r="AC436" s="3" t="n">
+      <c r="AD436" s="3" t="n">
         <v>2.92</v>
       </c>
-      <c r="AD436" s="2" t="inlineStr">
+      <c r="AE436" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -38405,20 +39118,21 @@
         <v>0.72</v>
       </c>
       <c r="V437" s="3" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="W437" s="3" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="X437" s="2" t="inlineStr"/>
       <c r="Y437" s="2" t="inlineStr"/>
       <c r="Z437" s="2" t="inlineStr"/>
       <c r="AA437" s="2" t="inlineStr"/>
       <c r="AB437" s="2" t="inlineStr"/>
-      <c r="AC437" s="3" t="n">
+      <c r="AC437" s="2" t="inlineStr"/>
+      <c r="AD437" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="AD437" s="2" t="inlineStr">
+      <c r="AE437" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -38501,10 +39215,11 @@
       <c r="Z438" s="2" t="inlineStr"/>
       <c r="AA438" s="2" t="inlineStr"/>
       <c r="AB438" s="2" t="inlineStr"/>
-      <c r="AC438" s="3" t="n">
+      <c r="AC438" s="2" t="inlineStr"/>
+      <c r="AD438" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="AD438" s="2" t="inlineStr">
+      <c r="AE438" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -38577,7 +39292,7 @@
         <v>1.8</v>
       </c>
       <c r="V439" s="3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W439" s="3" t="n">
         <v>1.27</v>
@@ -38587,10 +39302,11 @@
       <c r="Z439" s="2" t="inlineStr"/>
       <c r="AA439" s="2" t="inlineStr"/>
       <c r="AB439" s="2" t="inlineStr"/>
-      <c r="AC439" s="3" t="n">
+      <c r="AC439" s="2" t="inlineStr"/>
+      <c r="AD439" s="3" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD439" s="2" t="inlineStr">
+      <c r="AE439" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -38614,7 +39330,7 @@
         <v>0.77</v>
       </c>
       <c r="E440" s="3" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="F440" s="2" t="inlineStr"/>
       <c r="G440" s="3" t="n">
@@ -38663,20 +39379,21 @@
         <v>1.84</v>
       </c>
       <c r="V440" s="3" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="W440" s="3" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="X440" s="2" t="inlineStr"/>
       <c r="Y440" s="2" t="inlineStr"/>
       <c r="Z440" s="2" t="inlineStr"/>
       <c r="AA440" s="2" t="inlineStr"/>
       <c r="AB440" s="2" t="inlineStr"/>
-      <c r="AC440" s="3" t="n">
+      <c r="AC440" s="2" t="inlineStr"/>
+      <c r="AD440" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="AD440" s="2" t="inlineStr">
+      <c r="AE440" s="2" t="inlineStr">
         <is>
           <t>10.1002/zaac.200700440</t>
         </is>
@@ -38751,7 +39468,7 @@
         <v>1.37</v>
       </c>
       <c r="V441" s="3" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="W441" s="3" t="n">
         <v>2.05</v>
@@ -38765,12 +39482,15 @@
       <c r="Z441" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="AA441" s="2" t="inlineStr"/>
+      <c r="AA441" s="3" t="n">
+        <v>1.14</v>
+      </c>
       <c r="AB441" s="2" t="inlineStr"/>
-      <c r="AC441" s="3" t="n">
+      <c r="AC441" s="2" t="inlineStr"/>
+      <c r="AD441" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="AD441" s="2" t="inlineStr">
+      <c r="AE441" s="2" t="inlineStr">
         <is>
           <t>10.1002/zaac.200700440</t>
         </is>
@@ -38845,10 +39565,10 @@
         <v>0.58</v>
       </c>
       <c r="V442" s="3" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="W442" s="3" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="X442" s="3" t="n">
         <v>0.37</v>
@@ -38859,12 +39579,15 @@
       <c r="Z442" s="3" t="n">
         <v>0.66</v>
       </c>
-      <c r="AA442" s="2" t="inlineStr"/>
+      <c r="AA442" s="3" t="n">
+        <v>0.51</v>
+      </c>
       <c r="AB442" s="2" t="inlineStr"/>
-      <c r="AC442" s="3" t="n">
+      <c r="AC442" s="2" t="inlineStr"/>
+      <c r="AD442" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="AD442" s="2" t="inlineStr">
+      <c r="AE442" s="2" t="inlineStr">
         <is>
           <t>10.1002/zaac.200700440</t>
         </is>
@@ -38947,10 +39670,11 @@
       <c r="Z443" s="2" t="inlineStr"/>
       <c r="AA443" s="2" t="inlineStr"/>
       <c r="AB443" s="2" t="inlineStr"/>
-      <c r="AC443" s="3" t="n">
+      <c r="AC443" s="2" t="inlineStr"/>
+      <c r="AD443" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="AD443" s="2" t="inlineStr">
+      <c r="AE443" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -39025,10 +39749,11 @@
       <c r="Z444" s="2" t="inlineStr"/>
       <c r="AA444" s="2" t="inlineStr"/>
       <c r="AB444" s="2" t="inlineStr"/>
-      <c r="AC444" s="3" t="n">
+      <c r="AC444" s="2" t="inlineStr"/>
+      <c r="AD444" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="AD444" s="2" t="inlineStr">
+      <c r="AE444" s="2" t="inlineStr">
         <is>
           <t>10.1002/1521-3749(200207)628:7&lt;1511::AID-ZAAC1511&gt;3.0.CO;2-P</t>
         </is>
@@ -39103,10 +39828,11 @@
       <c r="Z445" s="2" t="inlineStr"/>
       <c r="AA445" s="2" t="inlineStr"/>
       <c r="AB445" s="2" t="inlineStr"/>
-      <c r="AC445" s="3" t="n">
+      <c r="AC445" s="2" t="inlineStr"/>
+      <c r="AD445" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD445" s="2" t="inlineStr">
+      <c r="AE445" s="2" t="inlineStr">
         <is>
           <t>10.1021/cm050412c</t>
         </is>
@@ -39130,7 +39856,7 @@
         <v>0.91</v>
       </c>
       <c r="E446" s="3" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="F446" s="3" t="n">
         <v>0.9</v>
@@ -39193,14 +39919,15 @@
       <c r="Z446" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="AA446" s="3" t="n">
+      <c r="AA446" s="2" t="inlineStr"/>
+      <c r="AB446" s="3" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB446" s="2" t="inlineStr"/>
-      <c r="AC446" s="3" t="n">
+      <c r="AC446" s="2" t="inlineStr"/>
+      <c r="AD446" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AD446" s="2" t="inlineStr">
+      <c r="AE446" s="2" t="inlineStr">
         <is>
           <t>10.1021/j100393a010</t>
         </is>
@@ -39236,7 +39963,7 @@
         <v>0.95</v>
       </c>
       <c r="I447" s="3" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="J447" s="3" t="n">
         <v>0.87</v>
@@ -39275,10 +40002,10 @@
         <v>1.49</v>
       </c>
       <c r="V447" s="3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W447" s="3" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X447" s="3" t="n">
         <v>1.38</v>
@@ -39289,12 +40016,15 @@
       <c r="Z447" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="AA447" s="2" t="inlineStr"/>
+      <c r="AA447" s="3" t="n">
+        <v>1.35</v>
+      </c>
       <c r="AB447" s="2" t="inlineStr"/>
-      <c r="AC447" s="3" t="n">
+      <c r="AC447" s="2" t="inlineStr"/>
+      <c r="AD447" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD447" s="2" t="inlineStr">
+      <c r="AE447" s="2" t="inlineStr">
         <is>
           <t>10.1021/j100393a010</t>
         </is>
@@ -39384,15 +40114,18 @@
         <v>9.93</v>
       </c>
       <c r="AA448" s="3" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AB448" s="3" t="n">
         <v>9.19</v>
       </c>
-      <c r="AB448" s="3" t="n">
+      <c r="AC448" s="3" t="n">
         <v>8.75</v>
       </c>
-      <c r="AC448" s="3" t="n">
+      <c r="AD448" s="3" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="AD448" s="2" t="inlineStr">
+      <c r="AE448" s="2" t="inlineStr">
         <is>
           <t>10.1016/0030-4018(86)90186-0</t>
         </is>
@@ -39467,10 +40200,11 @@
       <c r="Z449" s="2" t="inlineStr"/>
       <c r="AA449" s="2" t="inlineStr"/>
       <c r="AB449" s="2" t="inlineStr"/>
-      <c r="AC449" s="3" t="n">
+      <c r="AC449" s="2" t="inlineStr"/>
+      <c r="AD449" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD449" s="2" t="inlineStr">
+      <c r="AE449" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jlumin.2004.09.117</t>
         </is>
@@ -39494,7 +40228,7 @@
         <v>0.3</v>
       </c>
       <c r="E450" s="3" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="F450" s="3" t="n">
         <v>0.31</v>
@@ -39545,7 +40279,7 @@
         <v>0.7</v>
       </c>
       <c r="V450" s="3" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="W450" s="3" t="n">
         <v>0.42</v>
@@ -39560,15 +40294,18 @@
         <v>0.61</v>
       </c>
       <c r="AA450" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB450" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="AB450" s="3" t="n">
+      <c r="AC450" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC450" s="3" t="n">
+      <c r="AD450" s="3" t="n">
         <v>0.18</v>
       </c>
-      <c r="AD450" s="2" t="inlineStr">
+      <c r="AE450" s="2" t="inlineStr">
         <is>
           <t>10.1088/0953-8984/15/4/304</t>
         </is>
@@ -39592,7 +40329,7 @@
         <v>0.28</v>
       </c>
       <c r="E451" s="3" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="F451" s="3" t="n">
         <v>0.23</v>
@@ -39643,7 +40380,7 @@
         <v>1.13</v>
       </c>
       <c r="V451" s="3" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="W451" s="3" t="n">
         <v>0.34</v>
@@ -39658,15 +40395,18 @@
         <v>0.89</v>
       </c>
       <c r="AA451" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB451" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="AB451" s="3" t="n">
+      <c r="AC451" s="3" t="n">
         <v>0.58</v>
       </c>
-      <c r="AC451" s="3" t="n">
+      <c r="AD451" s="3" t="n">
         <v>0.16</v>
       </c>
-      <c r="AD451" s="2" t="inlineStr">
+      <c r="AE451" s="2" t="inlineStr">
         <is>
           <t>10.1088/0953-8984/15/4/304</t>
         </is>
@@ -39741,10 +40481,11 @@
       <c r="Z452" s="2" t="inlineStr"/>
       <c r="AA452" s="2" t="inlineStr"/>
       <c r="AB452" s="2" t="inlineStr"/>
-      <c r="AC452" s="3" t="n">
+      <c r="AC452" s="2" t="inlineStr"/>
+      <c r="AD452" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AD452" s="2" t="inlineStr">
+      <c r="AE452" s="2" t="inlineStr">
         <is>
           <t>10.7567/JJAPS.32S3.586</t>
         </is>
@@ -39819,10 +40560,11 @@
       <c r="Z453" s="2" t="inlineStr"/>
       <c r="AA453" s="2" t="inlineStr"/>
       <c r="AB453" s="2" t="inlineStr"/>
-      <c r="AC453" s="3" t="n">
+      <c r="AC453" s="2" t="inlineStr"/>
+      <c r="AD453" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="AD453" s="2" t="inlineStr">
+      <c r="AE453" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -39905,10 +40647,11 @@
       <c r="Z454" s="2" t="inlineStr"/>
       <c r="AA454" s="2" t="inlineStr"/>
       <c r="AB454" s="2" t="inlineStr"/>
-      <c r="AC454" s="3" t="n">
+      <c r="AC454" s="2" t="inlineStr"/>
+      <c r="AD454" s="3" t="n">
         <v>2.18</v>
       </c>
-      <c r="AD454" s="2" t="inlineStr">
+      <c r="AE454" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -39981,7 +40724,7 @@
         <v>1.96</v>
       </c>
       <c r="V455" s="3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="W455" s="3" t="n">
         <v>1.99</v>
@@ -39991,10 +40734,11 @@
       <c r="Z455" s="2" t="inlineStr"/>
       <c r="AA455" s="2" t="inlineStr"/>
       <c r="AB455" s="2" t="inlineStr"/>
-      <c r="AC455" s="3" t="n">
+      <c r="AC455" s="2" t="inlineStr"/>
+      <c r="AD455" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD455" s="2" t="inlineStr">
+      <c r="AE455" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.materresbull.2011.06.002</t>
         </is>
@@ -40077,10 +40821,11 @@
       <c r="Z456" s="2" t="inlineStr"/>
       <c r="AA456" s="2" t="inlineStr"/>
       <c r="AB456" s="2" t="inlineStr"/>
-      <c r="AC456" s="3" t="n">
+      <c r="AC456" s="2" t="inlineStr"/>
+      <c r="AD456" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD456" s="2" t="inlineStr">
+      <c r="AE456" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -40155,10 +40900,11 @@
       <c r="Z457" s="2" t="inlineStr"/>
       <c r="AA457" s="2" t="inlineStr"/>
       <c r="AB457" s="2" t="inlineStr"/>
-      <c r="AC457" s="3" t="n">
+      <c r="AC457" s="2" t="inlineStr"/>
+      <c r="AD457" s="3" t="n">
         <v>3.36</v>
       </c>
-      <c r="AD457" s="2" t="inlineStr">
+      <c r="AE457" s="2" t="inlineStr">
         <is>
           <t>10.1002/pssc.200390019</t>
         </is>
@@ -40192,7 +40938,7 @@
         <v>1.31</v>
       </c>
       <c r="I458" s="3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="J458" s="3" t="n">
         <v>1.29</v>
@@ -40234,17 +40980,18 @@
         <v>1.93</v>
       </c>
       <c r="W458" s="3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X458" s="2" t="inlineStr"/>
       <c r="Y458" s="2" t="inlineStr"/>
       <c r="Z458" s="2" t="inlineStr"/>
       <c r="AA458" s="2" t="inlineStr"/>
       <c r="AB458" s="2" t="inlineStr"/>
-      <c r="AC458" s="3" t="n">
+      <c r="AC458" s="2" t="inlineStr"/>
+      <c r="AD458" s="3" t="n">
         <v>2.02</v>
       </c>
-      <c r="AD458" s="2" t="inlineStr">
+      <c r="AE458" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.jcrysgro.2008.08.065</t>
         </is>
@@ -40327,10 +41074,11 @@
       <c r="Z459" s="2" t="inlineStr"/>
       <c r="AA459" s="2" t="inlineStr"/>
       <c r="AB459" s="2" t="inlineStr"/>
-      <c r="AC459" s="3" t="n">
+      <c r="AC459" s="2" t="inlineStr"/>
+      <c r="AD459" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="AD459" s="2" t="inlineStr">
+      <c r="AE459" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.68.235201</t>
         </is>
@@ -40420,15 +41168,18 @@
         <v>4</v>
       </c>
       <c r="AA460" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AB460" s="3" t="n">
         <v>3.41</v>
       </c>
-      <c r="AB460" s="3" t="n">
+      <c r="AC460" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="AC460" s="3" t="n">
+      <c r="AD460" s="3" t="n">
         <v>3.44</v>
       </c>
-      <c r="AD460" s="2" t="inlineStr">
+      <c r="AE460" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -40503,10 +41254,11 @@
       <c r="Z461" s="2" t="inlineStr"/>
       <c r="AA461" s="2" t="inlineStr"/>
       <c r="AB461" s="2" t="inlineStr"/>
-      <c r="AC461" s="3" t="n">
+      <c r="AC461" s="2" t="inlineStr"/>
+      <c r="AD461" s="3" t="n">
         <v>1.42</v>
       </c>
-      <c r="AD461" s="2" t="inlineStr">
+      <c r="AE461" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -40596,15 +41348,18 @@
         <v>4.21</v>
       </c>
       <c r="AA462" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB462" s="3" t="n">
         <v>3.76</v>
       </c>
-      <c r="AB462" s="3" t="n">
+      <c r="AC462" s="3" t="n">
         <v>3.74</v>
       </c>
-      <c r="AC462" s="3" t="n">
+      <c r="AD462" s="3" t="n">
         <v>3.72</v>
       </c>
-      <c r="AD462" s="2" t="inlineStr">
+      <c r="AE462" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -40694,15 +41449,18 @@
         <v>4.27</v>
       </c>
       <c r="AA463" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB463" s="3" t="n">
         <v>3.84</v>
       </c>
-      <c r="AB463" s="3" t="n">
+      <c r="AC463" s="3" t="n">
         <v>3.82</v>
       </c>
-      <c r="AC463" s="3" t="n">
+      <c r="AD463" s="3" t="n">
         <v>3.91</v>
       </c>
-      <c r="AD463" s="2" t="inlineStr">
+      <c r="AE463" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -40777,10 +41535,11 @@
       <c r="Z464" s="2" t="inlineStr"/>
       <c r="AA464" s="2" t="inlineStr"/>
       <c r="AB464" s="2" t="inlineStr"/>
-      <c r="AC464" s="3" t="n">
+      <c r="AC464" s="2" t="inlineStr"/>
+      <c r="AD464" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD464" s="2" t="inlineStr">
+      <c r="AE464" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -40858,7 +41617,7 @@
         <v>2.53</v>
       </c>
       <c r="W465" s="3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="X465" s="3" t="n">
         <v>2.71</v>
@@ -40870,15 +41629,18 @@
         <v>3.21</v>
       </c>
       <c r="AA465" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AB465" s="3" t="n">
         <v>2.84</v>
       </c>
-      <c r="AB465" s="3" t="n">
+      <c r="AC465" s="3" t="n">
         <v>2.71</v>
       </c>
-      <c r="AC465" s="3" t="n">
+      <c r="AD465" s="3" t="n">
         <v>2.82</v>
       </c>
-      <c r="AD465" s="2" t="inlineStr">
+      <c r="AE465" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -40957,10 +41719,11 @@
       <c r="Z466" s="2" t="inlineStr"/>
       <c r="AA466" s="2" t="inlineStr"/>
       <c r="AB466" s="2" t="inlineStr"/>
-      <c r="AC466" s="3" t="n">
+      <c r="AC466" s="2" t="inlineStr"/>
+      <c r="AD466" s="3" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD466" s="2" t="inlineStr">
+      <c r="AE466" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -41033,7 +41796,7 @@
         <v>2.16</v>
       </c>
       <c r="V467" s="3" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="W467" s="3" t="n">
         <v>1.99</v>
@@ -41043,10 +41806,11 @@
       <c r="Z467" s="2" t="inlineStr"/>
       <c r="AA467" s="2" t="inlineStr"/>
       <c r="AB467" s="2" t="inlineStr"/>
-      <c r="AC467" s="3" t="n">
+      <c r="AC467" s="2" t="inlineStr"/>
+      <c r="AD467" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AD467" s="2" t="inlineStr">
+      <c r="AE467" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -41119,20 +41883,21 @@
         <v>1.23</v>
       </c>
       <c r="V468" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="W468" s="3" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="X468" s="2" t="inlineStr"/>
       <c r="Y468" s="2" t="inlineStr"/>
       <c r="Z468" s="2" t="inlineStr"/>
       <c r="AA468" s="2" t="inlineStr"/>
       <c r="AB468" s="2" t="inlineStr"/>
-      <c r="AC468" s="3" t="n">
+      <c r="AC468" s="2" t="inlineStr"/>
+      <c r="AD468" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="AD468" s="2" t="inlineStr">
+      <c r="AE468" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -41213,10 +41978,11 @@
       <c r="Z469" s="2" t="inlineStr"/>
       <c r="AA469" s="2" t="inlineStr"/>
       <c r="AB469" s="2" t="inlineStr"/>
-      <c r="AC469" s="3" t="n">
+      <c r="AC469" s="2" t="inlineStr"/>
+      <c r="AD469" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="AD469" s="2" t="inlineStr">
+      <c r="AE469" s="2" t="inlineStr">
         <is>
           <t>10.1039/B921010E</t>
         </is>
@@ -41299,10 +42065,11 @@
       <c r="Z470" s="2" t="inlineStr"/>
       <c r="AA470" s="2" t="inlineStr"/>
       <c r="AB470" s="2" t="inlineStr"/>
-      <c r="AC470" s="3" t="n">
+      <c r="AC470" s="2" t="inlineStr"/>
+      <c r="AD470" s="3" t="n">
         <v>1.68</v>
       </c>
-      <c r="AD470" s="2" t="inlineStr">
+      <c r="AE470" s="2" t="inlineStr">
         <is>
           <t>10.1063/1.3442917</t>
         </is>
@@ -41378,17 +42145,18 @@
         <v>0.03</v>
       </c>
       <c r="W471" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="X471" s="2" t="inlineStr"/>
       <c r="Y471" s="2" t="inlineStr"/>
       <c r="Z471" s="2" t="inlineStr"/>
       <c r="AA471" s="2" t="inlineStr"/>
       <c r="AB471" s="2" t="inlineStr"/>
-      <c r="AC471" s="3" t="n">
+      <c r="AC471" s="2" t="inlineStr"/>
+      <c r="AD471" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="AD471" s="2" t="inlineStr">
+      <c r="AE471" s="2" t="inlineStr">
         <is>
           <t>10.1007/978-3-642-18865-7</t>
         </is>
@@ -41463,7 +42231,7 @@
         <v>1.89</v>
       </c>
       <c r="V472" s="3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="W472" s="3" t="n">
         <v>1.95</v>
@@ -41478,15 +42246,18 @@
         <v>2.13</v>
       </c>
       <c r="AA472" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB472" s="3" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB472" s="3" t="n">
+      <c r="AC472" s="3" t="n">
         <v>1.87</v>
       </c>
-      <c r="AC472" s="3" t="n">
+      <c r="AD472" s="3" t="n">
         <v>1.68</v>
       </c>
-      <c r="AD472" s="2" t="inlineStr">
+      <c r="AE472" s="2" t="inlineStr">
         <is>
           <t>10.1016/0022-3697(65)90043-0</t>
         </is>
@@ -41522,7 +42293,7 @@
         <v>0.36</v>
       </c>
       <c r="I473" s="3" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="J473" s="3" t="n">
         <v>0.21</v>
@@ -41564,7 +42335,7 @@
         <v>1.64</v>
       </c>
       <c r="W473" s="3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X473" s="3" t="n">
         <v>1.14</v>
@@ -41576,15 +42347,18 @@
         <v>1.39</v>
       </c>
       <c r="AA473" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB473" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="AB473" s="3" t="n">
+      <c r="AC473" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC473" s="3" t="n">
+      <c r="AD473" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="AD473" s="2" t="inlineStr">
+      <c r="AE473" s="2" t="inlineStr">
         <is>
           <t>10.1103/PhysRevB.80.035206</t>
         </is>
